--- a/project2_results.xlsx
+++ b/project2_results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="546" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="585" uniqueCount="39">
   <si>
     <t>Node</t>
   </si>
@@ -183,8 +183,8 @@
     <col min="1" max="1" width="5.36328125" customWidth="true"/>
     <col min="2" max="2" width="9.08984375" customWidth="true"/>
     <col min="3" max="3" width="9.08984375" customWidth="true"/>
-    <col min="4" max="4" width="7.08984375" customWidth="true"/>
-    <col min="5" max="5" width="7.08984375" customWidth="true"/>
+    <col min="4" max="4" width="8.08984375" customWidth="true"/>
+    <col min="5" max="5" width="8.08984375" customWidth="true"/>
     <col min="6" max="6" width="13.90625" customWidth="true"/>
   </cols>
   <sheetData>
@@ -265,7 +265,7 @@
         <v>0.0001</v>
       </c>
       <c r="F4" s="0">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -285,7 +285,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="0">
-        <v>50</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -305,7 +305,7 @@
         <v>5.0000000000000002e-05</v>
       </c>
       <c r="F6" s="0">
-        <v>74.999999999999886</v>
+        <v>49.999999999999879</v>
       </c>
     </row>
     <row r="7">
@@ -325,7 +325,7 @@
         <v>5.0000000000000002e-05</v>
       </c>
       <c r="F7" s="0">
-        <v>66.346153846153754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -345,7 +345,7 @@
         <v>0.0001</v>
       </c>
       <c r="F8" s="0">
-        <v>74.999999999999915</v>
+        <v>49.999999999999922</v>
       </c>
     </row>
     <row r="9">
@@ -365,7 +365,7 @@
         <v>5.0000000000000002e-05</v>
       </c>
       <c r="F9" s="0">
-        <v>83.653846153846061</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -385,7 +385,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="0">
-        <v>74.999999999999901</v>
+        <v>49.999999999999908</v>
       </c>
     </row>
     <row r="11">
@@ -405,7 +405,7 @@
         <v>7.5000000000000007e-05</v>
       </c>
       <c r="F11" s="0">
-        <v>81.730769230769127</v>
+        <v>74.999999999999915</v>
       </c>
     </row>
     <row r="12">
@@ -425,7 +425,7 @@
         <v>7.5000000000000007e-05</v>
       </c>
       <c r="F12" s="0">
-        <v>74.999999999999886</v>
+        <v>49.999999999999901</v>
       </c>
     </row>
     <row r="13">
@@ -445,7 +445,7 @@
         <v>0.0001</v>
       </c>
       <c r="F13" s="0">
-        <v>84.615384615384556</v>
+        <v>74.999999999999915</v>
       </c>
     </row>
     <row r="14">
@@ -465,7 +465,7 @@
         <v>2.5000000000000001e-05</v>
       </c>
       <c r="F14" s="0">
-        <v>68.26923076923066</v>
+        <v>24.99999999999994</v>
       </c>
     </row>
     <row r="15">
@@ -485,7 +485,7 @@
         <v>2.5000000000000001e-05</v>
       </c>
       <c r="F15" s="0">
-        <v>63.221153846153769</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -505,7 +505,7 @@
         <v>5.0000000000000002e-05</v>
       </c>
       <c r="F16" s="0">
-        <v>69.471153846153726</v>
+        <v>24.999999999999929</v>
       </c>
     </row>
     <row r="17">
@@ -525,7 +525,7 @@
         <v>7.5000000000000007e-05</v>
       </c>
       <c r="F17" s="0">
-        <v>68.269230769230674</v>
+        <v>24.99999999999995</v>
       </c>
     </row>
     <row r="18">
@@ -545,7 +545,7 @@
         <v>7.5000000000000007e-05</v>
       </c>
       <c r="F18" s="0">
-        <v>63.221153846153776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -565,7 +565,7 @@
         <v>0.0001</v>
       </c>
       <c r="F19" s="0">
-        <v>65.384615384615316</v>
+        <v>24.999999999999957</v>
       </c>
     </row>
     <row r="20">
@@ -585,7 +585,7 @@
         <v>2.5000000000000001e-05</v>
       </c>
       <c r="F20" s="0">
-        <v>74.999999999999886</v>
+        <v>49.999999999999901</v>
       </c>
     </row>
     <row r="21">
@@ -605,7 +605,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="0">
-        <v>65.384615384615287</v>
+        <v>24.99999999999995</v>
       </c>
     </row>
     <row r="22">
@@ -625,7 +625,7 @@
         <v>7.5000000000000007e-05</v>
       </c>
       <c r="F22" s="0">
-        <v>86.778846153846089</v>
+        <v>100</v>
       </c>
     </row>
     <row r="23">
@@ -645,7 +645,7 @@
         <v>5.0000000000000002e-05</v>
       </c>
       <c r="F23" s="0">
-        <v>80.528846153846061</v>
+        <v>74.999999999999915</v>
       </c>
     </row>
     <row r="24">
@@ -665,7 +665,7 @@
         <v>2.5000000000000001e-05</v>
       </c>
       <c r="F24" s="0">
-        <v>81.730769230769127</v>
+        <v>74.999999999999886</v>
       </c>
     </row>
     <row r="25">
@@ -685,7 +685,7 @@
         <v>2.5000000000000001e-05</v>
       </c>
       <c r="F25" s="0">
-        <v>86.778846153846061</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26">
@@ -705,7 +705,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="0">
-        <v>84.615384615384528</v>
+        <v>74.999999999999901</v>
       </c>
     </row>
     <row r="27">
@@ -713,19 +713,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>0.0050000000000000001</v>
+        <v>0.012500000000000001</v>
       </c>
       <c r="C27" s="0">
-        <v>-0.014999999999999999</v>
+        <v>0.087500000000000008</v>
       </c>
       <c r="D27" s="0">
-        <v>5.0000000000000004e-06</v>
+        <v>1.2500000000000001e-05</v>
       </c>
       <c r="E27" s="0">
-        <v>-1.4999999999999999e-05</v>
+        <v>8.7500000000000013e-05</v>
       </c>
       <c r="F27" s="0">
-        <v>4535500.7938482752</v>
+        <v>87.499999999999972</v>
       </c>
     </row>
     <row r="28">
@@ -733,19 +733,19 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>0.0050000000000000001</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="C28" s="0">
-        <v>-0.040000000000000001</v>
+        <v>0.087500000000000008</v>
       </c>
       <c r="D28" s="0">
-        <v>5.0000000000000004e-06</v>
+        <v>2.5000000000000001e-05</v>
       </c>
       <c r="E28" s="0">
-        <v>-4.0000000000000003e-05</v>
+        <v>8.7500000000000013e-05</v>
       </c>
       <c r="F28" s="0">
-        <v>4535471.8970458312</v>
+        <v>74.999999999999929</v>
       </c>
     </row>
     <row r="29">
@@ -753,19 +753,19 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>0.12</v>
+        <v>0.012500000000000001</v>
       </c>
       <c r="C29" s="0">
-        <v>-0.025000000000000001</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="D29" s="0">
-        <v>0.00011999999999999999</v>
+        <v>1.2500000000000001e-05</v>
       </c>
       <c r="E29" s="0">
-        <v>-2.5000000000000001e-05</v>
+        <v>0.0001</v>
       </c>
       <c r="F29" s="0">
-        <v>4535327.5242957659</v>
+        <v>87.499999999999957</v>
       </c>
     </row>
     <row r="30">
@@ -773,19 +773,19 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>0.14499999999999999</v>
+        <v>0.037500000000000013</v>
       </c>
       <c r="C30" s="0">
-        <v>-0.025000000000000001</v>
+        <v>0.0625</v>
       </c>
       <c r="D30" s="0">
-        <v>0.000145</v>
+        <v>3.750000000000001e-05</v>
       </c>
       <c r="E30" s="0">
-        <v>-2.5000000000000001e-05</v>
+        <v>6.2500000000000001e-05</v>
       </c>
       <c r="F30" s="0">
-        <v>4535287.5600163136</v>
+        <v>62.499999999999872</v>
       </c>
     </row>
     <row r="31">
@@ -793,19 +793,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>0.125</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="C31" s="0">
-        <v>0</v>
+        <v>0.0625</v>
       </c>
       <c r="D31" s="0">
-        <v>0.000125</v>
+        <v>5.0000000000000002e-05</v>
       </c>
       <c r="E31" s="0">
-        <v>0</v>
+        <v>6.2500000000000001e-05</v>
       </c>
       <c r="F31" s="0">
-        <v>4535320.6571097616</v>
+        <v>49.999999999999886</v>
       </c>
     </row>
     <row r="32">
@@ -813,19 +813,19 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>0.16</v>
+        <v>0.037500000000000013</v>
       </c>
       <c r="C32" s="0">
-        <v>-0.075000000000000011</v>
+        <v>0.075000000000000011</v>
       </c>
       <c r="D32" s="0">
-        <v>0.00016000000000000001</v>
+        <v>3.750000000000001e-05</v>
       </c>
       <c r="E32" s="0">
-        <v>-7.5000000000000007e-05</v>
+        <v>7.5000000000000007e-05</v>
       </c>
       <c r="F32" s="0">
-        <v>4535259.1542448318</v>
+        <v>62.499999999999894</v>
       </c>
     </row>
     <row r="33">
@@ -833,19 +833,19 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>0.185</v>
+        <v>0.037500000000000013</v>
       </c>
       <c r="C33" s="0">
-        <v>-0.075000000000000011</v>
+        <v>0.087500000000000008</v>
       </c>
       <c r="D33" s="0">
-        <v>0.000185</v>
+        <v>3.750000000000001e-05</v>
       </c>
       <c r="E33" s="0">
-        <v>-7.5000000000000007e-05</v>
+        <v>8.7500000000000013e-05</v>
       </c>
       <c r="F33" s="0">
-        <v>4535238.5901368866</v>
+        <v>62.499999999999901</v>
       </c>
     </row>
     <row r="34">
@@ -853,19 +853,19 @@
         <v>33</v>
       </c>
       <c r="B34" s="0">
-        <v>0.16500000000000001</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="C34" s="0">
-        <v>-0.050000000000000003</v>
+        <v>0.087500000000000008</v>
       </c>
       <c r="D34" s="0">
-        <v>0.000165</v>
+        <v>5.0000000000000002e-05</v>
       </c>
       <c r="E34" s="0">
-        <v>-5.0000000000000002e-05</v>
+        <v>8.7500000000000013e-05</v>
       </c>
       <c r="F34" s="0">
-        <v>4535262.7513132486</v>
+        <v>49.999999999999915</v>
       </c>
     </row>
     <row r="35">
@@ -873,19 +873,19 @@
         <v>34</v>
       </c>
       <c r="B35" s="0">
-        <v>0.17000000000000001</v>
+        <v>0.037500000000000013</v>
       </c>
       <c r="C35" s="0">
-        <v>-0.025000000000000001</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="D35" s="0">
-        <v>0.00017000000000000001</v>
+        <v>3.750000000000001e-05</v>
       </c>
       <c r="E35" s="0">
-        <v>-2.5000000000000001e-05</v>
+        <v>0.0001</v>
       </c>
       <c r="F35" s="0">
-        <v>4535248.7773736874</v>
+        <v>62.499999999999908</v>
       </c>
     </row>
     <row r="36">
@@ -893,19 +893,19 @@
         <v>35</v>
       </c>
       <c r="B36" s="0">
-        <v>0.19500000000000001</v>
+        <v>0.0625</v>
       </c>
       <c r="C36" s="0">
-        <v>-0.025000000000000001</v>
+        <v>0.037500000000000013</v>
       </c>
       <c r="D36" s="0">
-        <v>0.000195</v>
+        <v>6.2500000000000001e-05</v>
       </c>
       <c r="E36" s="0">
-        <v>-2.5000000000000001e-05</v>
+        <v>3.750000000000001e-05</v>
       </c>
       <c r="F36" s="0">
-        <v>4535219.0371734072</v>
+        <v>37.499999999999908</v>
       </c>
     </row>
     <row r="37">
@@ -913,19 +913,19 @@
         <v>36</v>
       </c>
       <c r="B37" s="0">
-        <v>0.17499999999999999</v>
+        <v>0.075000000000000011</v>
       </c>
       <c r="C37" s="0">
-        <v>0</v>
+        <v>0.037500000000000013</v>
       </c>
       <c r="D37" s="0">
-        <v>0.000175</v>
+        <v>7.5000000000000007e-05</v>
       </c>
       <c r="E37" s="0">
-        <v>0</v>
+        <v>3.750000000000001e-05</v>
       </c>
       <c r="F37" s="0">
-        <v>4535223.9199156454</v>
+        <v>24.999999999999929</v>
       </c>
     </row>
     <row r="38">
@@ -933,19 +933,19 @@
         <v>37</v>
       </c>
       <c r="B38" s="0">
-        <v>0.12</v>
+        <v>0.0625</v>
       </c>
       <c r="C38" s="0">
-        <v>-0.10000000000000001</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="D38" s="0">
-        <v>0.00011999999999999999</v>
+        <v>6.2500000000000001e-05</v>
       </c>
       <c r="E38" s="0">
-        <v>-0.0001</v>
+        <v>5.0000000000000002e-05</v>
       </c>
       <c r="F38" s="0">
-        <v>4535322.198724662</v>
+        <v>37.499999999999901</v>
       </c>
     </row>
     <row r="39">
@@ -953,19 +953,19 @@
         <v>38</v>
       </c>
       <c r="B39" s="0">
-        <v>0.12</v>
+        <v>0.087500000000000008</v>
       </c>
       <c r="C39" s="0">
-        <v>-0.075000000000000011</v>
+        <v>0.012500000000000001</v>
       </c>
       <c r="D39" s="0">
-        <v>0.00011999999999999999</v>
+        <v>8.7500000000000013e-05</v>
       </c>
       <c r="E39" s="0">
-        <v>-7.5000000000000007e-05</v>
+        <v>1.2500000000000001e-05</v>
       </c>
       <c r="F39" s="0">
-        <v>4535323.591241804</v>
+        <v>12.499999999999966</v>
       </c>
     </row>
     <row r="40">
@@ -976,16 +976,16 @@
         <v>0.10000000000000001</v>
       </c>
       <c r="C40" s="0">
-        <v>-0.075000000000000011</v>
+        <v>0.012500000000000001</v>
       </c>
       <c r="D40" s="0">
         <v>0.0001</v>
       </c>
       <c r="E40" s="0">
-        <v>-7.5000000000000007e-05</v>
+        <v>1.2500000000000001e-05</v>
       </c>
       <c r="F40" s="0">
-        <v>4535356.0556215728</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -993,19 +993,19 @@
         <v>40</v>
       </c>
       <c r="B41" s="0">
-        <v>0.16</v>
+        <v>0.087500000000000008</v>
       </c>
       <c r="C41" s="0">
-        <v>-0.10000000000000001</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="D41" s="0">
-        <v>0.00016000000000000001</v>
+        <v>8.7500000000000013e-05</v>
       </c>
       <c r="E41" s="0">
-        <v>-0.0001</v>
+        <v>2.5000000000000001e-05</v>
       </c>
       <c r="F41" s="0">
-        <v>4535240.1798188193</v>
+        <v>12.499999999999961</v>
       </c>
     </row>
     <row r="42">
@@ -1013,19 +1013,19 @@
         <v>41</v>
       </c>
       <c r="B42" s="0">
-        <v>0.14000000000000001</v>
+        <v>0.087500000000000008</v>
       </c>
       <c r="C42" s="0">
-        <v>-0.075000000000000011</v>
+        <v>0.037500000000000013</v>
       </c>
       <c r="D42" s="0">
-        <v>0.00014000000000000002</v>
+        <v>8.7500000000000013e-05</v>
       </c>
       <c r="E42" s="0">
-        <v>-7.5000000000000007e-05</v>
+        <v>3.750000000000001e-05</v>
       </c>
       <c r="F42" s="0">
-        <v>4535290.813264248</v>
+        <v>12.499999999999954</v>
       </c>
     </row>
     <row r="43">
@@ -1033,19 +1033,19 @@
         <v>42</v>
       </c>
       <c r="B43" s="0">
-        <v>0.12</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="C43" s="0">
-        <v>-0.050000000000000003</v>
+        <v>0.037500000000000013</v>
       </c>
       <c r="D43" s="0">
-        <v>0.00011999999999999999</v>
+        <v>0.0001</v>
       </c>
       <c r="E43" s="0">
-        <v>-5.0000000000000002e-05</v>
+        <v>3.750000000000001e-05</v>
       </c>
       <c r="F43" s="0">
-        <v>4535325.7284274539</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1053,19 +1053,19 @@
         <v>43</v>
       </c>
       <c r="B44" s="0">
-        <v>0.10000000000000001</v>
+        <v>0.087500000000000008</v>
       </c>
       <c r="C44" s="0">
-        <v>-0.025000000000000001</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="D44" s="0">
-        <v>0.0001</v>
+        <v>8.7500000000000013e-05</v>
       </c>
       <c r="E44" s="0">
-        <v>-2.5000000000000001e-05</v>
+        <v>5.0000000000000002e-05</v>
       </c>
       <c r="F44" s="0">
-        <v>4535358.7941229232</v>
+        <v>12.499999999999957</v>
       </c>
     </row>
     <row r="45">
@@ -1073,19 +1073,19 @@
         <v>44</v>
       </c>
       <c r="B45" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.0625</v>
       </c>
       <c r="C45" s="0">
-        <v>-0.025000000000000001</v>
+        <v>0.087500000000000008</v>
       </c>
       <c r="D45" s="0">
-        <v>4.0000000000000003e-05</v>
+        <v>6.2500000000000001e-05</v>
       </c>
       <c r="E45" s="0">
-        <v>-2.5000000000000001e-05</v>
+        <v>8.7500000000000013e-05</v>
       </c>
       <c r="F45" s="0">
-        <v>4535437.7140388526</v>
+        <v>37.49999999999995</v>
       </c>
     </row>
     <row r="46">
@@ -1093,19 +1093,19 @@
         <v>45</v>
       </c>
       <c r="B46" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.075000000000000011</v>
       </c>
       <c r="C46" s="0">
-        <v>-0.025000000000000001</v>
+        <v>0.087500000000000008</v>
       </c>
       <c r="D46" s="0">
-        <v>5.9999999999999995e-05</v>
+        <v>7.5000000000000007e-05</v>
       </c>
       <c r="E46" s="0">
-        <v>-2.5000000000000001e-05</v>
+        <v>8.7500000000000013e-05</v>
       </c>
       <c r="F46" s="0">
-        <v>4535412.649762976</v>
+        <v>24.999999999999957</v>
       </c>
     </row>
     <row r="47">
@@ -1113,19 +1113,19 @@
         <v>46</v>
       </c>
       <c r="B47" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.0625</v>
       </c>
       <c r="C47" s="0">
-        <v>0</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="D47" s="0">
-        <v>4.0000000000000003e-05</v>
+        <v>6.2500000000000001e-05</v>
       </c>
       <c r="E47" s="0">
-        <v>0</v>
+        <v>0.0001</v>
       </c>
       <c r="F47" s="0">
-        <v>4535436.0082661426</v>
+        <v>37.499999999999943</v>
       </c>
     </row>
     <row r="48">
@@ -1133,19 +1133,19 @@
         <v>47</v>
       </c>
       <c r="B48" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.087500000000000008</v>
       </c>
       <c r="C48" s="0">
-        <v>-0.075000000000000011</v>
+        <v>0.0625</v>
       </c>
       <c r="D48" s="0">
-        <v>8.0000000000000007e-05</v>
+        <v>8.7500000000000013e-05</v>
       </c>
       <c r="E48" s="0">
-        <v>-7.5000000000000007e-05</v>
+        <v>6.2500000000000001e-05</v>
       </c>
       <c r="F48" s="0">
-        <v>4535388.304317602</v>
+        <v>12.499999999999966</v>
       </c>
     </row>
     <row r="49">
@@ -1153,19 +1153,19 @@
         <v>48</v>
       </c>
       <c r="B49" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="C49" s="0">
-        <v>-0.050000000000000003</v>
+        <v>0.0625</v>
       </c>
       <c r="D49" s="0">
-        <v>8.0000000000000007e-05</v>
+        <v>0.0001</v>
       </c>
       <c r="E49" s="0">
-        <v>-5.0000000000000002e-05</v>
+        <v>6.2500000000000001e-05</v>
       </c>
       <c r="F49" s="0">
-        <v>4535386.3890972287</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -1173,19 +1173,19 @@
         <v>49</v>
       </c>
       <c r="B50" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.087500000000000008</v>
       </c>
       <c r="C50" s="0">
-        <v>-0.025000000000000001</v>
+        <v>0.075000000000000011</v>
       </c>
       <c r="D50" s="0">
-        <v>8.0000000000000007e-05</v>
+        <v>8.7500000000000013e-05</v>
       </c>
       <c r="E50" s="0">
-        <v>-2.5000000000000001e-05</v>
+        <v>7.5000000000000007e-05</v>
       </c>
       <c r="F50" s="0">
-        <v>4535386.5502689313</v>
+        <v>12.499999999999968</v>
       </c>
     </row>
     <row r="51">
@@ -1193,19 +1193,19 @@
         <v>50</v>
       </c>
       <c r="B51" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.087500000000000008</v>
       </c>
       <c r="C51" s="0">
-        <v>0</v>
+        <v>0.087500000000000008</v>
       </c>
       <c r="D51" s="0">
-        <v>8.0000000000000007e-05</v>
+        <v>8.7500000000000013e-05</v>
       </c>
       <c r="E51" s="0">
-        <v>0</v>
+        <v>8.7500000000000013e-05</v>
       </c>
       <c r="F51" s="0">
-        <v>4535388.4722639853</v>
+        <v>12.499999999999972</v>
       </c>
     </row>
     <row r="52">
@@ -1213,19 +1213,19 @@
         <v>51</v>
       </c>
       <c r="B52" s="0">
-        <v>0.059999999999999998</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="C52" s="0">
-        <v>-0.075000000000000011</v>
+        <v>0.087500000000000008</v>
       </c>
       <c r="D52" s="0">
-        <v>5.9999999999999995e-05</v>
+        <v>0.0001</v>
       </c>
       <c r="E52" s="0">
-        <v>-7.5000000000000007e-05</v>
+        <v>8.7500000000000013e-05</v>
       </c>
       <c r="F52" s="0">
-        <v>4535420.7285713637</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1233,19 +1233,19 @@
         <v>52</v>
       </c>
       <c r="B53" s="0">
-        <v>0.080000000000000002</v>
+        <v>0.087500000000000008</v>
       </c>
       <c r="C53" s="0">
-        <v>-0.10000000000000001</v>
+        <v>0.10000000000000001</v>
       </c>
       <c r="D53" s="0">
-        <v>8.0000000000000007e-05</v>
+        <v>8.7500000000000013e-05</v>
       </c>
       <c r="E53" s="0">
-        <v>-0.0001</v>
+        <v>0.0001</v>
       </c>
       <c r="F53" s="0">
-        <v>4535389.7822650066</v>
+        <v>12.499999999999966</v>
       </c>
     </row>
     <row r="54">
@@ -1253,19 +1253,19 @@
         <v>53</v>
       </c>
       <c r="B54" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.0625</v>
       </c>
       <c r="C54" s="0">
-        <v>-0.050000000000000003</v>
+        <v>0.0625</v>
       </c>
       <c r="D54" s="0">
-        <v>4.0000000000000003e-05</v>
+        <v>6.2500000000000001e-05</v>
       </c>
       <c r="E54" s="0">
-        <v>-5.0000000000000002e-05</v>
+        <v>6.2500000000000001e-05</v>
       </c>
       <c r="F54" s="0">
-        <v>4535440.2911066245</v>
+        <v>37.499999999999915</v>
       </c>
     </row>
     <row r="55">
@@ -1273,19 +1273,19 @@
         <v>54</v>
       </c>
       <c r="B55" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.075000000000000011</v>
       </c>
       <c r="C55" s="0">
-        <v>-0.075000000000000011</v>
+        <v>0.0625</v>
       </c>
       <c r="D55" s="0">
-        <v>4.0000000000000003e-05</v>
+        <v>7.5000000000000007e-05</v>
       </c>
       <c r="E55" s="0">
-        <v>-7.5000000000000007e-05</v>
+        <v>6.2500000000000001e-05</v>
       </c>
       <c r="F55" s="0">
-        <v>4535452.5237395177</v>
+        <v>24.99999999999994</v>
       </c>
     </row>
     <row r="56">
@@ -1293,19 +1293,19 @@
         <v>55</v>
       </c>
       <c r="B56" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.0625</v>
       </c>
       <c r="C56" s="0">
-        <v>-0.10000000000000001</v>
+        <v>0.075000000000000011</v>
       </c>
       <c r="D56" s="0">
-        <v>4.0000000000000003e-05</v>
+        <v>6.2500000000000001e-05</v>
       </c>
       <c r="E56" s="0">
-        <v>-0.0001</v>
+        <v>7.5000000000000007e-05</v>
       </c>
       <c r="F56" s="0">
-        <v>4535473.0741266916</v>
+        <v>37.499999999999929</v>
       </c>
     </row>
     <row r="57">
@@ -1313,19 +1313,19 @@
         <v>56</v>
       </c>
       <c r="B57" s="0">
-        <v>0.02</v>
+        <v>0.075000000000000011</v>
       </c>
       <c r="C57" s="0">
-        <v>-0.087500000000000008</v>
+        <v>0.012500000000000001</v>
       </c>
       <c r="D57" s="0">
-        <v>2.0000000000000002e-05</v>
+        <v>7.5000000000000007e-05</v>
       </c>
       <c r="E57" s="0">
-        <v>-8.7500000000000013e-05</v>
+        <v>1.2500000000000001e-05</v>
       </c>
       <c r="F57" s="0">
-        <v>4535502.4903339874</v>
+        <v>24.999999999999947</v>
       </c>
     </row>
     <row r="58">
@@ -1333,19 +1333,19 @@
         <v>57</v>
       </c>
       <c r="B58" s="0">
-        <v>0.017500000000000002</v>
+        <v>0.087500000000000008</v>
       </c>
       <c r="C58" s="0">
-        <v>-0.077500000000000013</v>
+        <v>0</v>
       </c>
       <c r="D58" s="0">
-        <v>1.7500000000000002e-05</v>
+        <v>8.7500000000000013e-05</v>
       </c>
       <c r="E58" s="0">
-        <v>-7.7500000000000014e-05</v>
+        <v>0</v>
       </c>
       <c r="F58" s="0">
-        <v>4535478.4977477677</v>
+        <v>12.49999999999997</v>
       </c>
     </row>
     <row r="59">
@@ -1353,19 +1353,19 @@
         <v>58</v>
       </c>
       <c r="B59" s="0">
-        <v>0.017500000000000002</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="C59" s="0">
-        <v>-0.089999999999999997</v>
+        <v>0.037500000000000013</v>
       </c>
       <c r="D59" s="0">
-        <v>1.7500000000000002e-05</v>
+        <v>5.0000000000000002e-05</v>
       </c>
       <c r="E59" s="0">
-        <v>-8.9999999999999992e-05</v>
+        <v>3.750000000000001e-05</v>
       </c>
       <c r="F59" s="0">
-        <v>4535512.599518029</v>
+        <v>49.999999999999886</v>
       </c>
     </row>
     <row r="60">
@@ -1373,19 +1373,19 @@
         <v>59</v>
       </c>
       <c r="B60" s="0">
-        <v>0.02</v>
+        <v>0.0625</v>
       </c>
       <c r="C60" s="0">
-        <v>-0.0625</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="D60" s="0">
-        <v>2.0000000000000002e-05</v>
+        <v>6.2500000000000001e-05</v>
       </c>
       <c r="E60" s="0">
-        <v>-6.2500000000000001e-05</v>
+        <v>2.5000000000000001e-05</v>
       </c>
       <c r="F60" s="0">
-        <v>4535462.4016358592</v>
+        <v>37.499999999999922</v>
       </c>
     </row>
     <row r="61">
@@ -1393,19 +1393,19 @@
         <v>60</v>
       </c>
       <c r="B61" s="0">
-        <v>0.017500000000000002</v>
+        <v>0.0625</v>
       </c>
       <c r="C61" s="0">
-        <v>-0.052499999999999998</v>
+        <v>0.012500000000000001</v>
       </c>
       <c r="D61" s="0">
-        <v>1.7500000000000002e-05</v>
+        <v>6.2500000000000001e-05</v>
       </c>
       <c r="E61" s="0">
-        <v>-5.2499999999999995e-05</v>
+        <v>1.2500000000000001e-05</v>
       </c>
       <c r="F61" s="0">
-        <v>4535460.7668246189</v>
+        <v>37.499999999999929</v>
       </c>
     </row>
     <row r="62">
@@ -1413,19 +1413,19 @@
         <v>61</v>
       </c>
       <c r="B62" s="0">
-        <v>0.017500000000000002</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="C62" s="0">
-        <v>-0.065000000000000002</v>
+        <v>0.012500000000000001</v>
       </c>
       <c r="D62" s="0">
-        <v>1.7500000000000002e-05</v>
+        <v>5.0000000000000002e-05</v>
       </c>
       <c r="E62" s="0">
-        <v>-6.5000000000000008e-05</v>
+        <v>1.2500000000000001e-05</v>
       </c>
       <c r="F62" s="0">
-        <v>4535464.7688345565</v>
+        <v>49.999999999999908</v>
       </c>
     </row>
     <row r="63">
@@ -1433,19 +1433,19 @@
         <v>62</v>
       </c>
       <c r="B63" s="0">
-        <v>0.014999999999999999</v>
+        <v>0.0625</v>
       </c>
       <c r="C63" s="0">
-        <v>-0.067500000000000004</v>
+        <v>0</v>
       </c>
       <c r="D63" s="0">
-        <v>1.4999999999999999e-05</v>
+        <v>6.2500000000000001e-05</v>
       </c>
       <c r="E63" s="0">
-        <v>-6.7500000000000001e-05</v>
+        <v>0</v>
       </c>
       <c r="F63" s="0">
-        <v>4535466.9611915071</v>
+        <v>37.499999999999929</v>
       </c>
     </row>
     <row r="64">
@@ -1453,19 +1453,19 @@
         <v>63</v>
       </c>
       <c r="B64" s="0">
-        <v>0.012500000000000001</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="C64" s="0">
-        <v>-0.057500000000000009</v>
+        <v>0.0625</v>
       </c>
       <c r="D64" s="0">
-        <v>1.2500000000000001e-05</v>
+        <v>2.5000000000000001e-05</v>
       </c>
       <c r="E64" s="0">
-        <v>-5.7500000000000009e-05</v>
+        <v>6.2500000000000001e-05</v>
       </c>
       <c r="F64" s="0">
-        <v>4535462.8912424147</v>
+        <v>74.999999999999901</v>
       </c>
     </row>
     <row r="65">
@@ -1473,19 +1473,19 @@
         <v>64</v>
       </c>
       <c r="B65" s="0">
-        <v>0.012500000000000001</v>
+        <v>0.037500000000000013</v>
       </c>
       <c r="C65" s="0">
-        <v>-0.070000000000000007</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="D65" s="0">
-        <v>1.2500000000000001e-05</v>
+        <v>3.750000000000001e-05</v>
       </c>
       <c r="E65" s="0">
-        <v>-7.0000000000000008e-05</v>
+        <v>5.0000000000000002e-05</v>
       </c>
       <c r="F65" s="0">
-        <v>4535468.9264436849</v>
+        <v>62.499999999999858</v>
       </c>
     </row>
     <row r="66">
@@ -1493,19 +1493,19 @@
         <v>65</v>
       </c>
       <c r="B66" s="0">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="C66" s="0">
-        <v>-0.037500000000000013</v>
+        <v>0.087500000000000008</v>
       </c>
       <c r="D66" s="0">
-        <v>2.0000000000000002e-05</v>
+        <v>0</v>
       </c>
       <c r="E66" s="0">
-        <v>-3.750000000000001e-05</v>
+        <v>8.7500000000000013e-05</v>
       </c>
       <c r="F66" s="0">
-        <v>4535460.931271296</v>
+        <v>100</v>
       </c>
     </row>
     <row r="67">
@@ -1513,19 +1513,19 @@
         <v>66</v>
       </c>
       <c r="B67" s="0">
-        <v>0.017500000000000002</v>
+        <v>0.012500000000000001</v>
       </c>
       <c r="C67" s="0">
-        <v>-0.0275</v>
+        <v>0.075000000000000011</v>
       </c>
       <c r="D67" s="0">
-        <v>1.7500000000000002e-05</v>
+        <v>1.2500000000000001e-05</v>
       </c>
       <c r="E67" s="0">
-        <v>-2.7500000000000001e-05</v>
+        <v>7.5000000000000007e-05</v>
       </c>
       <c r="F67" s="0">
-        <v>4535466.9862743942</v>
+        <v>87.499999999999972</v>
       </c>
     </row>
     <row r="68">
@@ -1533,19 +1533,19 @@
         <v>67</v>
       </c>
       <c r="B68" s="0">
-        <v>0.017500000000000002</v>
+        <v>0.012500000000000001</v>
       </c>
       <c r="C68" s="0">
-        <v>-0.040000000000000001</v>
+        <v>0.0625</v>
       </c>
       <c r="D68" s="0">
-        <v>1.7500000000000002e-05</v>
+        <v>1.2500000000000001e-05</v>
       </c>
       <c r="E68" s="0">
-        <v>-4.0000000000000003e-05</v>
+        <v>6.2500000000000001e-05</v>
       </c>
       <c r="F68" s="0">
-        <v>4535462.8001809176</v>
+        <v>87.499999999999957</v>
       </c>
     </row>
     <row r="69">
@@ -1553,19 +1553,19 @@
         <v>68</v>
       </c>
       <c r="B69" s="0">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="C69" s="0">
-        <v>-0.012500000000000001</v>
+        <v>0.0625</v>
       </c>
       <c r="D69" s="0">
-        <v>2.0000000000000002e-05</v>
+        <v>0</v>
       </c>
       <c r="E69" s="0">
-        <v>-1.2500000000000001e-05</v>
+        <v>6.2500000000000001e-05</v>
       </c>
       <c r="F69" s="0">
-        <v>4535461.9901509229</v>
+        <v>100</v>
       </c>
     </row>
     <row r="70">
@@ -1573,19 +1573,19 @@
         <v>69</v>
       </c>
       <c r="B70" s="0">
-        <v>0.017500000000000002</v>
+        <v>0.012500000000000001</v>
       </c>
       <c r="C70" s="0">
-        <v>-0.0025000000000000001</v>
+        <v>0.050000000000000003</v>
       </c>
       <c r="D70" s="0">
-        <v>1.7500000000000002e-05</v>
+        <v>1.2500000000000001e-05</v>
       </c>
       <c r="E70" s="0">
-        <v>-2.5000000000000002e-06</v>
+        <v>5.0000000000000002e-05</v>
       </c>
       <c r="F70" s="0">
-        <v>4535458.6319395108</v>
+        <v>87.499999999999957</v>
       </c>
     </row>
     <row r="71">
@@ -1593,19 +1593,19 @@
         <v>70</v>
       </c>
       <c r="B71" s="0">
-        <v>0.017500000000000002</v>
+        <v>0.037500000000000013</v>
       </c>
       <c r="C71" s="0">
-        <v>-0.014999999999999999</v>
+        <v>0.012500000000000001</v>
       </c>
       <c r="D71" s="0">
-        <v>1.7500000000000002e-05</v>
+        <v>3.750000000000001e-05</v>
       </c>
       <c r="E71" s="0">
-        <v>-1.4999999999999999e-05</v>
+        <v>1.2500000000000001e-05</v>
       </c>
       <c r="F71" s="0">
-        <v>4535467.0474883942</v>
+        <v>62.499999999999894</v>
       </c>
     </row>
     <row r="72">
@@ -1613,19 +1613,19 @@
         <v>71</v>
       </c>
       <c r="B72" s="0">
-        <v>0.014999999999999999</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="C72" s="0">
-        <v>-0.017500000000000002</v>
+        <v>0.012500000000000001</v>
       </c>
       <c r="D72" s="0">
-        <v>1.4999999999999999e-05</v>
+        <v>2.5000000000000001e-05</v>
       </c>
       <c r="E72" s="0">
-        <v>-1.7500000000000002e-05</v>
+        <v>1.2500000000000001e-05</v>
       </c>
       <c r="F72" s="0">
-        <v>4535472.4091142872</v>
+        <v>74.999999999999901</v>
       </c>
     </row>
     <row r="73">
@@ -1633,19 +1633,19 @@
         <v>72</v>
       </c>
       <c r="B73" s="0">
-        <v>0.012500000000000001</v>
+        <v>0.037500000000000013</v>
       </c>
       <c r="C73" s="0">
-        <v>-0.0074999999999999997</v>
+        <v>0</v>
       </c>
       <c r="D73" s="0">
-        <v>1.2500000000000001e-05</v>
+        <v>3.750000000000001e-05</v>
       </c>
       <c r="E73" s="0">
-        <v>-7.4999999999999993e-06</v>
+        <v>0</v>
       </c>
       <c r="F73" s="0">
-        <v>4535470.8493140619</v>
+        <v>62.499999999999901</v>
       </c>
     </row>
     <row r="74">
@@ -1656,16 +1656,16 @@
         <v>0.012500000000000001</v>
       </c>
       <c r="C74" s="0">
-        <v>-0.02</v>
+        <v>0.037500000000000013</v>
       </c>
       <c r="D74" s="0">
         <v>1.2500000000000001e-05</v>
       </c>
       <c r="E74" s="0">
-        <v>-2.0000000000000002e-05</v>
+        <v>3.750000000000001e-05</v>
       </c>
       <c r="F74" s="0">
-        <v>4535477.9174429728</v>
+        <v>87.499999999999943</v>
       </c>
     </row>
     <row r="75">
@@ -1673,19 +1673,19 @@
         <v>74</v>
       </c>
       <c r="B75" s="0">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C75" s="0">
-        <v>-0.047500000000000001</v>
+        <v>0.037500000000000013</v>
       </c>
       <c r="D75" s="0">
-        <v>1.0000000000000001e-05</v>
+        <v>0</v>
       </c>
       <c r="E75" s="0">
-        <v>-4.7500000000000003e-05</v>
+        <v>3.750000000000001e-05</v>
       </c>
       <c r="F75" s="0">
-        <v>4535464.8373334436</v>
+        <v>100</v>
       </c>
     </row>
     <row r="76">
@@ -1693,19 +1693,19 @@
         <v>75</v>
       </c>
       <c r="B76" s="0">
-        <v>0.0074999999999999997</v>
+        <v>0.012500000000000001</v>
       </c>
       <c r="C76" s="0">
-        <v>-0.037500000000000013</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="D76" s="0">
-        <v>7.4999999999999993e-06</v>
+        <v>1.2500000000000001e-05</v>
       </c>
       <c r="E76" s="0">
-        <v>-3.750000000000001e-05</v>
+        <v>2.5000000000000001e-05</v>
       </c>
       <c r="F76" s="0">
-        <v>4535473.3684317628</v>
+        <v>87.499999999999929</v>
       </c>
     </row>
     <row r="77">
@@ -1713,19 +1713,19 @@
         <v>76</v>
       </c>
       <c r="B77" s="0">
-        <v>0.0074999999999999997</v>
+        <v>0.012500000000000001</v>
       </c>
       <c r="C77" s="0">
-        <v>-0.050000000000000003</v>
+        <v>0.012500000000000001</v>
       </c>
       <c r="D77" s="0">
-        <v>7.4999999999999993e-06</v>
+        <v>1.2500000000000001e-05</v>
       </c>
       <c r="E77" s="0">
-        <v>-5.0000000000000002e-05</v>
+        <v>1.2500000000000001e-05</v>
       </c>
       <c r="F77" s="0">
-        <v>4535464.3213398894</v>
+        <v>87.499999999999929</v>
       </c>
     </row>
     <row r="78">
@@ -1733,19 +1733,19 @@
         <v>77</v>
       </c>
       <c r="B78" s="0">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="C78" s="0">
-        <v>-0.022499999999999999</v>
+        <v>0.012500000000000001</v>
       </c>
       <c r="D78" s="0">
-        <v>1.0000000000000001e-05</v>
+        <v>0</v>
       </c>
       <c r="E78" s="0">
-        <v>-2.2499999999999998e-05</v>
+        <v>1.2500000000000001e-05</v>
       </c>
       <c r="F78" s="0">
-        <v>4535483.2735736249</v>
+        <v>100</v>
       </c>
     </row>
     <row r="79">
@@ -1753,19 +1753,19 @@
         <v>78</v>
       </c>
       <c r="B79" s="0">
-        <v>0.0074999999999999997</v>
+        <v>0.012500000000000001</v>
       </c>
       <c r="C79" s="0">
-        <v>-0.012500000000000001</v>
+        <v>0</v>
       </c>
       <c r="D79" s="0">
-        <v>7.4999999999999993e-06</v>
+        <v>1.2500000000000001e-05</v>
       </c>
       <c r="E79" s="0">
-        <v>-1.2500000000000001e-05</v>
+        <v>0</v>
       </c>
       <c r="F79" s="0">
-        <v>4535488.5779397609</v>
+        <v>87.499999999999943</v>
       </c>
     </row>
     <row r="80">
@@ -1773,19 +1773,19 @@
         <v>79</v>
       </c>
       <c r="B80" s="0">
-        <v>0.0074999999999999997</v>
+        <v>0.037500000000000013</v>
       </c>
       <c r="C80" s="0">
-        <v>-0.025000000000000001</v>
+        <v>0.037500000000000013</v>
       </c>
       <c r="D80" s="0">
-        <v>7.4999999999999993e-06</v>
+        <v>3.750000000000001e-05</v>
       </c>
       <c r="E80" s="0">
-        <v>-2.5000000000000001e-05</v>
+        <v>3.750000000000001e-05</v>
       </c>
       <c r="F80" s="0">
-        <v>4535487.9304120801</v>
+        <v>62.499999999999879</v>
       </c>
     </row>
     <row r="81">
@@ -1793,19 +1793,19 @@
         <v>80</v>
       </c>
       <c r="B81" s="0">
-        <v>0.0050000000000000001</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="C81" s="0">
-        <v>-0.0275</v>
+        <v>0.037500000000000013</v>
       </c>
       <c r="D81" s="0">
-        <v>5.0000000000000004e-06</v>
+        <v>2.5000000000000001e-05</v>
       </c>
       <c r="E81" s="0">
-        <v>-2.7500000000000001e-05</v>
+        <v>3.750000000000001e-05</v>
       </c>
       <c r="F81" s="0">
-        <v>4535490.9134327909</v>
+        <v>74.999999999999915</v>
       </c>
     </row>
     <row r="82">
@@ -1813,19 +1813,19 @@
         <v>81</v>
       </c>
       <c r="B82" s="0">
-        <v>0.0025000000000000001</v>
+        <v>0.037500000000000013</v>
       </c>
       <c r="C82" s="0">
-        <v>-0.017500000000000002</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="D82" s="0">
-        <v>2.5000000000000002e-06</v>
+        <v>3.750000000000001e-05</v>
       </c>
       <c r="E82" s="0">
-        <v>-1.7500000000000002e-05</v>
+        <v>2.5000000000000001e-05</v>
       </c>
       <c r="F82" s="0">
-        <v>4535516.4773502415</v>
+        <v>62.499999999999879</v>
       </c>
     </row>
     <row r="83">
@@ -4041,7 +4041,7 @@
     <col min="2" max="2" width="6.36328125" customWidth="true"/>
     <col min="3" max="3" width="6.36328125" customWidth="true"/>
     <col min="4" max="4" width="6.36328125" customWidth="true"/>
-    <col min="5" max="5" width="11.453125" customWidth="true"/>
+    <col min="5" max="5" width="9.36328125" customWidth="true"/>
     <col min="6" max="6" width="15.7265625" customWidth="true"/>
     <col min="7" max="7" width="12" customWidth="true"/>
   </cols>
@@ -4077,19 +4077,19 @@
         <v>2</v>
       </c>
       <c r="C2" s="0">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="D2" s="0">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E2" s="0">
-        <v>52307692.307692528</v>
+        <v>85000000.000000239</v>
       </c>
       <c r="F2" s="0">
-        <v>-9807692.3076924682</v>
+        <v>1.1920928955078125e-07</v>
       </c>
       <c r="G2" s="0">
-        <v>53219221.179556981</v>
+        <v>85000000.000000239</v>
       </c>
     </row>
     <row r="3">
@@ -4097,22 +4097,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="0">
+        <v>26</v>
+      </c>
+      <c r="C3" s="0">
         <v>10</v>
       </c>
-      <c r="C3" s="0">
-        <v>5</v>
-      </c>
       <c r="D3" s="0">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E3" s="0">
-        <v>22884615.384615392</v>
+        <v>85000000.000000239</v>
       </c>
       <c r="F3" s="0">
-        <v>0</v>
+        <v>-5.9604644775390625e-08</v>
       </c>
       <c r="G3" s="0">
-        <v>22884615.384615392</v>
+        <v>85000000.000000239</v>
       </c>
     </row>
     <row r="4">
@@ -4120,22 +4120,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="0">
+        <v>28</v>
+      </c>
+      <c r="C4" s="0">
+        <v>27</v>
+      </c>
+      <c r="D4" s="0">
         <v>12</v>
       </c>
-      <c r="C4" s="0">
-        <v>11</v>
-      </c>
-      <c r="D4" s="0">
-        <v>7</v>
-      </c>
       <c r="E4" s="0">
-        <v>32692307.69230777</v>
+        <v>85000000.000000358</v>
       </c>
       <c r="F4" s="0">
-        <v>-8.9406967163085938e-08</v>
+        <v>1.1920928955078125e-07</v>
       </c>
       <c r="G4" s="0">
-        <v>32692307.69230777</v>
+        <v>85000000.000000358</v>
       </c>
     </row>
     <row r="5">
@@ -4143,22 +4143,22 @@
         <v>4</v>
       </c>
       <c r="B5" s="0">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="C5" s="0">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="D5" s="0">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="E5" s="0">
-        <v>22884615.384615392</v>
+        <v>85000000.000000239</v>
       </c>
       <c r="F5" s="0">
-        <v>-9807692.3076924682</v>
+        <v>1.1920928955078125e-07</v>
       </c>
       <c r="G5" s="0">
-        <v>24897719.769170538</v>
+        <v>85000000.000000239</v>
       </c>
     </row>
     <row r="6">
@@ -4166,22 +4166,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="0">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C6" s="0">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="D6" s="0">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E6" s="0">
-        <v>18798076.923076957</v>
+        <v>85000000.00000006</v>
       </c>
       <c r="F6" s="0">
-        <v>-4086538.4615384042</v>
+        <v>-1.1920928955078125e-07</v>
       </c>
       <c r="G6" s="0">
-        <v>19237138.36836319</v>
+        <v>85000000.00000006</v>
       </c>
     </row>
     <row r="7">
@@ -4189,22 +4189,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="0">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C7" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D7" s="0">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="E7" s="0">
-        <v>17163461.538461447</v>
+        <v>84999999.99999994</v>
       </c>
       <c r="F7" s="0">
-        <v>-44951923.076922804</v>
+        <v>-5.9604644775390625e-08</v>
       </c>
       <c r="G7" s="0">
-        <v>48117146.635018066</v>
+        <v>84999999.99999994</v>
       </c>
     </row>
     <row r="8">
@@ -4212,22 +4212,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="0">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C8" s="0">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D8" s="0">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="E8" s="0">
-        <v>10624999.999999881</v>
+        <v>85000000</v>
       </c>
       <c r="F8" s="0">
-        <v>-10624999.99999997</v>
+        <v>-1.1920928955078125e-07</v>
       </c>
       <c r="G8" s="0">
-        <v>15026019.100214029</v>
+        <v>85000000</v>
       </c>
     </row>
     <row r="9">
@@ -4235,22 +4235,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="0">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="C9" s="0">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="D9" s="0">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="E9" s="0">
-        <v>17163461.538461447</v>
+        <v>84999999.99999994</v>
       </c>
       <c r="F9" s="0">
-        <v>-4086538.4615384042</v>
+        <v>-1.1920928955078125e-07</v>
       </c>
       <c r="G9" s="0">
-        <v>17643248.243446503</v>
+        <v>84999999.99999994</v>
       </c>
     </row>
     <row r="10">
@@ -4258,22 +4258,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="0">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="C10" s="0">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D10" s="0">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E10" s="0">
-        <v>32692307.692307621</v>
+        <v>85000000</v>
       </c>
       <c r="F10" s="0">
-        <v>9807692.3076921999</v>
+        <v>0</v>
       </c>
       <c r="G10" s="0">
-        <v>34131771.279130548</v>
+        <v>85000000</v>
       </c>
     </row>
     <row r="11">
@@ -4281,22 +4281,22 @@
         <v>10</v>
       </c>
       <c r="B11" s="0">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C11" s="0">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D11" s="0">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E11" s="0">
-        <v>17163461.538461447</v>
+        <v>85000000</v>
       </c>
       <c r="F11" s="0">
-        <v>10624999.99999994</v>
+        <v>-5.9604644775390625e-08</v>
       </c>
       <c r="G11" s="0">
-        <v>20186010.922969505</v>
+        <v>85000000</v>
       </c>
     </row>
     <row r="12">
@@ -4304,22 +4304,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="0">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="C12" s="0">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D12" s="0">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E12" s="0">
-        <v>52307692.307692081</v>
+        <v>84999999.99999994</v>
       </c>
       <c r="F12" s="0">
-        <v>44951923.076922834</v>
+        <v>-5.9604644775390625e-08</v>
       </c>
       <c r="G12" s="0">
-        <v>68969341.470466256</v>
+        <v>84999999.99999994</v>
       </c>
     </row>
     <row r="13">
@@ -4327,22 +4327,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="0">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="C13" s="0">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="D13" s="0">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="E13" s="0">
-        <v>17163461.538461447</v>
+        <v>85000000</v>
       </c>
       <c r="F13" s="0">
-        <v>9807692.3076921999</v>
+        <v>0</v>
       </c>
       <c r="G13" s="0">
-        <v>19768035.825154964</v>
+        <v>85000000</v>
       </c>
     </row>
     <row r="14">
@@ -4350,22 +4350,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="0">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="C14" s="0">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="D14" s="0">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E14" s="0">
-        <v>18798076.923076957</v>
+        <v>85000000.00000006</v>
       </c>
       <c r="F14" s="0">
-        <v>0</v>
+        <v>-5.9604644775390625e-08</v>
       </c>
       <c r="G14" s="0">
-        <v>18798076.923076957</v>
+        <v>85000000.00000006</v>
       </c>
     </row>
     <row r="15">
@@ -4373,22 +4373,22 @@
         <v>14</v>
       </c>
       <c r="B15" s="0">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C15" s="0">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D15" s="0">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E15" s="0">
-        <v>10624999.999999911</v>
+        <v>85000000</v>
       </c>
       <c r="F15" s="0">
-        <v>4086538.4615383744</v>
+        <v>-5.9604644775390625e-08</v>
       </c>
       <c r="G15" s="0">
-        <v>11383778.880390752</v>
+        <v>85000000</v>
       </c>
     </row>
     <row r="16">
@@ -4396,22 +4396,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="0">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="C16" s="0">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D16" s="0">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="E16" s="0">
-        <v>22884615.384615332</v>
+        <v>85000000.000000119</v>
       </c>
       <c r="F16" s="0">
-        <v>-8.9406967163085938e-08</v>
+        <v>1.1920928955078125e-07</v>
       </c>
       <c r="G16" s="0">
-        <v>22884615.384615332</v>
+        <v>85000000.000000119</v>
       </c>
     </row>
     <row r="17">
@@ -4419,22 +4419,22 @@
         <v>16</v>
       </c>
       <c r="B17" s="0">
-        <v>15</v>
+        <v>31</v>
       </c>
       <c r="C17" s="0">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D17" s="0">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="E17" s="0">
-        <v>22884615.384615332</v>
+        <v>85000000.000000119</v>
       </c>
       <c r="F17" s="0">
-        <v>4086538.4615383744</v>
+        <v>-5.9604644775390625e-08</v>
       </c>
       <c r="G17" s="0">
-        <v>23246621.644862834</v>
+        <v>85000000.000000119</v>
       </c>
     </row>
     <row r="18">
@@ -4442,22 +4442,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="0">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C18" s="0">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="D18" s="0">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="E18" s="0">
-        <v>52307692.307691991</v>
+        <v>84999999.999999851</v>
       </c>
       <c r="F18" s="0">
-        <v>-9807692.3076922596</v>
+        <v>5.9604644775390625e-08</v>
       </c>
       <c r="G18" s="0">
-        <v>53219221.179556415</v>
+        <v>84999999.999999851</v>
       </c>
     </row>
     <row r="19">
@@ -4465,22 +4465,22 @@
         <v>18</v>
       </c>
       <c r="B19" s="0">
+        <v>35</v>
+      </c>
+      <c r="C19" s="0">
         <v>13</v>
       </c>
-      <c r="C19" s="0">
-        <v>5</v>
-      </c>
       <c r="D19" s="0">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E19" s="0">
-        <v>22884615.384615362</v>
+        <v>84999999.999999791</v>
       </c>
       <c r="F19" s="0">
-        <v>0</v>
+        <v>5.9604644775390625e-08</v>
       </c>
       <c r="G19" s="0">
-        <v>22884615.384615362</v>
+        <v>84999999.999999791</v>
       </c>
     </row>
     <row r="20">
@@ -4488,22 +4488,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="0">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="C20" s="0">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D20" s="0">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E20" s="0">
-        <v>32692307.692307681</v>
+        <v>84999999.999999762</v>
       </c>
       <c r="F20" s="0">
-        <v>5.9604644775390625e-08</v>
+        <v>0</v>
       </c>
       <c r="G20" s="0">
-        <v>32692307.692307681</v>
+        <v>84999999.999999762</v>
       </c>
     </row>
     <row r="21">
@@ -4511,22 +4511,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="0">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="C21" s="0">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D21" s="0">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="E21" s="0">
-        <v>22884615.384615362</v>
+        <v>84999999.999999791</v>
       </c>
       <c r="F21" s="0">
-        <v>-9807692.3076922596</v>
+        <v>5.9604644775390625e-08</v>
       </c>
       <c r="G21" s="0">
-        <v>24897719.76917043</v>
+        <v>84999999.999999791</v>
       </c>
     </row>
     <row r="22">
@@ -4534,22 +4534,22 @@
         <v>21</v>
       </c>
       <c r="B22" s="0">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C22" s="0">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="D22" s="0">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E22" s="0">
-        <v>18798076.923077017</v>
+        <v>84999999.999999821</v>
       </c>
       <c r="F22" s="0">
-        <v>-4086538.461538434</v>
+        <v>4.4703483581542969e-08</v>
       </c>
       <c r="G22" s="0">
-        <v>19237138.368363254</v>
+        <v>84999999.999999821</v>
       </c>
     </row>
     <row r="23">
@@ -4557,22 +4557,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="0">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="C23" s="0">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23" s="0">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="E23" s="0">
-        <v>17163461.538461685</v>
+        <v>84999999.999999836</v>
       </c>
       <c r="F23" s="0">
-        <v>-44951923.076923311</v>
+        <v>0</v>
       </c>
       <c r="G23" s="0">
-        <v>48117146.635018624</v>
+        <v>84999999.999999836</v>
       </c>
     </row>
     <row r="24">
@@ -4580,22 +4580,22 @@
         <v>23</v>
       </c>
       <c r="B24" s="0">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C24" s="0">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D24" s="0">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="E24" s="0">
-        <v>10625000</v>
+        <v>84999999.999999791</v>
       </c>
       <c r="F24" s="0">
-        <v>-10625000.000000119</v>
+        <v>0</v>
       </c>
       <c r="G24" s="0">
-        <v>15026019.100214219</v>
+        <v>84999999.999999791</v>
       </c>
     </row>
     <row r="25">
@@ -4603,22 +4603,22 @@
         <v>24</v>
       </c>
       <c r="B25" s="0">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="C25" s="0">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="D25" s="0">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E25" s="0">
-        <v>17163461.538461685</v>
+        <v>84999999.999999836</v>
       </c>
       <c r="F25" s="0">
-        <v>-4086538.461538434</v>
+        <v>4.4703483581542969e-08</v>
       </c>
       <c r="G25" s="0">
-        <v>17643248.243446741</v>
+        <v>84999999.999999836</v>
       </c>
     </row>
     <row r="26">
@@ -4626,22 +4626,22 @@
         <v>25</v>
       </c>
       <c r="B26" s="0">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="C26" s="0">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D26" s="0">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="E26" s="0">
-        <v>32692307.69230774</v>
+        <v>84999999.999999777</v>
       </c>
       <c r="F26" s="0">
-        <v>9807692.3076924086</v>
+        <v>-2.9802322387695313e-08</v>
       </c>
       <c r="G26" s="0">
-        <v>34131771.27913072</v>
+        <v>84999999.999999777</v>
       </c>
     </row>
     <row r="27">
@@ -4649,22 +4649,22 @@
         <v>26</v>
       </c>
       <c r="B27" s="0">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C27" s="0">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D27" s="0">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="E27" s="0">
-        <v>17163461.538461626</v>
+        <v>84999999.999999747</v>
       </c>
       <c r="F27" s="0">
-        <v>10625000</v>
+        <v>0</v>
       </c>
       <c r="G27" s="0">
-        <v>20186010.922969688</v>
+        <v>84999999.999999747</v>
       </c>
     </row>
     <row r="28">
@@ -4672,22 +4672,22 @@
         <v>27</v>
       </c>
       <c r="B28" s="0">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="C28" s="0">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D28" s="0">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="E28" s="0">
-        <v>52307692.307692587</v>
+        <v>84999999.999999762</v>
       </c>
       <c r="F28" s="0">
-        <v>44951923.07692337</v>
+        <v>0</v>
       </c>
       <c r="G28" s="0">
-        <v>68969341.470466986</v>
+        <v>84999999.999999762</v>
       </c>
     </row>
     <row r="29">
@@ -4695,22 +4695,22 @@
         <v>28</v>
       </c>
       <c r="B29" s="0">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="C29" s="0">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="D29" s="0">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="E29" s="0">
-        <v>17163461.538461626</v>
+        <v>84999999.999999747</v>
       </c>
       <c r="F29" s="0">
-        <v>9807692.3076924086</v>
+        <v>-1.4901161193847656e-08</v>
       </c>
       <c r="G29" s="0">
-        <v>19768035.825155225</v>
+        <v>84999999.999999747</v>
       </c>
     </row>
     <row r="30">
@@ -4718,22 +4718,22 @@
         <v>29</v>
       </c>
       <c r="B30" s="0">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C30" s="0">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="D30" s="0">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E30" s="0">
-        <v>18798076.923077017</v>
+        <v>84999999.999999806</v>
       </c>
       <c r="F30" s="0">
-        <v>0</v>
+        <v>5.9604644775390625e-08</v>
       </c>
       <c r="G30" s="0">
-        <v>18798076.923077017</v>
+        <v>84999999.999999806</v>
       </c>
     </row>
     <row r="31">
@@ -4741,22 +4741,22 @@
         <v>30</v>
       </c>
       <c r="B31" s="0">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C31" s="0">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D31" s="0">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E31" s="0">
-        <v>10625000</v>
+        <v>84999999.999999791</v>
       </c>
       <c r="F31" s="0">
-        <v>4086538.4615383744</v>
+        <v>4.4703483581542969e-08</v>
       </c>
       <c r="G31" s="0">
-        <v>11383778.880390836</v>
+        <v>84999999.999999791</v>
       </c>
     </row>
     <row r="32">
@@ -4764,22 +4764,22 @@
         <v>31</v>
       </c>
       <c r="B32" s="0">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="C32" s="0">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D32" s="0">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="E32" s="0">
-        <v>22884615.384615392</v>
+        <v>84999999.999999791</v>
       </c>
       <c r="F32" s="0">
-        <v>5.9604644775390625e-08</v>
+        <v>0</v>
       </c>
       <c r="G32" s="0">
-        <v>22884615.384615392</v>
+        <v>84999999.999999791</v>
       </c>
     </row>
     <row r="33">
@@ -4787,22 +4787,22 @@
         <v>32</v>
       </c>
       <c r="B33" s="0">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C33" s="0">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="D33" s="0">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="E33" s="0">
-        <v>22884615.384615392</v>
+        <v>84999999.999999791</v>
       </c>
       <c r="F33" s="0">
-        <v>4086538.4615383744</v>
+        <v>4.4703483581542969e-08</v>
       </c>
       <c r="G33" s="0">
-        <v>23246621.64486289</v>
+        <v>84999999.999999791</v>
       </c>
     </row>
     <row r="34">
@@ -4810,22 +4810,22 @@
         <v>33</v>
       </c>
       <c r="B34" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C34" s="0">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="D34" s="0">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="E34" s="0">
-        <v>-8274444.625</v>
+        <v>84999999.999999851</v>
       </c>
       <c r="F34" s="0">
-        <v>-9269336.1953125</v>
+        <v>2.9802322387695313e-08</v>
       </c>
       <c r="G34" s="0">
-        <v>12425257.637325747</v>
+        <v>84999999.999999851</v>
       </c>
     </row>
     <row r="35">
@@ -4833,22 +4833,22 @@
         <v>34</v>
       </c>
       <c r="B35" s="0">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="C35" s="0">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D35" s="0">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="E35" s="0">
-        <v>56783564.75</v>
+        <v>84999999.999999911</v>
       </c>
       <c r="F35" s="0">
-        <v>-58318444.51953125</v>
+        <v>-5.9604644775390625e-08</v>
       </c>
       <c r="G35" s="0">
-        <v>81396647.332031354</v>
+        <v>84999999.999999911</v>
       </c>
     </row>
     <row r="36">
@@ -4856,22 +4856,22 @@
         <v>35</v>
       </c>
       <c r="B36" s="0">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="C36" s="0">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="D36" s="0">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E36" s="0">
-        <v>11493103.03125</v>
+        <v>84999999.999999851</v>
       </c>
       <c r="F36" s="0">
-        <v>-61520224.73828125</v>
+        <v>0</v>
       </c>
       <c r="G36" s="0">
-        <v>62584578.524869531</v>
+        <v>84999999.999999851</v>
       </c>
     </row>
     <row r="37">
@@ -4879,22 +4879,22 @@
         <v>36</v>
       </c>
       <c r="B37" s="0">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="C37" s="0">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="D37" s="0">
-        <v>76</v>
+        <v>46</v>
       </c>
       <c r="E37" s="0">
-        <v>43976443.890625</v>
+        <v>84999999.999999911</v>
       </c>
       <c r="F37" s="0">
-        <v>-61520224.73828125</v>
+        <v>2.9802322387695313e-08</v>
       </c>
       <c r="G37" s="0">
-        <v>75621859.730595902</v>
+        <v>84999999.999999911</v>
       </c>
     </row>
     <row r="38">
@@ -4902,22 +4902,22 @@
         <v>37</v>
       </c>
       <c r="B38" s="0">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C38" s="0">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="D38" s="0">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="E38" s="0">
-        <v>225380496.1875</v>
+        <v>84999999.999999836</v>
       </c>
       <c r="F38" s="0">
-        <v>-67047988.7109375</v>
+        <v>-1.4901161193847656e-08</v>
       </c>
       <c r="G38" s="0">
-        <v>235142086.51771742</v>
+        <v>84999999.999999836</v>
       </c>
     </row>
     <row r="39">
@@ -4925,22 +4925,22 @@
         <v>38</v>
       </c>
       <c r="B39" s="0">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C39" s="0">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D39" s="0">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="E39" s="0">
-        <v>301486847.78125</v>
+        <v>84999999.999999821</v>
       </c>
       <c r="F39" s="0">
-        <v>30284599.78515625</v>
+        <v>0</v>
       </c>
       <c r="G39" s="0">
-        <v>303004086.39030218</v>
+        <v>84999999.999999821</v>
       </c>
     </row>
     <row r="40">
@@ -4948,22 +4948,22 @@
         <v>39</v>
       </c>
       <c r="B40" s="0">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="C40" s="0">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="D40" s="0">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="E40" s="0">
-        <v>419744077.75</v>
+        <v>84999999.999999836</v>
       </c>
       <c r="F40" s="0">
-        <v>-4403188.23046875</v>
+        <v>0</v>
       </c>
       <c r="G40" s="0">
-        <v>419767172.21906597</v>
+        <v>84999999.999999836</v>
       </c>
     </row>
     <row r="41">
@@ -4971,22 +4971,22 @@
         <v>40</v>
       </c>
       <c r="B41" s="0">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="C41" s="0">
-        <v>78</v>
+        <v>48</v>
       </c>
       <c r="D41" s="0">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="E41" s="0">
-        <v>162735695.703125</v>
+        <v>84999999.999999821</v>
       </c>
       <c r="F41" s="0">
-        <v>-4403188.23046875</v>
+        <v>-1.4901161193847656e-08</v>
       </c>
       <c r="G41" s="0">
-        <v>162795253.99277779</v>
+        <v>84999999.999999821</v>
       </c>
     </row>
     <row r="42">
@@ -4994,22 +4994,22 @@
         <v>41</v>
       </c>
       <c r="B42" s="0">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="C42" s="0">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D42" s="0">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="E42" s="0">
-        <v>115979891.375</v>
+        <v>84999999.999999896</v>
       </c>
       <c r="F42" s="0">
-        <v>-129311431.32421875</v>
+        <v>2.9802322387695313e-08</v>
       </c>
       <c r="G42" s="0">
-        <v>173703141.80945301</v>
+        <v>84999999.999999896</v>
       </c>
     </row>
     <row r="43">
@@ -5017,22 +5017,22 @@
         <v>42</v>
       </c>
       <c r="B43" s="0">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="C43" s="0">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D43" s="0">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="E43" s="0">
-        <v>600425892.1875</v>
+        <v>84999999.999999851</v>
       </c>
       <c r="F43" s="0">
-        <v>-67186825.29296875</v>
+        <v>0</v>
       </c>
       <c r="G43" s="0">
-        <v>604173254.54053605</v>
+        <v>84999999.999999851</v>
       </c>
     </row>
     <row r="44">
@@ -5040,22 +5040,22 @@
         <v>43</v>
       </c>
       <c r="B44" s="0">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="C44" s="0">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="D44" s="0">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E44" s="0">
-        <v>879575190.28125</v>
+        <v>84999999.999999836</v>
       </c>
       <c r="F44" s="0">
-        <v>-176500946.65625</v>
+        <v>0</v>
       </c>
       <c r="G44" s="0">
-        <v>897109301.88514352</v>
+        <v>84999999.999999836</v>
       </c>
     </row>
     <row r="45">
@@ -5063,22 +5063,22 @@
         <v>44</v>
       </c>
       <c r="B45" s="0">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="C45" s="0">
-        <v>81</v>
+        <v>51</v>
       </c>
       <c r="D45" s="0">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="E45" s="0">
-        <v>163169406.703125</v>
+        <v>84999999.999999866</v>
       </c>
       <c r="F45" s="0">
-        <v>-176500946.65625</v>
+        <v>2.9802322387695313e-08</v>
       </c>
       <c r="G45" s="0">
-        <v>240368133.192406</v>
+        <v>84999999.999999866</v>
       </c>
     </row>
     <row r="46">
@@ -5086,22 +5086,22 @@
         <v>45</v>
       </c>
       <c r="B46" s="0">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="C46" s="0">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="D46" s="0">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="E46" s="0">
-        <v>97486586.40625</v>
+        <v>84999999.999999836</v>
       </c>
       <c r="F46" s="0">
-        <v>-99021466.16015625</v>
+        <v>-5.9604644775390625e-08</v>
       </c>
       <c r="G46" s="0">
-        <v>138956415.0719578</v>
+        <v>84999999.999999836</v>
       </c>
     </row>
     <row r="47">
@@ -5109,22 +5109,22 @@
         <v>46</v>
       </c>
       <c r="B47" s="0">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="C47" s="0">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D47" s="0">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="E47" s="0">
-        <v>168609529.484375</v>
+        <v>84999999.999999836</v>
       </c>
       <c r="F47" s="0">
-        <v>-67186825.29296875</v>
+        <v>-2.9802322387695313e-08</v>
       </c>
       <c r="G47" s="0">
-        <v>181502735.31241953</v>
+        <v>84999999.999999836</v>
       </c>
     </row>
     <row r="48">
@@ -5132,22 +5132,22 @@
         <v>47</v>
       </c>
       <c r="B48" s="0">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="C48" s="0">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D48" s="0">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="E48" s="0">
-        <v>79284309.671875</v>
+        <v>84999999.999999851</v>
       </c>
       <c r="F48" s="0">
-        <v>-129311431.32421875</v>
+        <v>0</v>
       </c>
       <c r="G48" s="0">
-        <v>151682062.32532543</v>
+        <v>84999999.999999851</v>
       </c>
     </row>
     <row r="49">
@@ -5155,22 +5155,22 @@
         <v>48</v>
       </c>
       <c r="B49" s="0">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="C49" s="0">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="D49" s="0">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="E49" s="0">
-        <v>200444170.32421875</v>
+        <v>84999999.999999866</v>
       </c>
       <c r="F49" s="0">
-        <v>-99021466.16015625</v>
+        <v>-2.9802322387695313e-08</v>
       </c>
       <c r="G49" s="0">
-        <v>223569041.18744031</v>
+        <v>84999999.999999866</v>
       </c>
     </row>
     <row r="50">
@@ -5178,22 +5178,22 @@
         <v>49</v>
       </c>
       <c r="B50" s="0">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="C50" s="0">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="D50" s="0">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E50" s="0">
-        <v>67065781.8125</v>
+        <v>84999999.999999851</v>
       </c>
       <c r="F50" s="0">
-        <v>-13826822.83203125</v>
+        <v>-5.9604644775390625e-08</v>
       </c>
       <c r="G50" s="0">
-        <v>68476274.137472153</v>
+        <v>84999999.999999851</v>
       </c>
     </row>
     <row r="51">
@@ -5201,22 +5201,22 @@
         <v>50</v>
       </c>
       <c r="B51" s="0">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C51" s="0">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="D51" s="0">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="E51" s="0">
-        <v>84092124.125</v>
+        <v>84999999.999999791</v>
       </c>
       <c r="F51" s="0">
-        <v>-39659506.42578125</v>
+        <v>-1.1920928955078125e-07</v>
       </c>
       <c r="G51" s="0">
-        <v>92975060.041878924</v>
+        <v>84999999.999999791</v>
       </c>
     </row>
     <row r="52">
@@ -5224,22 +5224,22 @@
         <v>51</v>
       </c>
       <c r="B52" s="0">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="C52" s="0">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="D52" s="0">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E52" s="0">
-        <v>56098744.96875</v>
+        <v>84999999.999999821</v>
       </c>
       <c r="F52" s="0">
-        <v>-14366996.7265625</v>
+        <v>-5.9604644775390625e-08</v>
       </c>
       <c r="G52" s="0">
-        <v>57909237.449736036</v>
+        <v>84999999.999999821</v>
       </c>
     </row>
     <row r="53">
@@ -5247,22 +5247,22 @@
         <v>52</v>
       </c>
       <c r="B53" s="0">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C53" s="0">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="D53" s="0">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="E53" s="0">
-        <v>58259440.56640625</v>
+        <v>84999999.999999791</v>
       </c>
       <c r="F53" s="0">
-        <v>-13826822.83203125</v>
+        <v>-1.1920928955078125e-07</v>
       </c>
       <c r="G53" s="0">
-        <v>59877737.471776627</v>
+        <v>84999999.999999791</v>
       </c>
     </row>
     <row r="54">
@@ -5270,22 +5270,22 @@
         <v>53</v>
       </c>
       <c r="B54" s="0">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C54" s="0">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="D54" s="0">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="E54" s="0">
-        <v>115149533.5625</v>
+        <v>84999999.999999762</v>
       </c>
       <c r="F54" s="0">
-        <v>-39026806.625</v>
+        <v>-5.9604644775390625e-08</v>
       </c>
       <c r="G54" s="0">
-        <v>121583332.38979124</v>
+        <v>84999999.999999762</v>
       </c>
     </row>
     <row r="55">
@@ -5293,22 +5293,22 @@
         <v>54</v>
       </c>
       <c r="B55" s="0">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="C55" s="0">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="D55" s="0">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="E55" s="0">
-        <v>151823842.375</v>
+        <v>84999999.999999762</v>
       </c>
       <c r="F55" s="0">
-        <v>30284599.78515625</v>
+        <v>-5.9604644775390625e-08</v>
       </c>
       <c r="G55" s="0">
-        <v>154814844.56490576</v>
+        <v>84999999.999999762</v>
       </c>
     </row>
     <row r="56">
@@ -5316,22 +5316,22 @@
         <v>55</v>
       </c>
       <c r="B56" s="0">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="C56" s="0">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="D56" s="0">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="E56" s="0">
-        <v>109050520.453125</v>
+        <v>84999999.999999791</v>
       </c>
       <c r="F56" s="0">
-        <v>-67047988.7109375</v>
+        <v>-5.9604644775390625e-08</v>
       </c>
       <c r="G56" s="0">
-        <v>128013471.17112103</v>
+        <v>84999999.999999791</v>
       </c>
     </row>
     <row r="57">
@@ -5339,22 +5339,22 @@
         <v>56</v>
       </c>
       <c r="B57" s="0">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="C57" s="0">
-        <v>77</v>
+        <v>47</v>
       </c>
       <c r="D57" s="0">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="E57" s="0">
-        <v>221135248.7890625</v>
+        <v>84999999.999999791</v>
       </c>
       <c r="F57" s="0">
-        <v>-39026806.625</v>
+        <v>-5.9604644775390625e-08</v>
       </c>
       <c r="G57" s="0">
-        <v>224552643.92196703</v>
+        <v>84999999.999999791</v>
       </c>
     </row>
     <row r="58">
@@ -5362,22 +5362,22 @@
         <v>57</v>
       </c>
       <c r="B58" s="0">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C58" s="0">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="D58" s="0">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="E58" s="0">
-        <v>43403485.8125</v>
+        <v>84999999.999999791</v>
       </c>
       <c r="F58" s="0">
-        <v>-12905029</v>
+        <v>-1.1920928955078125e-07</v>
       </c>
       <c r="G58" s="0">
-        <v>45281368.731153987</v>
+        <v>84999999.999999791</v>
       </c>
     </row>
     <row r="59">
@@ -5385,22 +5385,22 @@
         <v>58</v>
       </c>
       <c r="B59" s="0">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="C59" s="0">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D59" s="0">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="E59" s="0">
-        <v>59960394.484375</v>
+        <v>84999999.999999821</v>
       </c>
       <c r="F59" s="0">
-        <v>-58318444.51953125</v>
+        <v>-1.4901161193847656e-07</v>
       </c>
       <c r="G59" s="0">
-        <v>83643827.494319692</v>
+        <v>84999999.999999821</v>
       </c>
     </row>
     <row r="60">
@@ -5408,22 +5408,22 @@
         <v>59</v>
       </c>
       <c r="B60" s="0">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="C60" s="0">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="D60" s="0">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="E60" s="0">
-        <v>29089750.1875</v>
+        <v>84999999.999999732</v>
       </c>
       <c r="F60" s="0">
-        <v>-9269336.1953125</v>
+        <v>-5.9604644775390625e-08</v>
       </c>
       <c r="G60" s="0">
-        <v>30530872.235704087</v>
+        <v>84999999.999999732</v>
       </c>
     </row>
     <row r="61">
@@ -5431,22 +5431,22 @@
         <v>60</v>
       </c>
       <c r="B61" s="0">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="C61" s="0">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="D61" s="0">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="E61" s="0">
-        <v>14546978.9765625</v>
+        <v>84999999.999999762</v>
       </c>
       <c r="F61" s="0">
-        <v>-12905029</v>
+        <v>-1.4901161193847656e-07</v>
       </c>
       <c r="G61" s="0">
-        <v>19446191.679488104</v>
+        <v>84999999.999999762</v>
       </c>
     </row>
     <row r="62">
@@ -5454,22 +5454,22 @@
         <v>61</v>
       </c>
       <c r="B62" s="0">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="C62" s="0">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="D62" s="0">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="E62" s="0">
-        <v>115782233.37890625</v>
+        <v>84999999.999999791</v>
       </c>
       <c r="F62" s="0">
-        <v>-39659506.42578125</v>
+        <v>-5.9604644775390625e-08</v>
       </c>
       <c r="G62" s="0">
-        <v>122386281.97696054</v>
+        <v>84999999.999999791</v>
       </c>
     </row>
     <row r="63">
@@ -5477,22 +5477,22 @@
         <v>62</v>
       </c>
       <c r="B63" s="0">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="C63" s="0">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="D63" s="0">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="E63" s="0">
-        <v>92248859.88671875</v>
+        <v>84999999.999999821</v>
       </c>
       <c r="F63" s="0">
-        <v>-50246328.16796875</v>
+        <v>-5.9604644775390625e-08</v>
       </c>
       <c r="G63" s="0">
-        <v>105045445.61646962</v>
+        <v>84999999.999999821</v>
       </c>
     </row>
     <row r="64">
@@ -5500,22 +5500,22 @@
         <v>63</v>
       </c>
       <c r="B64" s="0">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="C64" s="0">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="D64" s="0">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="E64" s="0">
-        <v>37555614.94921875</v>
+        <v>84999999.999999791</v>
       </c>
       <c r="F64" s="0">
-        <v>-14366996.7265625</v>
+        <v>-8.9406967163085938e-08</v>
       </c>
       <c r="G64" s="0">
-        <v>40209884.470799469</v>
+        <v>84999999.999999791</v>
       </c>
     </row>
     <row r="65">
@@ -5523,22 +5523,22 @@
         <v>64</v>
       </c>
       <c r="B65" s="0">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="C65" s="0">
-        <v>85</v>
+        <v>55</v>
       </c>
       <c r="D65" s="0">
-        <v>83</v>
+        <v>53</v>
       </c>
       <c r="E65" s="0">
-        <v>73434946.3125</v>
+        <v>84999999.999999791</v>
       </c>
       <c r="F65" s="0">
-        <v>-50246328.16796875</v>
+        <v>-8.9406967163085938e-08</v>
       </c>
       <c r="G65" s="0">
-        <v>88979687.762336895</v>
+        <v>84999999.999999791</v>
       </c>
     </row>
     <row r="66">
@@ -5546,22 +5546,22 @@
         <v>65</v>
       </c>
       <c r="B66" s="0">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C66" s="0">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="D66" s="0">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="E66" s="0">
-        <v>187717396</v>
+        <v>84999999.999999851</v>
       </c>
       <c r="F66" s="0">
-        <v>-22510413.16796875</v>
+        <v>1.4901161193847656e-08</v>
       </c>
       <c r="G66" s="0">
-        <v>189062263.45311082</v>
+        <v>84999999.999999851</v>
       </c>
     </row>
     <row r="67">
@@ -5569,22 +5569,22 @@
         <v>66</v>
       </c>
       <c r="B67" s="0">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="C67" s="0">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="D67" s="0">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="E67" s="0">
-        <v>144255637.69140625</v>
+        <v>84999999.999999821</v>
       </c>
       <c r="F67" s="0">
-        <v>-7748940.6328125</v>
+        <v>5.9604644775390625e-08</v>
       </c>
       <c r="G67" s="0">
-        <v>144463611.63519731</v>
+        <v>84999999.999999821</v>
       </c>
     </row>
     <row r="68">
@@ -5592,22 +5592,22 @@
         <v>67</v>
       </c>
       <c r="B68" s="0">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="C68" s="0">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="D68" s="0">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E68" s="0">
-        <v>154817249.578125</v>
+        <v>84999999.999999821</v>
       </c>
       <c r="F68" s="0">
-        <v>-5368771.99609375</v>
+        <v>2.9802322387695313e-08</v>
       </c>
       <c r="G68" s="0">
-        <v>154910311.08251473</v>
+        <v>84999999.999999821</v>
       </c>
     </row>
     <row r="69">
@@ -5615,22 +5615,22 @@
         <v>68</v>
       </c>
       <c r="B69" s="0">
-        <v>86</v>
+        <v>38</v>
       </c>
       <c r="C69" s="0">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="D69" s="0">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="E69" s="0">
-        <v>144255637.69140625</v>
+        <v>84999999.999999821</v>
       </c>
       <c r="F69" s="0">
-        <v>-13818061.5078125</v>
+        <v>1.4901161193847656e-08</v>
       </c>
       <c r="G69" s="0">
-        <v>144915933.66358289</v>
+        <v>84999999.999999821</v>
       </c>
     </row>
     <row r="70">
@@ -5638,22 +5638,22 @@
         <v>69</v>
       </c>
       <c r="B70" s="0">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C70" s="0">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="D70" s="0">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="E70" s="0">
-        <v>136287142.2890625</v>
+        <v>84999999.999999821</v>
       </c>
       <c r="F70" s="0">
-        <v>-2645364.0078125</v>
+        <v>8.9406967163085938e-08</v>
       </c>
       <c r="G70" s="0">
-        <v>136312813.42578545</v>
+        <v>84999999.999999821</v>
       </c>
     </row>
     <row r="71">
@@ -5661,22 +5661,22 @@
         <v>70</v>
       </c>
       <c r="B71" s="0">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="C71" s="0">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D71" s="0">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="E71" s="0">
-        <v>129139815.8046875</v>
+        <v>84999999.999999851</v>
       </c>
       <c r="F71" s="0">
-        <v>-3808311.02734375</v>
+        <v>5.9604644775390625e-08</v>
       </c>
       <c r="G71" s="0">
-        <v>129195956.82121637</v>
+        <v>84999999.999999851</v>
       </c>
     </row>
     <row r="72">
@@ -5684,22 +5684,22 @@
         <v>71</v>
       </c>
       <c r="B72" s="0">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="C72" s="0">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="D72" s="0">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E72" s="0">
-        <v>135469957.98828125</v>
+        <v>84999999.999999881</v>
       </c>
       <c r="F72" s="0">
-        <v>3848215.0390625</v>
+        <v>5.9604644775390625e-08</v>
       </c>
       <c r="G72" s="0">
-        <v>135524603.95195243</v>
+        <v>84999999.999999881</v>
       </c>
     </row>
     <row r="73">
@@ -5707,22 +5707,22 @@
         <v>72</v>
       </c>
       <c r="B73" s="0">
-        <v>89</v>
+        <v>35</v>
       </c>
       <c r="C73" s="0">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="D73" s="0">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="E73" s="0">
-        <v>129139815.8046875</v>
+        <v>84999999.999999851</v>
       </c>
       <c r="F73" s="0">
-        <v>-1215898.7109375</v>
+        <v>8.9406967163085938e-08</v>
       </c>
       <c r="G73" s="0">
-        <v>129145539.7439024</v>
+        <v>84999999.999999851</v>
       </c>
     </row>
     <row r="74">
@@ -5730,22 +5730,22 @@
         <v>73</v>
       </c>
       <c r="B74" s="0">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="C74" s="0">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="D74" s="0">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="E74" s="0">
-        <v>147509642.55859375</v>
+        <v>84999999.999999821</v>
       </c>
       <c r="F74" s="0">
-        <v>283027.61328125</v>
+        <v>0</v>
       </c>
       <c r="G74" s="0">
-        <v>147509914.08171171</v>
+        <v>84999999.999999821</v>
       </c>
     </row>
     <row r="75">
@@ -5753,22 +5753,22 @@
         <v>74</v>
       </c>
       <c r="B75" s="0">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="C75" s="0">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D75" s="0">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="E75" s="0">
-        <v>144221018.83984375</v>
+        <v>84999999.999999821</v>
       </c>
       <c r="F75" s="0">
-        <v>8041266.05859375</v>
+        <v>0</v>
       </c>
       <c r="G75" s="0">
-        <v>144445021.49616531</v>
+        <v>84999999.999999821</v>
       </c>
     </row>
     <row r="76">
@@ -5776,22 +5776,22 @@
         <v>75</v>
       </c>
       <c r="B76" s="0">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="C76" s="0">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="D76" s="0">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E76" s="0">
-        <v>149749529.1015625</v>
+        <v>84999999.999999821</v>
       </c>
       <c r="F76" s="0">
-        <v>5363560.57421875</v>
+        <v>0</v>
       </c>
       <c r="G76" s="0">
-        <v>149845551.31258661</v>
+        <v>84999999.999999821</v>
       </c>
     </row>
     <row r="77">
@@ -5799,22 +5799,22 @@
         <v>76</v>
       </c>
       <c r="B77" s="0">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="C77" s="0">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="D77" s="0">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="E77" s="0">
-        <v>144221018.83984375</v>
+        <v>84999999.999999821</v>
       </c>
       <c r="F77" s="0">
-        <v>940752.3515625</v>
+        <v>0</v>
       </c>
       <c r="G77" s="0">
-        <v>144224087.06658378</v>
+        <v>84999999.999999821</v>
       </c>
     </row>
     <row r="78">
@@ -5822,22 +5822,22 @@
         <v>77</v>
       </c>
       <c r="B78" s="0">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C78" s="0">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="D78" s="0">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="E78" s="0">
-        <v>136287142.2890625</v>
+        <v>84999999.999999851</v>
       </c>
       <c r="F78" s="0">
-        <v>-6155241.55078125</v>
+        <v>5.9604644775390625e-08</v>
       </c>
       <c r="G78" s="0">
-        <v>136426068.44686112</v>
+        <v>84999999.999999851</v>
       </c>
     </row>
     <row r="79">
@@ -5845,22 +5845,22 @@
         <v>78</v>
       </c>
       <c r="B79" s="0">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="C79" s="0">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="D79" s="0">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="E79" s="0">
-        <v>135469957.98828125</v>
+        <v>84999999.999999881</v>
       </c>
       <c r="F79" s="0">
-        <v>1040417.375</v>
+        <v>5.9604644775390625e-08</v>
       </c>
       <c r="G79" s="0">
-        <v>135473953.16318518</v>
+        <v>84999999.999999881</v>
       </c>
     </row>
     <row r="80">
@@ -5868,22 +5868,22 @@
         <v>79</v>
       </c>
       <c r="B80" s="0">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="C80" s="0">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="D80" s="0">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E80" s="0">
-        <v>143319364.35546875</v>
+        <v>84999999.999999851</v>
       </c>
       <c r="F80" s="0">
-        <v>-3069194.9453125</v>
+        <v>2.9802322387695313e-08</v>
       </c>
       <c r="G80" s="0">
-        <v>143352224.10854998</v>
+        <v>84999999.999999851</v>
       </c>
     </row>
     <row r="81">
@@ -5891,22 +5891,22 @@
         <v>80</v>
       </c>
       <c r="B81" s="0">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="C81" s="0">
-        <v>92</v>
+        <v>60</v>
       </c>
       <c r="D81" s="0">
-        <v>87</v>
+        <v>56</v>
       </c>
       <c r="E81" s="0">
-        <v>143319364.35546875</v>
+        <v>84999999.999999851</v>
       </c>
       <c r="F81" s="0">
-        <v>-529463.8974609375</v>
+        <v>5.9604644775390625e-08</v>
       </c>
       <c r="G81" s="0">
-        <v>143320342.34983644</v>
+        <v>84999999.999999851</v>
       </c>
     </row>
     <row r="82">
@@ -5914,22 +5914,22 @@
         <v>81</v>
       </c>
       <c r="B82" s="0">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C82" s="0">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="D82" s="0">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="E82" s="0">
-        <v>119350177.23046875</v>
+        <v>84999999.99999994</v>
       </c>
       <c r="F82" s="0">
-        <v>-15765845.30078125</v>
+        <v>-5.9604644775390625e-08</v>
       </c>
       <c r="G82" s="0">
-        <v>120386987.18296953</v>
+        <v>84999999.99999994</v>
       </c>
     </row>
     <row r="83">
@@ -5937,22 +5937,22 @@
         <v>82</v>
       </c>
       <c r="B83" s="0">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="C83" s="0">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="D83" s="0">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="E83" s="0">
-        <v>109315617.94140625</v>
+        <v>85000000.000000119</v>
       </c>
       <c r="F83" s="0">
-        <v>-47422623.40625</v>
+        <v>-1.1920928955078125e-07</v>
       </c>
       <c r="G83" s="0">
-        <v>119158757.7001477</v>
+        <v>85000000.000000119</v>
       </c>
     </row>
     <row r="84">
@@ -5960,22 +5960,22 @@
         <v>83</v>
       </c>
       <c r="B84" s="0">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="C84" s="0">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="D84" s="0">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E84" s="0">
-        <v>102310862.375</v>
+        <v>85000000.000000298</v>
       </c>
       <c r="F84" s="0">
-        <v>-19362737.89453125</v>
+        <v>5.9604644775390625e-08</v>
       </c>
       <c r="G84" s="0">
-        <v>104126981.03127982</v>
+        <v>85000000.000000298</v>
       </c>
     </row>
     <row r="85">
@@ -5983,22 +5983,22 @@
         <v>84</v>
       </c>
       <c r="B85" s="0">
-        <v>95</v>
+        <v>29</v>
       </c>
       <c r="C85" s="0">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="D85" s="0">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="E85" s="0">
-        <v>109315617.94140625</v>
+        <v>85000000.00000006</v>
       </c>
       <c r="F85" s="0">
-        <v>-13758933.44140625</v>
+        <v>-5.9604644775390625e-08</v>
       </c>
       <c r="G85" s="0">
-        <v>110178094.80725534</v>
+        <v>85000000.00000006</v>
       </c>
     </row>
     <row r="86">
@@ -6006,22 +6006,22 @@
         <v>85</v>
       </c>
       <c r="B86" s="0">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C86" s="0">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="D86" s="0">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="E86" s="0">
-        <v>105198270.12109375</v>
+        <v>85000000.000000358</v>
       </c>
       <c r="F86" s="0">
-        <v>-127920220.3984375</v>
+        <v>0</v>
       </c>
       <c r="G86" s="0">
-        <v>165620828.47050196</v>
+        <v>85000000.000000358</v>
       </c>
     </row>
     <row r="87">
@@ -6029,22 +6029,22 @@
         <v>86</v>
       </c>
       <c r="B87" s="0">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="C87" s="0">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D87" s="0">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="E87" s="0">
-        <v>108175311.0859375</v>
+        <v>85000000.000000239</v>
       </c>
       <c r="F87" s="0">
-        <v>-536749367.78515625</v>
+        <v>0</v>
       </c>
       <c r="G87" s="0">
-        <v>547541579.92457914</v>
+        <v>85000000.000000239</v>
       </c>
     </row>
     <row r="88">
@@ -6052,22 +6052,22 @@
         <v>87</v>
       </c>
       <c r="B88" s="0">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="C88" s="0">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="D88" s="0">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="E88" s="0">
-        <v>34637663.90234375</v>
+        <v>85000000.000000239</v>
       </c>
       <c r="F88" s="0">
-        <v>-187345746.3359375</v>
+        <v>0</v>
       </c>
       <c r="G88" s="0">
-        <v>190520855.63208342</v>
+        <v>85000000.000000239</v>
       </c>
     </row>
     <row r="89">
@@ -6075,22 +6075,22 @@
         <v>88</v>
       </c>
       <c r="B89" s="0">
-        <v>98</v>
+        <v>26</v>
       </c>
       <c r="C89" s="0">
-        <v>99</v>
+        <v>65</v>
       </c>
       <c r="D89" s="0">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="E89" s="0">
-        <v>108175311.0859375</v>
+        <v>85000000.000000239</v>
       </c>
       <c r="F89" s="0">
-        <v>-128515628.5859375</v>
+        <v>0</v>
       </c>
       <c r="G89" s="0">
-        <v>167982632.19564691</v>
+        <v>85000000.000000239</v>
       </c>
     </row>
     <row r="90">
@@ -6098,22 +6098,22 @@
         <v>89</v>
       </c>
       <c r="B90" s="0">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C90" s="0">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="D90" s="0">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="E90" s="0">
-        <v>73152325.7265625</v>
+        <v>85000000.000000358</v>
       </c>
       <c r="F90" s="0">
-        <v>-17270018.07421875</v>
+        <v>0</v>
       </c>
       <c r="G90" s="0">
-        <v>75163264.188624352</v>
+        <v>85000000.000000358</v>
       </c>
     </row>
     <row r="91">
@@ -6121,22 +6121,22 @@
         <v>90</v>
       </c>
       <c r="B91" s="0">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="C91" s="0">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D91" s="0">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="E91" s="0">
-        <v>25077061.5625</v>
+        <v>85000000.000000239</v>
       </c>
       <c r="F91" s="0">
-        <v>-68442471.36328125</v>
+        <v>0</v>
       </c>
       <c r="G91" s="0">
-        <v>72891912.46580781</v>
+        <v>85000000.000000239</v>
       </c>
     </row>
     <row r="92">
@@ -6144,22 +6144,22 @@
         <v>91</v>
       </c>
       <c r="B92" s="0">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="C92" s="0">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="D92" s="0">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="E92" s="0">
-        <v>30809691.96484375</v>
+        <v>85000000.000000239</v>
       </c>
       <c r="F92" s="0">
-        <v>-3068860.91796875</v>
+        <v>0</v>
       </c>
       <c r="G92" s="0">
-        <v>30962154.742562629</v>
+        <v>85000000.000000239</v>
       </c>
     </row>
     <row r="93">
@@ -6167,22 +6167,22 @@
         <v>92</v>
       </c>
       <c r="B93" s="0">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="C93" s="0">
-        <v>102</v>
+        <v>68</v>
       </c>
       <c r="D93" s="0">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="E93" s="0">
-        <v>25077061.5625</v>
+        <v>85000000.000000239</v>
       </c>
       <c r="F93" s="0">
-        <v>-7654965.23828125</v>
+        <v>0</v>
       </c>
       <c r="G93" s="0">
-        <v>26219410.927950103</v>
+        <v>85000000.000000239</v>
       </c>
     </row>
     <row r="94">
@@ -6190,22 +6190,22 @@
         <v>93</v>
       </c>
       <c r="B94" s="0">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="C94" s="0">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="D94" s="0">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="E94" s="0">
-        <v>105198270.12109375</v>
+        <v>85000000.000000358</v>
       </c>
       <c r="F94" s="0">
-        <v>-46599153.83984375</v>
+        <v>-1.1920928955078125e-07</v>
       </c>
       <c r="G94" s="0">
-        <v>115057190.88809717</v>
+        <v>85000000.000000358</v>
       </c>
     </row>
     <row r="95">
@@ -6213,22 +6213,22 @@
         <v>94</v>
       </c>
       <c r="B95" s="0">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="C95" s="0">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="D95" s="0">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="E95" s="0">
-        <v>34637663.90234375</v>
+        <v>85000000.000000239</v>
       </c>
       <c r="F95" s="0">
-        <v>-60793989.4921875</v>
+        <v>0</v>
       </c>
       <c r="G95" s="0">
-        <v>69969114.036036864</v>
+        <v>85000000.000000239</v>
       </c>
     </row>
     <row r="96">
@@ -6236,22 +6236,22 @@
         <v>95</v>
       </c>
       <c r="B96" s="0">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="C96" s="0">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="D96" s="0">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="E96" s="0">
-        <v>76891313.23046875</v>
+        <v>85000000.000000417</v>
       </c>
       <c r="F96" s="0">
-        <v>-14278828.0625</v>
+        <v>5.9604644775390625e-08</v>
       </c>
       <c r="G96" s="0">
-        <v>78205875.617785245</v>
+        <v>85000000.000000417</v>
       </c>
     </row>
     <row r="97">
@@ -6259,22 +6259,22 @@
         <v>96</v>
       </c>
       <c r="B97" s="0">
-        <v>100</v>
+        <v>66</v>
       </c>
       <c r="C97" s="0">
-        <v>101</v>
+        <v>67</v>
       </c>
       <c r="D97" s="0">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="E97" s="0">
-        <v>76891313.23046875</v>
+        <v>85000000.000000417</v>
       </c>
       <c r="F97" s="0">
-        <v>-69244719.35546875</v>
+        <v>0</v>
       </c>
       <c r="G97" s="0">
-        <v>103475142.95193647</v>
+        <v>85000000.000000417</v>
       </c>
     </row>
     <row r="98">
@@ -6282,22 +6282,22 @@
         <v>97</v>
       </c>
       <c r="B98" s="0">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C98" s="0">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="D98" s="0">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="E98" s="0">
-        <v>162430438.9296875</v>
+        <v>85000000.00000006</v>
       </c>
       <c r="F98" s="0">
-        <v>15320396.2890625</v>
+        <v>5.9604644775390625e-08</v>
       </c>
       <c r="G98" s="0">
-        <v>163151347.01664236</v>
+        <v>85000000.00000006</v>
       </c>
     </row>
     <row r="99">
@@ -6305,22 +6305,22 @@
         <v>98</v>
       </c>
       <c r="B99" s="0">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="C99" s="0">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D99" s="0">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="E99" s="0">
-        <v>164077392.43359375</v>
+        <v>84999999.99999994</v>
       </c>
       <c r="F99" s="0">
-        <v>54362835.15625</v>
+        <v>5.9604644775390625e-08</v>
       </c>
       <c r="G99" s="0">
-        <v>172848802.58200559</v>
+        <v>84999999.99999994</v>
       </c>
     </row>
     <row r="100">
@@ -6328,22 +6328,22 @@
         <v>99</v>
       </c>
       <c r="B100" s="0">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="C100" s="0">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="D100" s="0">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E100" s="0">
-        <v>198123309.40234375</v>
+        <v>84999999.999999881</v>
       </c>
       <c r="F100" s="0">
-        <v>42227739.1640625</v>
+        <v>0</v>
       </c>
       <c r="G100" s="0">
-        <v>202573511.80113587</v>
+        <v>84999999.999999881</v>
       </c>
     </row>
     <row r="101">
@@ -6351,22 +6351,22 @@
         <v>100</v>
       </c>
       <c r="B101" s="0">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="C101" s="0">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="D101" s="0">
-        <v>106</v>
+        <v>72</v>
       </c>
       <c r="E101" s="0">
-        <v>164077392.43359375</v>
+        <v>84999999.99999994</v>
       </c>
       <c r="F101" s="0">
-        <v>14991005.58203125</v>
+        <v>5.9604644775390625e-08</v>
       </c>
       <c r="G101" s="0">
-        <v>164760799.20954505</v>
+        <v>84999999.99999994</v>
       </c>
     </row>
     <row r="102">
@@ -6374,22 +6374,22 @@
         <v>101</v>
       </c>
       <c r="B102" s="0">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C102" s="0">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="D102" s="0">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="E102" s="0">
-        <v>119795910.1484375</v>
+        <v>85000000.000000239</v>
       </c>
       <c r="F102" s="0">
-        <v>72550384.2734375</v>
+        <v>-1.1920928955078125e-07</v>
       </c>
       <c r="G102" s="0">
-        <v>140052198.64934629</v>
+        <v>85000000.000000239</v>
       </c>
     </row>
     <row r="103">
@@ -6397,22 +6397,22 @@
         <v>102</v>
       </c>
       <c r="B103" s="0">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="C103" s="0">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D103" s="0">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="E103" s="0">
-        <v>46272757.83984375</v>
+        <v>85000000.000000358</v>
       </c>
       <c r="F103" s="0">
-        <v>51365321.4375</v>
+        <v>0</v>
       </c>
       <c r="G103" s="0">
-        <v>69134393.499057457</v>
+        <v>85000000.000000358</v>
       </c>
     </row>
     <row r="104">
@@ -6420,22 +6420,22 @@
         <v>103</v>
       </c>
       <c r="B104" s="0">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="C104" s="0">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="D104" s="0">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="E104" s="0">
-        <v>82437451.75390625</v>
+        <v>85000000.000000477</v>
       </c>
       <c r="F104" s="0">
-        <v>116186769.87890625</v>
+        <v>0</v>
       </c>
       <c r="G104" s="0">
-        <v>142461570.06916475</v>
+        <v>85000000.000000477</v>
       </c>
     </row>
     <row r="105">
@@ -6443,22 +6443,22 @@
         <v>104</v>
       </c>
       <c r="B105" s="0">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="C105" s="0">
-        <v>108</v>
+        <v>74</v>
       </c>
       <c r="D105" s="0">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="E105" s="0">
-        <v>46272757.83984375</v>
+        <v>85000000.000000358</v>
       </c>
       <c r="F105" s="0">
-        <v>87255014.7421875</v>
+        <v>-1.1920928955078125e-07</v>
       </c>
       <c r="G105" s="0">
-        <v>98765407.485435814</v>
+        <v>85000000.000000358</v>
       </c>
     </row>
     <row r="106">
@@ -6466,22 +6466,22 @@
         <v>105</v>
       </c>
       <c r="B106" s="0">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C106" s="0">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="D106" s="0">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="E106" s="0">
-        <v>302978004.55859375</v>
+        <v>85000000.000000298</v>
       </c>
       <c r="F106" s="0">
-        <v>135167659.3515625</v>
+        <v>1.1920928955078125e-07</v>
       </c>
       <c r="G106" s="0">
-        <v>331761913.69849449</v>
+        <v>85000000.000000298</v>
       </c>
     </row>
     <row r="107">
@@ -6489,22 +6489,22 @@
         <v>106</v>
       </c>
       <c r="B107" s="0">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="C107" s="0">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D107" s="0">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="E107" s="0">
-        <v>194774763.30078125</v>
+        <v>85000000.000000477</v>
       </c>
       <c r="F107" s="0">
-        <v>229831907.7109375</v>
+        <v>0</v>
       </c>
       <c r="G107" s="0">
-        <v>301263861.45856303</v>
+        <v>85000000.000000477</v>
       </c>
     </row>
     <row r="108">
@@ -6512,22 +6512,22 @@
         <v>107</v>
       </c>
       <c r="B108" s="0">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="C108" s="0">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="D108" s="0">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="E108" s="0">
-        <v>676331117.8828125</v>
+        <v>85000000.000000358</v>
       </c>
       <c r="F108" s="0">
-        <v>542053391.26953125</v>
+        <v>0</v>
       </c>
       <c r="G108" s="0">
-        <v>866744287.55164826</v>
+        <v>85000000.000000358</v>
       </c>
     </row>
     <row r="109">
@@ -6535,22 +6535,22 @@
         <v>108</v>
       </c>
       <c r="B109" s="0">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="C109" s="0">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="D109" s="0">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="E109" s="0">
-        <v>194774763.30078125</v>
+        <v>85000000.000000477</v>
       </c>
       <c r="F109" s="0">
-        <v>156808307.609375</v>
+        <v>1.1920928955078125e-07</v>
       </c>
       <c r="G109" s="0">
-        <v>250052102.07913014</v>
+        <v>85000000.000000477</v>
       </c>
     </row>
     <row r="110">
@@ -6558,22 +6558,22 @@
         <v>109</v>
       </c>
       <c r="B110" s="0">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C110" s="0">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="D110" s="0">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="E110" s="0">
-        <v>119795910.1484375</v>
+        <v>85000000.000000298</v>
       </c>
       <c r="F110" s="0">
-        <v>63219131.609375</v>
+        <v>1.1920928955078125e-07</v>
       </c>
       <c r="G110" s="0">
-        <v>135453751.10987508</v>
+        <v>85000000.000000298</v>
       </c>
     </row>
     <row r="111">
@@ -6581,22 +6581,22 @@
         <v>110</v>
       </c>
       <c r="B111" s="0">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="C111" s="0">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="D111" s="0">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="E111" s="0">
-        <v>82437451.75390625</v>
+        <v>85000000.000000477</v>
       </c>
       <c r="F111" s="0">
-        <v>139962058.4765625</v>
+        <v>0</v>
       </c>
       <c r="G111" s="0">
-        <v>162435560.34524682</v>
+        <v>85000000.000000477</v>
       </c>
     </row>
     <row r="112">
@@ -6604,22 +6604,22 @@
         <v>111</v>
       </c>
       <c r="B112" s="0">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="C112" s="0">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="D112" s="0">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E112" s="0">
-        <v>189067145.33984375</v>
+        <v>85000000.000000179</v>
       </c>
       <c r="F112" s="0">
-        <v>44038971.98046875</v>
+        <v>0</v>
       </c>
       <c r="G112" s="0">
-        <v>194128350.58294323</v>
+        <v>85000000.000000179</v>
       </c>
     </row>
     <row r="113">
@@ -6627,22 +6627,22 @@
         <v>112</v>
       </c>
       <c r="B113" s="0">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="C113" s="0">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="D113" s="0">
-        <v>105</v>
+        <v>71</v>
       </c>
       <c r="E113" s="0">
-        <v>189067145.33984375</v>
+        <v>85000000.000000179</v>
       </c>
       <c r="F113" s="0">
-        <v>118636119.76171875</v>
+        <v>0</v>
       </c>
       <c r="G113" s="0">
-        <v>223205990.86734763</v>
+        <v>85000000.000000179</v>
       </c>
     </row>
     <row r="114">
@@ -6650,22 +6650,22 @@
         <v>113</v>
       </c>
       <c r="B114" s="0">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C114" s="0">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="D114" s="0">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="E114" s="0">
-        <v>119350177.23046875</v>
+        <v>84999999.99999994</v>
       </c>
       <c r="F114" s="0">
-        <v>-1850383.3125</v>
+        <v>5.9604644775390625e-08</v>
       </c>
       <c r="G114" s="0">
-        <v>119364520.37078471</v>
+        <v>84999999.99999994</v>
       </c>
     </row>
     <row r="115">
@@ -6673,22 +6673,22 @@
         <v>114</v>
       </c>
       <c r="B115" s="0">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="C115" s="0">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="D115" s="0">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="E115" s="0">
-        <v>102310862.375</v>
+        <v>85000000.000000358</v>
       </c>
       <c r="F115" s="0">
-        <v>4563072.5859375</v>
+        <v>1.1920928955078125e-07</v>
       </c>
       <c r="G115" s="0">
-        <v>102412568.52232896</v>
+        <v>85000000.000000358</v>
       </c>
     </row>
     <row r="116">
@@ -6696,22 +6696,22 @@
         <v>115</v>
       </c>
       <c r="B116" s="0">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="C116" s="0">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="D116" s="0">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E116" s="0">
-        <v>122355770.15625</v>
+        <v>85000000</v>
       </c>
       <c r="F116" s="0">
-        <v>6471052.60546875</v>
+        <v>1.1920928955078125e-07</v>
       </c>
       <c r="G116" s="0">
-        <v>122526768.55427071</v>
+        <v>85000000</v>
       </c>
     </row>
     <row r="117">
@@ -6719,22 +6719,22 @@
         <v>116</v>
       </c>
       <c r="B117" s="0">
-        <v>97</v>
+        <v>64</v>
       </c>
       <c r="C117" s="0">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="D117" s="0">
-        <v>90</v>
+        <v>58</v>
       </c>
       <c r="E117" s="0">
-        <v>122355770.15625</v>
+        <v>85000000</v>
       </c>
       <c r="F117" s="0">
-        <v>554091.0205078125</v>
+        <v>1.1920928955078125e-07</v>
       </c>
       <c r="G117" s="0">
-        <v>122357024.75701216</v>
+        <v>85000000</v>
       </c>
     </row>
     <row r="118">
@@ -6742,22 +6742,22 @@
         <v>117</v>
       </c>
       <c r="B118" s="0">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C118" s="0">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="D118" s="0">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="E118" s="0">
-        <v>73152325.7265625</v>
+        <v>85000000.000000358</v>
       </c>
       <c r="F118" s="0">
-        <v>17458867.58984375</v>
+        <v>0</v>
       </c>
       <c r="G118" s="0">
-        <v>75206880.115617037</v>
+        <v>85000000.000000358</v>
       </c>
     </row>
     <row r="119">
@@ -6765,22 +6765,22 @@
         <v>118</v>
       </c>
       <c r="B119" s="0">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="C119" s="0">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="D119" s="0">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="E119" s="0">
-        <v>30809691.96484375</v>
+        <v>85000000.000000239</v>
       </c>
       <c r="F119" s="0">
-        <v>38994868.73828125</v>
+        <v>-1.1920928955078125e-07</v>
       </c>
       <c r="G119" s="0">
-        <v>49697453.726366527</v>
+        <v>85000000.000000239</v>
       </c>
     </row>
     <row r="120">
@@ -6788,22 +6788,22 @@
         <v>119</v>
       </c>
       <c r="B120" s="0">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="C120" s="0">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="D120" s="0">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="E120" s="0">
-        <v>86219800.12109375</v>
+        <v>85000000.000000179</v>
       </c>
       <c r="F120" s="0">
-        <v>45689496.25390625</v>
+        <v>-1.7881393432617188e-07</v>
       </c>
       <c r="G120" s="0">
-        <v>97577579.39638117</v>
+        <v>85000000.000000179</v>
       </c>
     </row>
     <row r="121">
@@ -6811,22 +6811,22 @@
         <v>120</v>
       </c>
       <c r="B121" s="0">
-        <v>103</v>
+        <v>69</v>
       </c>
       <c r="C121" s="0">
-        <v>107</v>
+        <v>73</v>
       </c>
       <c r="D121" s="0">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="E121" s="0">
-        <v>86219800.12109375</v>
+        <v>85000000.000000239</v>
       </c>
       <c r="F121" s="0">
-        <v>27912847.108398438</v>
+        <v>-1.1920928955078125e-07</v>
       </c>
       <c r="G121" s="0">
-        <v>90625498.435143441</v>
+        <v>85000000.000000239</v>
       </c>
     </row>
     <row r="122">
@@ -6834,22 +6834,22 @@
         <v>121</v>
       </c>
       <c r="B122" s="0">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C122" s="0">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="D122" s="0">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="E122" s="0">
-        <v>133600656.25390625</v>
+        <v>84999999.999999881</v>
       </c>
       <c r="F122" s="0">
-        <v>10165338.57421875</v>
+        <v>0</v>
       </c>
       <c r="G122" s="0">
-        <v>133986825.69492763</v>
+        <v>84999999.999999881</v>
       </c>
     </row>
     <row r="123">
@@ -6857,22 +6857,22 @@
         <v>122</v>
       </c>
       <c r="B123" s="0">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="C123" s="0">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D123" s="0">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="E123" s="0">
-        <v>130121313.6015625</v>
+        <v>85000000</v>
       </c>
       <c r="F123" s="0">
-        <v>27197972.09375</v>
+        <v>1.1920928955078125e-07</v>
       </c>
       <c r="G123" s="0">
-        <v>132933389.10675745</v>
+        <v>85000000</v>
       </c>
     </row>
     <row r="124">
@@ -6880,22 +6880,22 @@
         <v>123</v>
       </c>
       <c r="B124" s="0">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="C124" s="0">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="D124" s="0">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E124" s="0">
-        <v>149937421.2421875</v>
+        <v>85000000</v>
       </c>
       <c r="F124" s="0">
-        <v>5325982.13671875</v>
+        <v>0</v>
       </c>
       <c r="G124" s="0">
-        <v>150031984.5048976</v>
+        <v>85000000</v>
       </c>
     </row>
     <row r="125">
@@ -6903,22 +6903,22 @@
         <v>124</v>
       </c>
       <c r="B125" s="0">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="C125" s="0">
-        <v>104</v>
+        <v>70</v>
       </c>
       <c r="D125" s="0">
-        <v>93</v>
+        <v>61</v>
       </c>
       <c r="E125" s="0">
-        <v>149937421.2421875</v>
+        <v>85000000</v>
       </c>
       <c r="F125" s="0">
-        <v>23234750.572265625</v>
+        <v>1.1920928955078125e-07</v>
       </c>
       <c r="G125" s="0">
-        <v>151727004.59348881</v>
+        <v>85000000</v>
       </c>
     </row>
     <row r="126">
@@ -6926,22 +6926,22 @@
         <v>125</v>
       </c>
       <c r="B126" s="0">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C126" s="0">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="D126" s="0">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="E126" s="0">
-        <v>109374950.05859375</v>
+        <v>85000000.000000239</v>
       </c>
       <c r="F126" s="0">
-        <v>10214342.723632813</v>
+        <v>0</v>
       </c>
       <c r="G126" s="0">
-        <v>109850864.80131008</v>
+        <v>85000000.000000239</v>
       </c>
     </row>
     <row r="127">
@@ -6949,22 +6949,22 @@
         <v>126</v>
       </c>
       <c r="B127" s="0">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="C127" s="0">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="D127" s="0">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="E127" s="0">
-        <v>130121313.6015625</v>
+        <v>85000000</v>
       </c>
       <c r="F127" s="0">
-        <v>36909193.55859375</v>
+        <v>-1.7881393432617188e-07</v>
       </c>
       <c r="G127" s="0">
-        <v>135254740.48084936</v>
+        <v>85000000</v>
       </c>
     </row>
     <row r="128">
@@ -6972,22 +6972,22 @@
         <v>127</v>
       </c>
       <c r="B128" s="0">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="C128" s="0">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="D128" s="0">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="E128" s="0">
-        <v>133600656.25390625</v>
+        <v>84999999.999999881</v>
       </c>
       <c r="F128" s="0">
-        <v>15466961.475585938</v>
+        <v>0</v>
       </c>
       <c r="G128" s="0">
-        <v>134492982.15431792</v>
+        <v>84999999.999999881</v>
       </c>
     </row>
     <row r="129">
@@ -6995,22 +6995,22 @@
         <v>128</v>
       </c>
       <c r="B129" s="0">
-        <v>114</v>
+        <v>80</v>
       </c>
       <c r="C129" s="0">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="D129" s="0">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="E129" s="0">
-        <v>109374950.05859375</v>
+        <v>85000000.000000179</v>
       </c>
       <c r="F129" s="0">
-        <v>20312102.72265625</v>
+        <v>0</v>
       </c>
       <c r="G129" s="0">
-        <v>111245050.3048815</v>
+        <v>85000000.000000179</v>
       </c>
     </row>
     <row r="130">
@@ -11969,7 +11969,7 @@
         <v>85</v>
       </c>
       <c r="X2" s="0">
-        <v>0.040000000000000001</v>
+        <v>0.02</v>
       </c>
       <c r="Y2" s="0">
         <v>20</v>

--- a/project2_results.xlsx
+++ b/project2_results.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="234" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="429" uniqueCount="39">
   <si>
     <t>Node</t>
   </si>
@@ -225,7 +225,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="0">
-        <v>24885.090036099591</v>
+        <v>9431.5943319371381</v>
       </c>
     </row>
     <row r="3">
@@ -245,7 +245,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="0">
-        <v>23873.826059151852</v>
+        <v>8740.8614680877654</v>
       </c>
     </row>
     <row r="4">
@@ -265,7 +265,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="0">
-        <v>10597.408070298217</v>
+        <v>3294.2090500424697</v>
       </c>
     </row>
     <row r="5">
@@ -325,7 +325,7 @@
         <v>-0.0040000000000000001</v>
       </c>
       <c r="F7" s="0">
-        <v>10939.861389368491</v>
+        <v>3532.8914558830106</v>
       </c>
     </row>
     <row r="8">
@@ -345,7 +345,7 @@
         <v>-0.0040000000000000001</v>
       </c>
       <c r="F8" s="0">
-        <v>20839.927669986406</v>
+        <v>5724.0675815745899</v>
       </c>
     </row>
     <row r="9">
@@ -365,7 +365,7 @@
         <v>-0.00021210000000000001</v>
       </c>
       <c r="F9" s="0">
-        <v>24582.642869831641</v>
+        <v>8730.329540408884</v>
       </c>
     </row>
     <row r="10">
@@ -385,7 +385,7 @@
         <v>-0.0028</v>
       </c>
       <c r="F10" s="0">
-        <v>21882.76370368166</v>
+        <v>6643.8564817519255</v>
       </c>
     </row>
     <row r="11">
@@ -405,7 +405,7 @@
         <v>-0.0022000000000000001</v>
       </c>
       <c r="F11" s="0">
-        <v>22232.74957370471</v>
+        <v>7050.9098170508478</v>
       </c>
     </row>
     <row r="12">
@@ -425,7 +425,7 @@
         <v>-0.0016000000000000001</v>
       </c>
       <c r="F12" s="0">
-        <v>22580.246228296877</v>
+        <v>7452.2007977482872</v>
       </c>
     </row>
     <row r="13">
@@ -445,7 +445,7 @@
         <v>-0.001</v>
       </c>
       <c r="F13" s="0">
-        <v>22940.438533452511</v>
+        <v>7860.5594842637374</v>
       </c>
     </row>
     <row r="14">
@@ -465,7 +465,7 @@
         <v>-0.00040000000000000002</v>
       </c>
       <c r="F14" s="0">
-        <v>23382.234146422969</v>
+        <v>8337.0508555303913</v>
       </c>
     </row>
     <row r="15">
@@ -485,7 +485,7 @@
         <v>-0.0040000000000000001</v>
       </c>
       <c r="F15" s="0">
-        <v>20360.871945057832</v>
+        <v>5944.5080813484301</v>
       </c>
     </row>
     <row r="16">
@@ -505,7 +505,7 @@
         <v>-0.0033999999999999998</v>
       </c>
       <c r="F16" s="0">
-        <v>20524.842442879493</v>
+        <v>6134.735574387747</v>
       </c>
     </row>
     <row r="17">
@@ -525,7 +525,7 @@
         <v>-0.0028</v>
       </c>
       <c r="F17" s="0">
-        <v>20778.678567361891</v>
+        <v>6429.7887255091328</v>
       </c>
     </row>
     <row r="18">
@@ -545,7 +545,7 @@
         <v>-0.0022000000000000001</v>
       </c>
       <c r="F18" s="0">
-        <v>21054.445568775704</v>
+        <v>6747.9690643652093</v>
       </c>
     </row>
     <row r="19">
@@ -565,7 +565,7 @@
         <v>-0.0016000000000000001</v>
       </c>
       <c r="F19" s="0">
-        <v>21349.689629402634</v>
+        <v>7084.5229319944938</v>
       </c>
     </row>
     <row r="20">
@@ -585,7 +585,7 @@
         <v>-0.001</v>
       </c>
       <c r="F20" s="0">
-        <v>21672.844144692514</v>
+        <v>7444.8903149584194</v>
       </c>
     </row>
     <row r="21">
@@ -605,7 +605,7 @@
         <v>-0.00040000000000000002</v>
       </c>
       <c r="F21" s="0">
-        <v>22047.302286040634</v>
+        <v>7847.954095686946</v>
       </c>
     </row>
     <row r="22">
@@ -625,7 +625,7 @@
         <v>-0.0040000000000000001</v>
       </c>
       <c r="F22" s="0">
-        <v>19419.271132956928</v>
+        <v>5924.750258264884</v>
       </c>
     </row>
     <row r="23">
@@ -645,7 +645,7 @@
         <v>-0.0033999999999999998</v>
       </c>
       <c r="F23" s="0">
-        <v>19493.543644241308</v>
+        <v>6009.2548644713697</v>
       </c>
     </row>
     <row r="24">
@@ -665,7 +665,7 @@
         <v>-0.0028</v>
       </c>
       <c r="F24" s="0">
-        <v>19652.66255411071</v>
+        <v>6192.5937815316465</v>
       </c>
     </row>
     <row r="25">
@@ -685,7 +685,7 @@
         <v>-0.0022000000000000001</v>
       </c>
       <c r="F25" s="0">
-        <v>19856.66450463358</v>
+        <v>6426.6547829063747</v>
       </c>
     </row>
     <row r="26">
@@ -705,7 +705,7 @@
         <v>-0.0016000000000000001</v>
       </c>
       <c r="F26" s="0">
-        <v>20091.222575845441</v>
+        <v>6693.0315509060565</v>
       </c>
     </row>
     <row r="27">
@@ -725,7 +725,7 @@
         <v>-0.001</v>
       </c>
       <c r="F27" s="0">
-        <v>20353.946129874254</v>
+        <v>6986.524747888503</v>
       </c>
     </row>
     <row r="28">
@@ -745,7 +745,7 @@
         <v>-0.00040000000000000002</v>
       </c>
       <c r="F28" s="0">
-        <v>20647.562484734884</v>
+        <v>7307.9132489667318</v>
       </c>
     </row>
     <row r="29">
@@ -765,7 +765,7 @@
         <v>-0.0040000000000000001</v>
       </c>
       <c r="F29" s="0">
-        <v>18335.14310579505</v>
+        <v>5737.8085145044488</v>
       </c>
     </row>
     <row r="30">
@@ -785,7 +785,7 @@
         <v>-0.0033999999999999998</v>
       </c>
       <c r="F30" s="0">
-        <v>18377.398447018139</v>
+        <v>5784.9398437011987</v>
       </c>
     </row>
     <row r="31">
@@ -805,7 +805,7 @@
         <v>-0.0028</v>
       </c>
       <c r="F31" s="0">
-        <v>18481.763500206067</v>
+        <v>5904.6767532397089</v>
       </c>
     </row>
     <row r="32">
@@ -825,7 +825,7 @@
         <v>-0.0022000000000000001</v>
       </c>
       <c r="F32" s="0">
-        <v>18628.327319802469</v>
+        <v>6073.0247348225848</v>
       </c>
     </row>
     <row r="33">
@@ -845,7 +845,7 @@
         <v>-0.0016000000000000001</v>
       </c>
       <c r="F33" s="0">
-        <v>18804.59003947131</v>
+        <v>6274.4237408348554</v>
       </c>
     </row>
     <row r="34">
@@ -865,7 +865,7 @@
         <v>-0.001</v>
       </c>
       <c r="F34" s="0">
-        <v>19004.155314224172</v>
+        <v>6500.2638767228054</v>
       </c>
     </row>
     <row r="35">
@@ -885,7 +885,7 @@
         <v>-0.00040000000000000002</v>
       </c>
       <c r="F35" s="0">
-        <v>19223.28427888103</v>
+        <v>6745.4082705759465</v>
       </c>
     </row>
     <row r="36">
@@ -905,7 +905,7 @@
         <v>-0.0040000000000000001</v>
       </c>
       <c r="F36" s="0">
-        <v>17172.188783743397</v>
+        <v>5458.3752086082677</v>
       </c>
     </row>
     <row r="37">
@@ -925,7 +925,7 @@
         <v>-0.0033999999999999998</v>
       </c>
       <c r="F37" s="0">
-        <v>17199.143537830107</v>
+        <v>5488.0192425892692</v>
       </c>
     </row>
     <row r="38">
@@ -945,7 +945,7 @@
         <v>-0.0028</v>
       </c>
       <c r="F38" s="0">
-        <v>17268.665679892962</v>
+        <v>5568.1486529034037</v>
       </c>
     </row>
     <row r="39">
@@ -965,7 +965,7 @@
         <v>-0.0022000000000000001</v>
       </c>
       <c r="F39" s="0">
-        <v>17370.291234898901</v>
+        <v>5686.3436623093967</v>
       </c>
     </row>
     <row r="40">
@@ -985,7 +985,7 @@
         <v>-0.0016000000000000001</v>
       </c>
       <c r="F40" s="0">
-        <v>17494.654948013162</v>
+        <v>5831.3748008879693</v>
       </c>
     </row>
     <row r="41">
@@ -1005,7 +1005,7 @@
         <v>-0.001</v>
       </c>
       <c r="F41" s="0">
-        <v>17634.800808670083</v>
+        <v>5994.6987475919068</v>
       </c>
     </row>
     <row r="42">
@@ -1025,7 +1025,7 @@
         <v>-0.00040000000000000002</v>
       </c>
       <c r="F42" s="0">
-        <v>17785.744228214764</v>
+        <v>6169.9849141323339</v>
       </c>
     </row>
     <row r="43">
@@ -1045,7 +1045,7 @@
         <v>-0.0040000000000000001</v>
       </c>
       <c r="F43" s="0">
-        <v>15960.649706588525</v>
+        <v>5121.3399483607627</v>
       </c>
     </row>
     <row r="44">
@@ -1065,7 +1065,7 @@
         <v>-0.0033999999999999998</v>
       </c>
       <c r="F44" s="0">
-        <v>15978.321240665948</v>
+        <v>5140.6132651442131</v>
       </c>
     </row>
     <row r="45">
@@ -1085,7 +1085,7 @@
         <v>-0.0028</v>
       </c>
       <c r="F45" s="0">
-        <v>16023.464446636774</v>
+        <v>5193.5549534752399</v>
       </c>
     </row>
     <row r="46">
@@ -1105,7 +1105,7 @@
         <v>-0.0022000000000000001</v>
       </c>
       <c r="F46" s="0">
-        <v>16089.516991887009</v>
+        <v>5272.8264606236316</v>
       </c>
     </row>
     <row r="47">
@@ -1125,7 +1125,7 @@
         <v>-0.0016000000000000001</v>
       </c>
       <c r="F47" s="0">
-        <v>16168.937709012349</v>
+        <v>5370.0330528157174</v>
       </c>
     </row>
     <row r="48">
@@ -1145,7 +1145,7 @@
         <v>-0.001</v>
       </c>
       <c r="F48" s="0">
-        <v>16254.648744228227</v>
+        <v>5477.1713986245204</v>
       </c>
     </row>
     <row r="49">
@@ -1165,7 +1165,7 @@
         <v>-0.00040000000000000002</v>
       </c>
       <c r="F49" s="0">
-        <v>16340.322824560431</v>
+        <v>5586.6780508862375</v>
       </c>
     </row>
     <row r="50">
@@ -1185,7 +1185,7 @@
         <v>-0.0040000000000000001</v>
       </c>
       <c r="F50" s="0">
-        <v>14718.716966221566</v>
+        <v>4747.3405572811898</v>
       </c>
     </row>
     <row r="51">
@@ -1205,7 +1205,7 @@
         <v>-0.0033999999999999998</v>
       </c>
       <c r="F51" s="0">
-        <v>14730.0272716084</v>
+        <v>4759.5389161515814</v>
       </c>
     </row>
     <row r="52">
@@ -1225,7 +1225,7 @@
         <v>-0.0028</v>
       </c>
       <c r="F52" s="0">
-        <v>14757.353874101187</v>
+        <v>4792.6314352297186</v>
       </c>
     </row>
     <row r="53">
@@ -1245,7 +1245,7 @@
         <v>-0.0022000000000000001</v>
       </c>
       <c r="F53" s="0">
-        <v>14795.374577000013</v>
+        <v>4841.3741738941708</v>
       </c>
     </row>
     <row r="54">
@@ -1265,7 +1265,7 @@
         <v>-0.0016000000000000001</v>
       </c>
       <c r="F54" s="0">
-        <v>14836.93015192098</v>
+        <v>4898.7595511267491</v>
       </c>
     </row>
     <row r="55">
@@ -1285,7 +1285,7 @@
         <v>-0.001</v>
       </c>
       <c r="F55" s="0">
-        <v>14874.533634670037</v>
+        <v>4957.2757432042199</v>
       </c>
     </row>
     <row r="56">
@@ -1305,7 +1305,7 @@
         <v>-0.00040000000000000002</v>
       </c>
       <c r="F56" s="0">
-        <v>14902.30059054698</v>
+        <v>5010.1885328741528</v>
       </c>
     </row>
     <row r="57">
@@ -1325,7 +1325,7 @@
         <v>-0.0040000000000000001</v>
       </c>
       <c r="F57" s="0">
-        <v>13458.727928965669</v>
+        <v>4350.4115178756529</v>
       </c>
     </row>
     <row r="58">
@@ -1345,7 +1345,7 @@
         <v>-0.0033999999999999998</v>
       </c>
       <c r="F58" s="0">
-        <v>13465.717005444891</v>
+        <v>4357.5704069512039</v>
       </c>
     </row>
     <row r="59">
@@ -1365,7 +1365,7 @@
         <v>-0.0028</v>
       </c>
       <c r="F59" s="0">
-        <v>13480.549201159542</v>
+        <v>4376.0576973978796</v>
       </c>
     </row>
     <row r="60">
@@ -1385,7 +1385,7 @@
         <v>-0.0022000000000000001</v>
       </c>
       <c r="F60" s="0">
-        <v>13497.697290090873</v>
+        <v>4401.2792485965829</v>
       </c>
     </row>
     <row r="61">
@@ -1405,7 +1405,7 @@
         <v>-0.0016000000000000001</v>
       </c>
       <c r="F61" s="0">
-        <v>13508.874687001528</v>
+        <v>4426.3552345928874</v>
       </c>
     </row>
     <row r="62">
@@ -1425,7 +1425,7 @@
         <v>-0.001</v>
       </c>
       <c r="F62" s="0">
-        <v>13504.255051983972</v>
+        <v>4442.9834901914583</v>
       </c>
     </row>
     <row r="63">
@@ -1445,7 +1445,7 @@
         <v>-0.00040000000000000002</v>
       </c>
       <c r="F63" s="0">
-        <v>13475.354516968178</v>
+        <v>4443.2878311468467</v>
       </c>
     </row>
     <row r="64">
@@ -1465,7 +1465,7 @@
         <v>-0.0040000000000000001</v>
       </c>
       <c r="F64" s="0">
-        <v>12188.934142003389</v>
+        <v>3940.5090036223373</v>
       </c>
     </row>
     <row r="65">
@@ -1485,7 +1485,7 @@
         <v>-0.0033999999999999998</v>
       </c>
       <c r="F65" s="0">
-        <v>12193.563620045943</v>
+        <v>3944.2734963796993</v>
       </c>
     </row>
     <row r="66">
@@ -1505,7 +1505,7 @@
         <v>-0.0028</v>
       </c>
       <c r="F66" s="0">
-        <v>12201.428635001215</v>
+        <v>3952.7496988140101</v>
       </c>
     </row>
     <row r="67">
@@ -1525,7 +1525,7 @@
         <v>-0.0022000000000000001</v>
       </c>
       <c r="F67" s="0">
-        <v>12205.990695202414</v>
+        <v>3961.329888501401</v>
       </c>
     </row>
     <row r="68">
@@ -1545,7 +1545,7 @@
         <v>-0.0016000000000000001</v>
       </c>
       <c r="F68" s="0">
-        <v>12196.616254010278</v>
+        <v>3962.3986484567617</v>
       </c>
     </row>
     <row r="69">
@@ -1565,7 +1565,7 @@
         <v>-0.001</v>
       </c>
       <c r="F69" s="0">
-        <v>12158.257369296154</v>
+        <v>3945.0151518218781</v>
       </c>
     </row>
     <row r="70">
@@ -1585,7 +1585,7 @@
         <v>-0.00040000000000000002</v>
       </c>
       <c r="F70" s="0">
-        <v>12070.729309404654</v>
+        <v>3894.1585768551222</v>
       </c>
     </row>
     <row r="71">
@@ -1605,7 +1605,7 @@
         <v>-0.0033999999999999998</v>
       </c>
       <c r="F71" s="0">
-        <v>10918.172930348055</v>
+        <v>3526.2460123089395</v>
       </c>
     </row>
     <row r="72">
@@ -1625,7 +1625,7 @@
         <v>-0.0028</v>
       </c>
       <c r="F72" s="0">
-        <v>10925.611023596952</v>
+        <v>3529.3377129770579</v>
       </c>
     </row>
     <row r="73">
@@ -1645,7 +1645,7 @@
         <v>-0.0022000000000000001</v>
       </c>
       <c r="F73" s="0">
-        <v>10928.220601707289</v>
+        <v>3528.8919581382475</v>
       </c>
     </row>
     <row r="74">
@@ -1665,7 +1665,7 @@
         <v>-0.0016000000000000001</v>
       </c>
       <c r="F74" s="0">
-        <v>10913.342264541019</v>
+        <v>3516.8943189108827</v>
       </c>
     </row>
     <row r="75">
@@ -1685,7 +1685,7 @@
         <v>-0.001</v>
       </c>
       <c r="F75" s="0">
-        <v>10861.428861785711</v>
+        <v>3480.5198917841699</v>
       </c>
     </row>
     <row r="76">
@@ -1705,7 +1705,7 @@
         <v>-0.00040000000000000002</v>
       </c>
       <c r="F76" s="0">
-        <v>10737.850542439204</v>
+        <v>3396.6741055218686</v>
       </c>
     </row>
     <row r="77">
@@ -1725,7 +1725,7 @@
         <v>-0.0040000000000000001</v>
       </c>
       <c r="F77" s="0">
-        <v>9632.7489576030621</v>
+        <v>3105.3773618285027</v>
       </c>
     </row>
     <row r="78">
@@ -1745,7 +1745,7 @@
         <v>-0.0033999999999999998</v>
       </c>
       <c r="F78" s="0">
-        <v>9639.8583539071551</v>
+        <v>3107.0603471466793</v>
       </c>
     </row>
     <row r="79">
@@ -1765,7 +1765,7 @@
         <v>-0.0028</v>
       </c>
       <c r="F79" s="0">
-        <v>9654.6219273312545</v>
+        <v>3109.4631826470413</v>
       </c>
     </row>
     <row r="80">
@@ -1785,7 +1785,7 @@
         <v>-0.0022000000000000001</v>
       </c>
       <c r="F80" s="0">
-        <v>9667.9384234887693</v>
+        <v>3108.0059121636473</v>
       </c>
     </row>
     <row r="81">
@@ -1805,7 +1805,7 @@
         <v>-0.0016000000000000001</v>
       </c>
       <c r="F81" s="0">
-        <v>9667.1033406607967</v>
+        <v>3095.7667772643513</v>
       </c>
     </row>
     <row r="82">
@@ -1825,7 +1825,7 @@
         <v>-0.001</v>
       </c>
       <c r="F82" s="0">
-        <v>9636.2652708664646</v>
+        <v>3063.4959908820479</v>
       </c>
     </row>
     <row r="83">
@@ -1845,7 +1845,7 @@
         <v>-0.00040000000000000002</v>
       </c>
       <c r="F83" s="0">
-        <v>9555.8173148569731</v>
+        <v>2999.4806654273216</v>
       </c>
     </row>
     <row r="84">
@@ -1865,7 +1865,7 @@
         <v>-0.0040000000000000001</v>
       </c>
       <c r="F84" s="0">
-        <v>8340.5999638009289</v>
+        <v>2684.0143366403313</v>
       </c>
     </row>
     <row r="85">
@@ -1885,7 +1885,7 @@
         <v>-0.0033999999999999998</v>
       </c>
       <c r="F85" s="0">
-        <v>8353.8896003462451</v>
+        <v>2687.1548318022355</v>
       </c>
     </row>
     <row r="86">
@@ -1905,7 +1905,7 @@
         <v>-0.0028</v>
       </c>
       <c r="F86" s="0">
-        <v>8385.0799083321526</v>
+        <v>2693.4487583007813</v>
       </c>
     </row>
     <row r="87">
@@ -1925,7 +1925,7 @@
         <v>-0.0022000000000000001</v>
       </c>
       <c r="F87" s="0">
-        <v>8421.8078242557476</v>
+        <v>2697.9017306049491</v>
       </c>
     </row>
     <row r="88">
@@ -1945,7 +1945,7 @@
         <v>-0.0016000000000000001</v>
       </c>
       <c r="F88" s="0">
-        <v>8450.8674037469336</v>
+        <v>2694.6708871008295</v>
       </c>
     </row>
     <row r="89">
@@ -1965,7 +1965,7 @@
         <v>-0.001</v>
       </c>
       <c r="F89" s="0">
-        <v>8460.7115661623866</v>
+        <v>2678.2166290523514</v>
       </c>
     </row>
     <row r="90">
@@ -1985,7 +1985,7 @@
         <v>-0.00040000000000000002</v>
       </c>
       <c r="F90" s="0">
-        <v>8443.7753164787009</v>
+        <v>2645.1047267274466</v>
       </c>
     </row>
     <row r="91">
@@ -2005,7 +2005,7 @@
         <v>-0.0040000000000000001</v>
       </c>
       <c r="F91" s="0">
-        <v>7024.4547352094778</v>
+        <v>2257.1974503224533</v>
       </c>
     </row>
     <row r="92">
@@ -2025,7 +2025,7 @@
         <v>-0.0033999999999999998</v>
       </c>
       <c r="F92" s="0">
-        <v>7050.02017534474</v>
+        <v>2264.0958851211494</v>
       </c>
     </row>
     <row r="93">
@@ -2045,7 +2045,7 @@
         <v>-0.0028</v>
       </c>
       <c r="F93" s="0">
-        <v>7110.0002813953552</v>
+        <v>2279.2752881489023</v>
       </c>
     </row>
     <row r="94">
@@ -2065,7 +2065,7 @@
         <v>-0.0022000000000000001</v>
       </c>
       <c r="F94" s="0">
-        <v>7183.3455614551349</v>
+        <v>2295.481364854536</v>
       </c>
     </row>
     <row r="95">
@@ -2085,7 +2085,7 @@
         <v>-0.0016000000000000001</v>
       </c>
       <c r="F95" s="0">
-        <v>7253.8468839088082</v>
+        <v>2306.7984114816691</v>
       </c>
     </row>
     <row r="96">
@@ -2105,7 +2105,7 @@
         <v>-0.001</v>
       </c>
       <c r="F96" s="0">
-        <v>7311.9382735574427</v>
+        <v>2309.5949114990799</v>
       </c>
     </row>
     <row r="97">
@@ -2125,7 +2125,7 @@
         <v>-0.00040000000000000002</v>
       </c>
       <c r="F97" s="0">
-        <v>7354.454946737399</v>
+        <v>2303.1594684706442</v>
       </c>
     </row>
     <row r="98">
@@ -2145,7 +2145,7 @@
         <v>-0.0040000000000000001</v>
       </c>
       <c r="F98" s="0">
-        <v>5659.3515932909259</v>
+        <v>1817.2778633578373</v>
       </c>
     </row>
     <row r="99">
@@ -2165,7 +2165,7 @@
         <v>-0.0033999999999999998</v>
       </c>
       <c r="F99" s="0">
-        <v>5711.736084427891</v>
+        <v>1832.7559702110079</v>
       </c>
     </row>
     <row r="100">
@@ -2185,7 +2185,7 @@
         <v>-0.0028</v>
       </c>
       <c r="F100" s="0">
-        <v>5821.5554804493913</v>
+        <v>1864.0751443191423</v>
       </c>
     </row>
     <row r="101">
@@ -2205,7 +2205,7 @@
         <v>-0.0022000000000000001</v>
       </c>
       <c r="F101" s="0">
-        <v>5947.7272562606231</v>
+        <v>1897.9500291826207</v>
       </c>
     </row>
     <row r="102">
@@ -2225,7 +2225,7 @@
         <v>-0.0016000000000000001</v>
       </c>
       <c r="F102" s="0">
-        <v>6069.2362968757216</v>
+        <v>1927.4464824722277</v>
       </c>
     </row>
     <row r="103">
@@ -2245,7 +2245,7 @@
         <v>-0.001</v>
       </c>
       <c r="F103" s="0">
-        <v>6178.7396974211842</v>
+        <v>1950.2051369916517</v>
       </c>
     </row>
     <row r="104">
@@ -2265,7 +2265,7 @@
         <v>-0.00040000000000000002</v>
       </c>
       <c r="F104" s="0">
-        <v>6276.5541655232828</v>
+        <v>1966.8733104632149</v>
       </c>
     </row>
     <row r="105">
@@ -2285,7 +2285,7 @@
         <v>-0.0040000000000000001</v>
       </c>
       <c r="F105" s="0">
-        <v>4191.2256524131226</v>
+        <v>1346.9587024217865</v>
       </c>
     </row>
     <row r="106">
@@ -2305,7 +2305,7 @@
         <v>-0.0033999999999999998</v>
       </c>
       <c r="F106" s="0">
-        <v>4316.0170886265041</v>
+        <v>1385.5749880459034</v>
       </c>
     </row>
     <row r="107">
@@ -2325,7 +2325,7 @@
         <v>-0.0028</v>
       </c>
       <c r="F107" s="0">
-        <v>4516.7582997136924</v>
+        <v>1446.3192897340355</v>
       </c>
     </row>
     <row r="108">
@@ -2345,7 +2345,7 @@
         <v>-0.0022000000000000001</v>
       </c>
       <c r="F108" s="0">
-        <v>4716.7716862622419</v>
+        <v>1504.7971250845762</v>
       </c>
     </row>
     <row r="109">
@@ -2365,7 +2365,7 @@
         <v>-0.0016000000000000001</v>
       </c>
       <c r="F109" s="0">
-        <v>4896.6313499122716</v>
+        <v>1554.8323522329667</v>
       </c>
     </row>
     <row r="110">
@@ -2385,7 +2385,7 @@
         <v>-0.001</v>
       </c>
       <c r="F110" s="0">
-        <v>5057.2300537282881</v>
+        <v>1596.905843532086</v>
       </c>
     </row>
     <row r="111">
@@ -2405,7 +2405,7 @@
         <v>-0.00040000000000000002</v>
       </c>
       <c r="F111" s="0">
-        <v>5205.9839362016037</v>
+        <v>1633.9506781503171</v>
       </c>
     </row>
     <row r="112">
@@ -2425,7 +2425,7 @@
         <v>-0.0040000000000000001</v>
       </c>
       <c r="F112" s="0">
-        <v>2474.7995195365443</v>
+        <v>799.81513120619275</v>
       </c>
     </row>
     <row r="113">
@@ -2445,7 +2445,7 @@
         <v>-0.0033999999999999998</v>
       </c>
       <c r="F113" s="0">
-        <v>2844.3483179513137</v>
+        <v>916.26598981678421</v>
       </c>
     </row>
     <row r="114">
@@ -2465,7 +2465,7 @@
         <v>-0.0028</v>
       </c>
       <c r="F114" s="0">
-        <v>3212.6889435166359</v>
+        <v>1030.8299014865206</v>
       </c>
     </row>
     <row r="115">
@@ -2485,7 +2485,7 @@
         <v>-0.0022000000000000001</v>
       </c>
       <c r="F115" s="0">
-        <v>3505.9698391623824</v>
+        <v>1120.0868291886823</v>
       </c>
     </row>
     <row r="116">
@@ -2505,7 +2505,7 @@
         <v>-0.0016000000000000001</v>
       </c>
       <c r="F116" s="0">
-        <v>3743.2873627828303</v>
+        <v>1190.1799578429759</v>
       </c>
     </row>
     <row r="117">
@@ -2525,7 +2525,7 @@
         <v>-0.001</v>
       </c>
       <c r="F117" s="0">
-        <v>3947.5652313780929</v>
+        <v>1248.6352067534081</v>
       </c>
     </row>
     <row r="118">
@@ -2545,7 +2545,7 @@
         <v>-0.00040000000000000002</v>
       </c>
       <c r="F118" s="0">
-        <v>4136.9204484615611</v>
+        <v>1301.7199518493562</v>
       </c>
     </row>
     <row r="119">
@@ -2585,7 +2585,7 @@
         <v>-0.0033999999999999998</v>
       </c>
       <c r="F120" s="0">
-        <v>1373.8877201255652</v>
+        <v>448.843938528519</v>
       </c>
     </row>
     <row r="121">
@@ -2605,7 +2605,7 @@
         <v>-0.0028</v>
       </c>
       <c r="F121" s="0">
-        <v>1983.6793172391515</v>
+        <v>640.64749720658051</v>
       </c>
     </row>
     <row r="122">
@@ -2625,7 +2625,7 @@
         <v>-0.0022000000000000001</v>
       </c>
       <c r="F122" s="0">
-        <v>2351.1313640878198</v>
+        <v>754.54033234065446</v>
       </c>
     </row>
     <row r="123">
@@ -2645,7 +2645,7 @@
         <v>-0.0016000000000000001</v>
       </c>
       <c r="F123" s="0">
-        <v>2622.9830306785721</v>
+        <v>837.16544319684613</v>
       </c>
     </row>
     <row r="124">
@@ -2665,7 +2665,7 @@
         <v>-0.001</v>
       </c>
       <c r="F124" s="0">
-        <v>2852.8230605396852</v>
+        <v>905.73507378921215</v>
       </c>
     </row>
     <row r="125">
@@ -2685,7 +2685,7 @@
         <v>-0.00040000000000000002</v>
       </c>
       <c r="F125" s="0">
-        <v>3066.1325833970614</v>
+        <v>968.71772935717559</v>
       </c>
     </row>
     <row r="126">
@@ -2705,7 +2705,7 @@
         <v>-0.0040000000000000001</v>
       </c>
       <c r="F126" s="0">
-        <v>266.32050441164717</v>
+        <v>97.90201574472934</v>
       </c>
     </row>
     <row r="127">
@@ -2725,7 +2725,7 @@
         <v>-0.0033999999999999998</v>
       </c>
       <c r="F127" s="0">
-        <v>647.52324531179852</v>
+        <v>218.46226709071263</v>
       </c>
     </row>
     <row r="128">
@@ -2745,7 +2745,7 @@
         <v>-0.0028</v>
       </c>
       <c r="F128" s="0">
-        <v>997.0092412265883</v>
+        <v>328.37581647062911</v>
       </c>
     </row>
     <row r="129">
@@ -2765,7 +2765,7 @@
         <v>-0.0022000000000000001</v>
       </c>
       <c r="F129" s="0">
-        <v>1291.8932692711749</v>
+        <v>420.26155977050979</v>
       </c>
     </row>
     <row r="130">
@@ -2785,7 +2785,7 @@
         <v>-0.0016000000000000001</v>
       </c>
       <c r="F130" s="0">
-        <v>1544.6903353039559</v>
+        <v>498.20640881454204</v>
       </c>
     </row>
     <row r="131">
@@ -2805,7 +2805,7 @@
         <v>-0.001</v>
       </c>
       <c r="F131" s="0">
-        <v>1774.6113967050155</v>
+        <v>568.42191584941918</v>
       </c>
     </row>
     <row r="132">
@@ -2825,7 +2825,7 @@
         <v>-0.00040000000000000002</v>
       </c>
       <c r="F132" s="0">
-        <v>1994.7530497027087</v>
+        <v>635.29491935809949</v>
       </c>
     </row>
     <row r="133">
@@ -2845,7 +2845,7 @@
         <v>-0.0028</v>
       </c>
       <c r="F133" s="0">
-        <v>64.941133084227516</v>
+        <v>34.131941814713414</v>
       </c>
     </row>
     <row r="134">
@@ -2865,7 +2865,7 @@
         <v>-0.0022000000000000001</v>
       </c>
       <c r="F134" s="0">
-        <v>274.74213646633376</v>
+        <v>99.923681456213856</v>
       </c>
     </row>
     <row r="135">
@@ -2885,7 +2885,7 @@
         <v>-0.0016000000000000001</v>
       </c>
       <c r="F135" s="0">
-        <v>489.27364456106119</v>
+        <v>166.97671644139297</v>
       </c>
     </row>
     <row r="136">
@@ -2905,7 +2905,7 @@
         <v>-0.001</v>
       </c>
       <c r="F136" s="0">
-        <v>706.17914127371273</v>
+        <v>234.45126143582326</v>
       </c>
     </row>
     <row r="137">
@@ -2925,7 +2925,7 @@
         <v>-0.00040000000000000002</v>
       </c>
       <c r="F137" s="0">
-        <v>923.84457001937824</v>
+        <v>301.78454914724728</v>
       </c>
     </row>
   </sheetData>
@@ -2983,13 +2983,13 @@
         <v>22</v>
       </c>
       <c r="E2" s="0">
-        <v>158120569.60661602</v>
+        <v>31777961.27577424</v>
       </c>
       <c r="F2" s="0">
-        <v>-5986173.3399376869</v>
+        <v>-6676938.3028728962</v>
       </c>
       <c r="G2" s="0">
-        <v>158233842.15766385</v>
+        <v>32471838.998507284</v>
       </c>
     </row>
     <row r="3">
@@ -3006,13 +3006,13 @@
         <v>21</v>
       </c>
       <c r="E3" s="0">
-        <v>153584803.84793234</v>
+        <v>26483413.699394941</v>
       </c>
       <c r="F3" s="0">
-        <v>-10521939.098620415</v>
+        <v>-11971485.879252195</v>
       </c>
       <c r="G3" s="0">
-        <v>153944805.61357999</v>
+        <v>29063511.063366629</v>
       </c>
     </row>
     <row r="4">
@@ -3029,13 +3029,13 @@
         <v>21</v>
       </c>
       <c r="E4" s="0">
-        <v>133393448.38096142</v>
+        <v>2799024.9368356466</v>
       </c>
       <c r="F4" s="0">
-        <v>-23229153.858068466</v>
+        <v>-26948894.847236514</v>
       </c>
       <c r="G4" s="0">
-        <v>135400907.16064659</v>
+        <v>27093864.140879545</v>
       </c>
     </row>
     <row r="5">
@@ -3052,13 +3052,13 @@
         <v>101</v>
       </c>
       <c r="E5" s="0">
-        <v>166119034.15315545</v>
+        <v>52787001.783895344</v>
       </c>
       <c r="F5" s="0">
-        <v>-15512981.743940592</v>
+        <v>-3224142.7235850692</v>
       </c>
       <c r="G5" s="0">
-        <v>166841799.65034261</v>
+        <v>52885372.775797054</v>
       </c>
     </row>
     <row r="6">
@@ -3075,13 +3075,13 @@
         <v>31</v>
       </c>
       <c r="E6" s="0">
-        <v>178221778.69467211</v>
+        <v>54779818.606034994</v>
       </c>
       <c r="F6" s="0">
-        <v>-14396953.625841618</v>
+        <v>-16744292.999182343</v>
       </c>
       <c r="G6" s="0">
-        <v>178802334.0865474</v>
+        <v>57281758.654501565</v>
       </c>
     </row>
     <row r="7">
@@ -3098,13 +3098,13 @@
         <v>73</v>
       </c>
       <c r="E7" s="0">
-        <v>183717371.89731264</v>
+        <v>65803495.172008634</v>
       </c>
       <c r="F7" s="0">
-        <v>7354398.7236685753</v>
+        <v>5153043.8429509997</v>
       </c>
       <c r="G7" s="0">
-        <v>183864515.11219388</v>
+        <v>66004953.130048797</v>
       </c>
     </row>
     <row r="8">
@@ -3121,13 +3121,13 @@
         <v>69</v>
       </c>
       <c r="E8" s="0">
-        <v>183717371.89731264</v>
+        <v>65803495.172008634</v>
       </c>
       <c r="F8" s="0">
-        <v>12399808.484629154</v>
+        <v>7204681.4536236525</v>
       </c>
       <c r="G8" s="0">
-        <v>184135352.35611591</v>
+        <v>66196732.636141129</v>
       </c>
     </row>
     <row r="9">
@@ -3144,13 +3144,13 @@
         <v>36</v>
       </c>
       <c r="E9" s="0">
-        <v>166919445.46830464</v>
+        <v>42063751.824190021</v>
       </c>
       <c r="F9" s="0">
-        <v>-3818590.1622838974</v>
+        <v>-4199571.4806418419</v>
       </c>
       <c r="G9" s="0">
-        <v>166963118.40126196</v>
+        <v>42272870.947548255</v>
       </c>
     </row>
     <row r="10">
@@ -3167,13 +3167,13 @@
         <v>75</v>
       </c>
       <c r="E10" s="0">
-        <v>167454707.24081588</v>
+        <v>56269070.680060744</v>
       </c>
       <c r="F10" s="0">
-        <v>11396793.768011332</v>
+        <v>9068837.7727528811</v>
       </c>
       <c r="G10" s="0">
-        <v>167842086.15629733</v>
+        <v>56995193.953053452</v>
       </c>
     </row>
     <row r="11">
@@ -3190,13 +3190,13 @@
         <v>66</v>
       </c>
       <c r="E11" s="0">
-        <v>181017429.91180921</v>
+        <v>61262040.134780109</v>
       </c>
       <c r="F11" s="0">
-        <v>1328045.835552454</v>
+        <v>-151407.66034281254</v>
       </c>
       <c r="G11" s="0">
-        <v>181022301.49243516</v>
+        <v>61262227.234691851</v>
       </c>
     </row>
     <row r="12">
@@ -3213,13 +3213,13 @@
         <v>4</v>
       </c>
       <c r="E12" s="0">
-        <v>137906004.04907465</v>
+        <v>43365164.413380846</v>
       </c>
       <c r="F12" s="0">
-        <v>-27581200.809814941</v>
+        <v>-8673032.8826761711</v>
       </c>
       <c r="G12" s="0">
-        <v>140637081.13756743</v>
+        <v>44223963.91079767</v>
       </c>
     </row>
     <row r="13">
@@ -3236,13 +3236,13 @@
         <v>57</v>
       </c>
       <c r="E13" s="0">
-        <v>179110621.03983045</v>
+        <v>56945538.803386808</v>
       </c>
       <c r="F13" s="0">
-        <v>-990119.16788983345</v>
+        <v>-1014175.9523698092</v>
       </c>
       <c r="G13" s="0">
-        <v>179113357.69629347</v>
+        <v>56954569.109689504</v>
       </c>
     </row>
     <row r="14">
@@ -3259,13 +3259,13 @@
         <v>14</v>
       </c>
       <c r="E14" s="0">
-        <v>94193237.610291004</v>
+        <v>-43343609.717271566</v>
       </c>
       <c r="F14" s="0">
-        <v>-23229153.858068466</v>
+        <v>-26948894.847236514</v>
       </c>
       <c r="G14" s="0">
-        <v>97015254.473049536</v>
+        <v>51038333.013633676</v>
       </c>
     </row>
     <row r="15">
@@ -3282,13 +3282,13 @@
         <v>21</v>
       </c>
       <c r="E15" s="0">
-        <v>146100663.14040947</v>
+        <v>17776433.904820085</v>
       </c>
       <c r="F15" s="0">
-        <v>-10521939.098620415</v>
+        <v>-11971485.879252195</v>
       </c>
       <c r="G15" s="0">
-        <v>146479059.84290889</v>
+        <v>21431707.270527277</v>
       </c>
     </row>
     <row r="16">
@@ -3305,13 +3305,13 @@
         <v>12</v>
       </c>
       <c r="E16" s="0">
-        <v>174328851.51001787</v>
+        <v>52087697.64845407</v>
       </c>
       <c r="F16" s="0">
-        <v>-51027243.230381489</v>
+        <v>-57850813.92302227</v>
       </c>
       <c r="G16" s="0">
-        <v>181643408.96518755</v>
+        <v>77845005.734940469</v>
       </c>
     </row>
     <row r="17">
@@ -3328,13 +3328,13 @@
         <v>51</v>
       </c>
       <c r="E17" s="0">
-        <v>179365664.44254136</v>
+        <v>56797498.418115497</v>
       </c>
       <c r="F17" s="0">
-        <v>-3871268.686478138</v>
+        <v>-4688106.8694027662</v>
       </c>
       <c r="G17" s="0">
-        <v>179407436.58543605</v>
+        <v>56990649.86973542</v>
       </c>
     </row>
     <row r="18">
@@ -3351,13 +3351,13 @@
         <v>114</v>
       </c>
       <c r="E18" s="0">
-        <v>174109697.05597651</v>
+        <v>55275840.606324703</v>
       </c>
       <c r="F18" s="0">
-        <v>-41548126.883147418</v>
+        <v>-12644731.424472898</v>
       </c>
       <c r="G18" s="0">
-        <v>178998417.46904364</v>
+        <v>56703684.07372547</v>
       </c>
     </row>
     <row r="19">
@@ -3374,13 +3374,13 @@
         <v>19</v>
       </c>
       <c r="E19" s="0">
-        <v>186843885.43258667</v>
+        <v>64935122.001571417</v>
       </c>
       <c r="F19" s="0">
-        <v>-53048236.690983772</v>
+        <v>-57100702.269874692</v>
       </c>
       <c r="G19" s="0">
-        <v>194228609.9923701</v>
+        <v>86469996.351751044</v>
       </c>
     </row>
     <row r="20">
@@ -3397,13 +3397,13 @@
         <v>66</v>
       </c>
       <c r="E20" s="0">
-        <v>185903278.00709367</v>
+        <v>65727183.035951018</v>
       </c>
       <c r="F20" s="0">
-        <v>1328045.835552454</v>
+        <v>-151407.66034281254</v>
       </c>
       <c r="G20" s="0">
-        <v>185908021.55776948</v>
+        <v>65727357.425359935</v>
       </c>
     </row>
     <row r="21">
@@ -3420,13 +3420,13 @@
         <v>56</v>
       </c>
       <c r="E21" s="0">
-        <v>178498446.94458532</v>
+        <v>56231613.915784478</v>
       </c>
       <c r="F21" s="0">
-        <v>-1602293.2631349564</v>
+        <v>-1728100.8399721384</v>
       </c>
       <c r="G21" s="0">
-        <v>178505638.30123133</v>
+        <v>56258161.50646019</v>
       </c>
     </row>
     <row r="22">
@@ -3443,13 +3443,13 @@
         <v>66</v>
       </c>
       <c r="E22" s="0">
-        <v>181017429.91180921</v>
+        <v>61262040.134780109</v>
       </c>
       <c r="F22" s="0">
-        <v>-369690.23229789734</v>
+        <v>63148.602164804936</v>
       </c>
       <c r="G22" s="0">
-        <v>181017807.41889626</v>
+        <v>61262072.681401864</v>
       </c>
     </row>
     <row r="23">
@@ -3466,13 +3466,13 @@
         <v>34</v>
       </c>
       <c r="E23" s="0">
-        <v>193991888.28682947</v>
+        <v>71621726.626877189</v>
       </c>
       <c r="F23" s="0">
-        <v>-31043269.993054867</v>
+        <v>-34728789.129194975</v>
       </c>
       <c r="G23" s="0">
-        <v>196460014.59063223</v>
+        <v>79597490.66016604</v>
       </c>
     </row>
     <row r="24">
@@ -3489,13 +3489,13 @@
         <v>11</v>
       </c>
       <c r="E24" s="0">
-        <v>174328851.51001787</v>
+        <v>52087697.64845407</v>
       </c>
       <c r="F24" s="0">
-        <v>-41826241.922148228</v>
+        <v>-47678464.580815315</v>
       </c>
       <c r="G24" s="0">
-        <v>179276275.5696691</v>
+        <v>70614192.844645813</v>
       </c>
     </row>
     <row r="25">
@@ -3512,13 +3512,13 @@
         <v>25</v>
       </c>
       <c r="E25" s="0">
-        <v>186843885.43258667</v>
+        <v>64935122.001571417</v>
       </c>
       <c r="F25" s="0">
-        <v>-37219170.154081822</v>
+        <v>-41578202.905846596</v>
       </c>
       <c r="G25" s="0">
-        <v>190514839.71203941</v>
+        <v>77105881.917261764</v>
       </c>
     </row>
     <row r="26">
@@ -3535,13 +3535,13 @@
         <v>15</v>
       </c>
       <c r="E26" s="0">
-        <v>156412060.97863436</v>
+        <v>30326265.467728973</v>
       </c>
       <c r="F26" s="0">
-        <v>-35960117.635006428</v>
+        <v>-41799196.408863068</v>
       </c>
       <c r="G26" s="0">
-        <v>160492563.31652108</v>
+        <v>51641603.360525921</v>
       </c>
     </row>
     <row r="27">
@@ -3558,13 +3558,13 @@
         <v>45</v>
       </c>
       <c r="E27" s="0">
-        <v>181443017.76001835</v>
+        <v>58581603.572150111</v>
       </c>
       <c r="F27" s="0">
-        <v>-17618192.691186905</v>
+        <v>-20546077.965297818</v>
       </c>
       <c r="G27" s="0">
-        <v>182296377.93320557</v>
+        <v>62080154.613536902</v>
       </c>
     </row>
     <row r="28">
@@ -3581,13 +3581,13 @@
         <v>15</v>
       </c>
       <c r="E28" s="0">
-        <v>137756031.64997721</v>
+        <v>8106652.8497886658</v>
       </c>
       <c r="F28" s="0">
-        <v>-54616146.963662624</v>
+        <v>-64018809.026803255</v>
       </c>
       <c r="G28" s="0">
-        <v>148187879.95347637</v>
+        <v>64530037.421632513</v>
       </c>
     </row>
     <row r="29">
@@ -3604,13 +3604,13 @@
         <v>26</v>
       </c>
       <c r="E29" s="0">
-        <v>191220365.55042839</v>
+        <v>68886956.748473883</v>
       </c>
       <c r="F29" s="0">
-        <v>-41595650.271922588</v>
+        <v>-45530037.652749062</v>
       </c>
       <c r="G29" s="0">
-        <v>195692172.35950845</v>
+        <v>82573586.204832226</v>
       </c>
     </row>
     <row r="30">
@@ -3627,13 +3627,13 @@
         <v>27</v>
       </c>
       <c r="E30" s="0">
-        <v>201772745.82929611</v>
+        <v>79688205.27202785</v>
       </c>
       <c r="F30" s="0">
-        <v>-50501292.065896988</v>
+        <v>-53682870.469511986</v>
       </c>
       <c r="G30" s="0">
-        <v>207996686.17508972</v>
+        <v>96083612.761611164</v>
       </c>
     </row>
     <row r="31">
@@ -3650,13 +3650,13 @@
         <v>96</v>
       </c>
       <c r="E31" s="0">
-        <v>154320385.71335113</v>
+        <v>48442244.919713676</v>
       </c>
       <c r="F31" s="0">
-        <v>-6023195.3671604395</v>
+        <v>911687.7623617053</v>
       </c>
       <c r="G31" s="0">
-        <v>154437885.01902133</v>
+        <v>48450823.186376981</v>
       </c>
     </row>
     <row r="32">
@@ -3673,13 +3673,13 @@
         <v>12</v>
       </c>
       <c r="E32" s="0">
-        <v>150457517.39245772</v>
+        <v>34574808.312827051</v>
       </c>
       <c r="F32" s="0">
-        <v>-62587711.837481499</v>
+        <v>-67502944.262775898</v>
       </c>
       <c r="G32" s="0">
-        <v>162956086.76251814</v>
+        <v>75842368.46256955</v>
       </c>
     </row>
     <row r="33">
@@ -3696,13 +3696,13 @@
         <v>47</v>
       </c>
       <c r="E33" s="0">
-        <v>195516307.18741036</v>
+        <v>73651884.51787591</v>
       </c>
       <c r="F33" s="0">
-        <v>-12137161.380395412</v>
+        <v>-15513442.403743267</v>
       </c>
       <c r="G33" s="0">
-        <v>195892667.19960594</v>
+        <v>75267967.876439899</v>
       </c>
     </row>
     <row r="34">
@@ -3719,13 +3719,13 @@
         <v>8</v>
       </c>
       <c r="E34" s="0">
-        <v>97430472.789387703</v>
+        <v>-23820174.735598087</v>
       </c>
       <c r="F34" s="0">
-        <v>-231913027.227808</v>
+        <v>-253969095.56163335</v>
       </c>
       <c r="G34" s="0">
-        <v>251547906.42326889</v>
+        <v>255083716.1106692</v>
       </c>
     </row>
     <row r="35">
@@ -3742,13 +3742,13 @@
         <v>75</v>
       </c>
       <c r="E35" s="0">
-        <v>188824491.9867723</v>
+        <v>70476966.772210896</v>
       </c>
       <c r="F35" s="0">
-        <v>17506928.574088573</v>
+        <v>11878153.053825974</v>
       </c>
       <c r="G35" s="0">
-        <v>189634335.82070753</v>
+        <v>71470926.714164227</v>
       </c>
     </row>
     <row r="36">
@@ -3765,13 +3765,13 @@
         <v>39</v>
       </c>
       <c r="E36" s="0">
-        <v>187809942.191782</v>
+        <v>65356747.643569112</v>
       </c>
       <c r="F36" s="0">
-        <v>-11251268.259423256</v>
+        <v>-13770933.893878818</v>
       </c>
       <c r="G36" s="0">
-        <v>188146659.34723902</v>
+        <v>66791789.037686042</v>
       </c>
     </row>
     <row r="37">
@@ -3788,13 +3788,13 @@
         <v>66</v>
       </c>
       <c r="E37" s="0">
-        <v>182991767.60919809</v>
+        <v>62326159.346817374</v>
       </c>
       <c r="F37" s="0">
-        <v>-1583464.5623426437</v>
+        <v>-3552431.3494764567</v>
       </c>
       <c r="G37" s="0">
-        <v>182998618.49959129</v>
+        <v>62427316.996789262</v>
       </c>
     </row>
     <row r="38">
@@ -3811,13 +3811,13 @@
         <v>108</v>
       </c>
       <c r="E38" s="0">
-        <v>163390398.17667091</v>
+        <v>51659089.205248713</v>
       </c>
       <c r="F38" s="0">
-        <v>-33619982.512896776</v>
+        <v>-9929859.8926916122</v>
       </c>
       <c r="G38" s="0">
-        <v>166813445.02317116</v>
+        <v>52604786.997043617</v>
       </c>
     </row>
     <row r="39">
@@ -3834,13 +3834,13 @@
         <v>72</v>
       </c>
       <c r="E39" s="0">
-        <v>178539975.24762344</v>
+        <v>59625523.179734945</v>
       </c>
       <c r="F39" s="0">
-        <v>2107764.4318883419</v>
+        <v>1699665.5572100282</v>
       </c>
       <c r="G39" s="0">
-        <v>178552416.48413029</v>
+        <v>59649743.314313397</v>
       </c>
     </row>
     <row r="40">
@@ -3857,13 +3857,13 @@
         <v>107</v>
       </c>
       <c r="E40" s="0">
-        <v>166119034.15315545</v>
+        <v>52787001.783895344</v>
       </c>
       <c r="F40" s="0">
-        <v>-25480119.01708746</v>
+        <v>-7088323.8460219801</v>
       </c>
       <c r="G40" s="0">
-        <v>168061804.02786997</v>
+        <v>53260791.322313771</v>
       </c>
     </row>
     <row r="41">
@@ -3880,13 +3880,13 @@
         <v>133</v>
       </c>
       <c r="E41" s="0">
-        <v>149517364.52191013</v>
+        <v>46924206.419529468</v>
       </c>
       <c r="F41" s="0">
-        <v>-30391963.646753043</v>
+        <v>-9499179.9562337082</v>
       </c>
       <c r="G41" s="0">
-        <v>152574944.69238162</v>
+        <v>47876043.779154547</v>
       </c>
     </row>
     <row r="42">
@@ -3903,13 +3903,13 @@
         <v>88</v>
       </c>
       <c r="E42" s="0">
-        <v>166536774.83307791</v>
+        <v>54581242.925873756</v>
       </c>
       <c r="F42" s="0">
-        <v>-1394589.6755223274</v>
+        <v>2331019.8902010918</v>
       </c>
       <c r="G42" s="0">
-        <v>166542613.92258248</v>
+        <v>54630996.083375208</v>
       </c>
     </row>
     <row r="43">
@@ -3926,13 +3926,13 @@
         <v>91</v>
       </c>
       <c r="E43" s="0">
-        <v>189590246.21322036</v>
+        <v>61106487.945603401</v>
       </c>
       <c r="F43" s="0">
-        <v>-7421136.2444033623</v>
+        <v>-2192731.8041991889</v>
       </c>
       <c r="G43" s="0">
-        <v>189735433.49186918</v>
+        <v>61145817.042634405</v>
       </c>
     </row>
     <row r="44">
@@ -3949,13 +3949,13 @@
         <v>95</v>
       </c>
       <c r="E44" s="0">
-        <v>162742883.1190337</v>
+        <v>52221409.986713529</v>
       </c>
       <c r="F44" s="0">
-        <v>2399302.0385220051</v>
+        <v>4690852.8293614984</v>
       </c>
       <c r="G44" s="0">
-        <v>162760568.49300915</v>
+        <v>52431667.542308368</v>
       </c>
     </row>
     <row r="45">
@@ -3972,13 +3972,13 @@
         <v>122</v>
       </c>
       <c r="E45" s="0">
-        <v>152758131.84473735</v>
+        <v>48019196.537493095</v>
       </c>
       <c r="F45" s="0">
-        <v>-32560670.896991014</v>
+        <v>-9714031.0005851835</v>
       </c>
       <c r="G45" s="0">
-        <v>156189769.62002447</v>
+        <v>48991893.557880767</v>
       </c>
     </row>
     <row r="46">
@@ -3995,13 +3995,13 @@
         <v>120</v>
       </c>
       <c r="E46" s="0">
-        <v>163602117.30222929</v>
+        <v>51785753.720137134</v>
       </c>
       <c r="F46" s="0">
-        <v>-52055706.636894703</v>
+        <v>-16134818.310660481</v>
       </c>
       <c r="G46" s="0">
-        <v>171684155.87711883</v>
+        <v>54241097.428801365</v>
       </c>
     </row>
     <row r="47">
@@ -4018,13 +4018,13 @@
         <v>94</v>
       </c>
       <c r="E47" s="0">
-        <v>167819833.16302061</v>
+        <v>53741523.276337504</v>
       </c>
       <c r="F47" s="0">
-        <v>-8229613.5335565806</v>
+        <v>-396170.83579987288</v>
       </c>
       <c r="G47" s="0">
-        <v>168021495.47535807</v>
+        <v>53742983.499171913</v>
       </c>
     </row>
     <row r="48">
@@ -4041,13 +4041,13 @@
         <v>114</v>
       </c>
       <c r="E48" s="0">
-        <v>171530261.67248017</v>
+        <v>54500625.251918346</v>
       </c>
       <c r="F48" s="0">
-        <v>-25480119.01708746</v>
+        <v>-7088323.8460219801</v>
       </c>
       <c r="G48" s="0">
-        <v>173412419.20506865</v>
+        <v>54959644.174577072</v>
       </c>
     </row>
     <row r="49">
@@ -4064,13 +4064,13 @@
         <v>91</v>
       </c>
       <c r="E49" s="0">
-        <v>180636280.4827131</v>
+        <v>58674574.93818289</v>
       </c>
       <c r="F49" s="0">
-        <v>-8497181.6905038357</v>
+        <v>-2150415.4289316535</v>
       </c>
       <c r="G49" s="0">
-        <v>180836024.95993665</v>
+        <v>58713967.935180694</v>
       </c>
     </row>
     <row r="50">
@@ -4087,13 +4087,13 @@
         <v>130</v>
       </c>
       <c r="E50" s="0">
-        <v>151778767.27336663</v>
+        <v>47234898.083202466</v>
       </c>
       <c r="F50" s="0">
-        <v>-31186734.174673229</v>
+        <v>-9473675.4970630407</v>
       </c>
       <c r="G50" s="0">
-        <v>154949690.49179968</v>
+        <v>48175576.01476267</v>
       </c>
     </row>
     <row r="51">
@@ -4110,13 +4110,13 @@
         <v>105</v>
       </c>
       <c r="E51" s="0">
-        <v>184846267.27089071</v>
+        <v>59182079.399556816</v>
       </c>
       <c r="F51" s="0">
-        <v>-28438338.237351656</v>
+        <v>-8605442.7391520441</v>
       </c>
       <c r="G51" s="0">
-        <v>187021072.62467399</v>
+        <v>59804449.389592007</v>
       </c>
     </row>
     <row r="52">
@@ -4133,13 +4133,13 @@
         <v>85</v>
       </c>
       <c r="E52" s="0">
-        <v>179851786.02487302</v>
+        <v>58935376.782386959</v>
       </c>
       <c r="F52" s="0">
-        <v>-1886503.6223144531</v>
+        <v>206446.65181416273</v>
       </c>
       <c r="G52" s="0">
-        <v>179861679.72153968</v>
+        <v>58935738.36562974</v>
       </c>
     </row>
     <row r="53">
@@ -4156,13 +4156,13 @@
         <v>91</v>
       </c>
       <c r="E53" s="0">
-        <v>184714835.20854652</v>
+        <v>59933350.779820561</v>
       </c>
       <c r="F53" s="0">
-        <v>-4418626.9646704197</v>
+        <v>-891639.58729398251</v>
       </c>
       <c r="G53" s="0">
-        <v>184767677.39616528</v>
+        <v>59939982.95670969</v>
       </c>
     </row>
     <row r="54">
@@ -4179,13 +4179,13 @@
         <v>63</v>
       </c>
       <c r="E54" s="0">
-        <v>180221729.59818411</v>
+        <v>58550395.664296389</v>
       </c>
       <c r="F54" s="0">
-        <v>-655842.72269511223</v>
+        <v>-533303.1406263113</v>
       </c>
       <c r="G54" s="0">
-        <v>180222922.92890465</v>
+        <v>58552824.395459011</v>
       </c>
     </row>
     <row r="55">
@@ -4202,13 +4202,13 @@
         <v>79</v>
       </c>
       <c r="E55" s="0">
-        <v>176535168.22467852</v>
+        <v>58098092.387482345</v>
       </c>
       <c r="F55" s="0">
-        <v>-5203121.4225091934</v>
+        <v>-630837.74309039116</v>
       </c>
       <c r="G55" s="0">
-        <v>176611828.85824189</v>
+        <v>58101517.151641928</v>
       </c>
     </row>
     <row r="56">
@@ -4225,13 +4225,13 @@
         <v>92</v>
       </c>
       <c r="E56" s="0">
-        <v>182529680.13401163</v>
+        <v>58820020.375882685</v>
       </c>
       <c r="F56" s="0">
-        <v>-15557747.769712567</v>
+        <v>-4436882.9986523688</v>
       </c>
       <c r="G56" s="0">
-        <v>183191505.38573179</v>
+        <v>58987123.40640951</v>
       </c>
     </row>
     <row r="57">
@@ -4248,13 +4248,13 @@
         <v>106</v>
       </c>
       <c r="E57" s="0">
-        <v>184846267.27089071</v>
+        <v>59182079.399556816</v>
       </c>
       <c r="F57" s="0">
-        <v>-17874334.906591177</v>
+        <v>-4798942.0223261118</v>
       </c>
       <c r="G57" s="0">
-        <v>185708466.07609075</v>
+        <v>59376328.335365221</v>
       </c>
     </row>
     <row r="58">
@@ -4271,13 +4271,13 @@
         <v>112</v>
       </c>
       <c r="E58" s="0">
-        <v>208315251.35864714</v>
+        <v>66218123.932504065</v>
       </c>
       <c r="F58" s="0">
-        <v>-52181588.621753991</v>
+        <v>-16229887.48654598</v>
       </c>
       <c r="G58" s="0">
-        <v>214751396.12981868</v>
+        <v>68178069.677620009</v>
       </c>
     </row>
     <row r="59">
@@ -4294,13 +4294,13 @@
         <v>77</v>
       </c>
       <c r="E59" s="0">
-        <v>182178906.75446248</v>
+        <v>59486614.673796296</v>
       </c>
       <c r="F59" s="0">
-        <v>-1882698.5105862618</v>
+        <v>-444903.48126977682</v>
       </c>
       <c r="G59" s="0">
-        <v>182188634.71669385</v>
+        <v>59488278.378655091</v>
       </c>
     </row>
     <row r="60">
@@ -4317,13 +4317,13 @@
         <v>127</v>
       </c>
       <c r="E60" s="0">
-        <v>139778260.76844648</v>
+        <v>44238488.104259804</v>
       </c>
       <c r="F60" s="0">
-        <v>-49510516.087928563</v>
+        <v>-15571086.162154838</v>
       </c>
       <c r="G60" s="0">
-        <v>148287738.49089769</v>
+        <v>46898854.506480076</v>
       </c>
     </row>
     <row r="61">
@@ -4340,13 +4340,13 @@
         <v>35</v>
       </c>
       <c r="E61" s="0">
-        <v>164751862.29065085</v>
+        <v>39586385.001958966</v>
       </c>
       <c r="F61" s="0">
-        <v>-5986173.3399376869</v>
+        <v>-6676938.3028728962</v>
       </c>
       <c r="G61" s="0">
-        <v>164860578.67026115</v>
+        <v>40145527.554432422</v>
       </c>
     </row>
     <row r="62">
@@ -4363,13 +4363,13 @@
         <v>36</v>
       </c>
       <c r="E62" s="0">
-        <v>171855524.54435682</v>
+        <v>47674814.214309931</v>
       </c>
       <c r="F62" s="0">
-        <v>-9848970.1255707741</v>
+        <v>-11351666.461169004</v>
       </c>
       <c r="G62" s="0">
-        <v>172137513.42734802</v>
+        <v>49007634.525802173</v>
       </c>
     </row>
     <row r="63">
@@ -4386,13 +4386,13 @@
         <v>18</v>
       </c>
       <c r="E63" s="0">
-        <v>169685650.75346756</v>
+        <v>45519523.206668258</v>
       </c>
       <c r="F63" s="0">
-        <v>-41826241.922148228</v>
+        <v>-47678464.580815315</v>
       </c>
       <c r="G63" s="0">
-        <v>174764569.02060506</v>
+        <v>65918608.736429431</v>
       </c>
     </row>
     <row r="64">
@@ -4409,13 +4409,13 @@
         <v>29</v>
       </c>
       <c r="E64" s="0">
-        <v>165877365.96982432</v>
+        <v>40788245.6746912</v>
       </c>
       <c r="F64" s="0">
-        <v>-14785049.201622963</v>
+        <v>-16962728.851288915</v>
       </c>
       <c r="G64" s="0">
-        <v>166534975.96895805</v>
+        <v>44174824.90402554</v>
       </c>
     </row>
     <row r="65">
@@ -4432,13 +4432,13 @@
         <v>18</v>
       </c>
       <c r="E65" s="0">
-        <v>178282832.58726883</v>
+        <v>55461278.987528563</v>
       </c>
       <c r="F65" s="0">
-        <v>-33229060.088346958</v>
+        <v>-37736708.79995501</v>
       </c>
       <c r="G65" s="0">
-        <v>181353077.80596143</v>
+        <v>67082133.671977662</v>
       </c>
     </row>
     <row r="66">
@@ -4455,13 +4455,13 @@
         <v>36</v>
       </c>
       <c r="E66" s="0">
-        <v>171634702.59694052</v>
+        <v>47746661.868396521</v>
       </c>
       <c r="F66" s="0">
-        <v>-3818590.1622834206</v>
+        <v>-4199571.4806418419</v>
       </c>
       <c r="G66" s="0">
-        <v>171677176.02048242</v>
+        <v>47930993.315348797</v>
       </c>
     </row>
     <row r="67">
@@ -4478,13 +4478,13 @@
         <v>43</v>
       </c>
       <c r="E67" s="0">
-        <v>175940471.55198598</v>
+        <v>52983247.069606185</v>
       </c>
       <c r="F67" s="0">
-        <v>-2503467.3276348114</v>
+        <v>-2730386.5443221331</v>
       </c>
       <c r="G67" s="0">
-        <v>175958281.64254084</v>
+        <v>53053552.950960294</v>
       </c>
     </row>
     <row r="68">
@@ -4501,13 +4501,13 @@
         <v>63</v>
       </c>
       <c r="E68" s="0">
-        <v>179887453.15298963</v>
+        <v>58069522.85255301</v>
       </c>
       <c r="F68" s="0">
-        <v>-990119.16788983345</v>
+        <v>-1014175.9523698092</v>
       </c>
       <c r="G68" s="0">
-        <v>179890177.99156144</v>
+        <v>58078378.3966593</v>
       </c>
     </row>
     <row r="69">
@@ -4524,13 +4524,13 @@
         <v>43</v>
       </c>
       <c r="E69" s="0">
-        <v>172949825.4315896</v>
+        <v>49215846.804716349</v>
       </c>
       <c r="F69" s="0">
-        <v>-2503467.3276348114</v>
+        <v>-2730386.5443221331</v>
       </c>
       <c r="G69" s="0">
-        <v>172967943.4620122</v>
+        <v>49291526.527251355</v>
       </c>
     </row>
     <row r="70">
@@ -4547,13 +4547,13 @@
         <v>6</v>
       </c>
       <c r="E70" s="0">
-        <v>180680347.70720077</v>
+        <v>59220560.243357658</v>
       </c>
       <c r="F70" s="0">
-        <v>-631415.4334359169</v>
+        <v>-272583.64532876015</v>
       </c>
       <c r="G70" s="0">
-        <v>180681450.99330077</v>
+        <v>59221187.57151746</v>
       </c>
     </row>
     <row r="71">
@@ -4570,13 +4570,13 @@
         <v>79</v>
       </c>
       <c r="E71" s="0">
-        <v>178539975.24762344</v>
+        <v>59625523.179734945</v>
       </c>
       <c r="F71" s="0">
-        <v>-1886503.6223144531</v>
+        <v>206446.65181416273</v>
       </c>
       <c r="G71" s="0">
-        <v>178549941.63353568</v>
+        <v>59625880.577792346</v>
       </c>
     </row>
     <row r="72">
@@ -4593,13 +4593,13 @@
         <v>71</v>
       </c>
       <c r="E72" s="0">
-        <v>180056788.63764024</v>
+        <v>59482225.130085588</v>
       </c>
       <c r="F72" s="0">
-        <v>-2091506.235080719</v>
+        <v>-340401.69588464499</v>
       </c>
       <c r="G72" s="0">
-        <v>180068935.50202164</v>
+        <v>59483199.138418458</v>
       </c>
     </row>
     <row r="73">
@@ -4616,13 +4616,13 @@
         <v>65</v>
       </c>
       <c r="E73" s="0">
-        <v>181208746.87242937</v>
+        <v>59968633.132714748</v>
       </c>
       <c r="F73" s="0">
-        <v>-2429312.5986051559</v>
+        <v>-3573053.0864830017</v>
       </c>
       <c r="G73" s="0">
-        <v>181225030.01180029</v>
+        <v>60074983.713397361</v>
       </c>
     </row>
     <row r="74">
@@ -4639,13 +4639,13 @@
         <v>64</v>
       </c>
       <c r="E74" s="0">
-        <v>180655409.17809486</v>
+        <v>58954384.137898207</v>
       </c>
       <c r="F74" s="0">
-        <v>-655842.72269511223</v>
+        <v>-533303.1406263113</v>
       </c>
       <c r="G74" s="0">
-        <v>180656599.64413643</v>
+        <v>58956796.226717286</v>
       </c>
     </row>
     <row r="75">
@@ -4662,13 +4662,13 @@
         <v>64</v>
       </c>
       <c r="E75" s="0">
-        <v>180221729.59818411</v>
+        <v>58550395.664296389</v>
       </c>
       <c r="F75" s="0">
-        <v>-2101227.7262423039</v>
+        <v>-2619032.8132790327</v>
       </c>
       <c r="G75" s="0">
-        <v>180233978.42060336</v>
+        <v>58608942.707770206</v>
       </c>
     </row>
     <row r="76">
@@ -4685,13 +4685,13 @@
         <v>38</v>
       </c>
       <c r="E76" s="0">
-        <v>181443017.76001835</v>
+        <v>58581603.572150111</v>
       </c>
       <c r="F76" s="0">
-        <v>-9357443.9104499817</v>
+        <v>-11230130.179355502</v>
       </c>
       <c r="G76" s="0">
-        <v>181684150.2454178</v>
+        <v>59648303.420380883</v>
       </c>
     </row>
     <row r="77">
@@ -4708,13 +4708,13 @@
         <v>57</v>
       </c>
       <c r="E77" s="0">
-        <v>180880662.00006652</v>
+        <v>59014612.859510541</v>
       </c>
       <c r="F77" s="0">
-        <v>-2101227.7262420654</v>
+        <v>-2619032.8132790327</v>
       </c>
       <c r="G77" s="0">
-        <v>180892866.20411497</v>
+        <v>59072699.818401217</v>
       </c>
     </row>
     <row r="78">
@@ -4731,13 +4731,13 @@
         <v>50</v>
       </c>
       <c r="E78" s="0">
-        <v>176841645.61648583</v>
+        <v>53985532.77395618</v>
       </c>
       <c r="F78" s="0">
-        <v>-1602293.2631349564</v>
+        <v>-1728100.8399721384</v>
       </c>
       <c r="G78" s="0">
-        <v>176848904.34505907</v>
+        <v>54013184.329393223</v>
       </c>
     </row>
     <row r="79">
@@ -4754,13 +4754,13 @@
         <v>50</v>
       </c>
       <c r="E79" s="0">
-        <v>179110621.03983045</v>
+        <v>56945538.803386808</v>
       </c>
       <c r="F79" s="0">
-        <v>-3871268.686478138</v>
+        <v>-4688106.8694027662</v>
       </c>
       <c r="G79" s="0">
-        <v>179152452.6500172</v>
+        <v>57138189.817555249</v>
       </c>
     </row>
     <row r="80">
@@ -4777,13 +4777,13 @@
         <v>37</v>
       </c>
       <c r="E80" s="0">
-        <v>176403508.04462719</v>
+        <v>53067440.75232327</v>
       </c>
       <c r="F80" s="0">
-        <v>-14396953.625841618</v>
+        <v>-16744292.999182343</v>
       </c>
       <c r="G80" s="0">
-        <v>176990027.75341746</v>
+        <v>55646425.006857425</v>
       </c>
     </row>
     <row r="81">
@@ -4800,13 +4800,13 @@
         <v>64</v>
       </c>
       <c r="E81" s="0">
-        <v>181208746.87242937</v>
+        <v>59968633.132714748</v>
       </c>
       <c r="F81" s="0">
-        <v>-1114210.4519970417</v>
+        <v>-1200795.344860673</v>
       </c>
       <c r="G81" s="0">
-        <v>181212172.35055575</v>
+        <v>59980654.125029117</v>
       </c>
     </row>
     <row r="82">
@@ -4823,13 +4823,13 @@
         <v>58</v>
       </c>
       <c r="E82" s="0">
-        <v>183837615.64546156</v>
+        <v>62346781.083824992</v>
       </c>
       <c r="F82" s="0">
-        <v>-2429312.5986053944</v>
+        <v>-3573053.0864830017</v>
       </c>
       <c r="G82" s="0">
-        <v>183853665.95722315</v>
+        <v>62449081.817695476</v>
       </c>
     </row>
     <row r="83">
@@ -4846,13 +4846,13 @@
         <v>66</v>
       </c>
       <c r="E83" s="0">
-        <v>180740828.28227067</v>
+        <v>59983364.660234928</v>
       </c>
       <c r="F83" s="0">
-        <v>-646291.86183643341</v>
+        <v>-1215526.8723803759</v>
       </c>
       <c r="G83" s="0">
-        <v>180741983.78166577</v>
+        <v>59995679.357268713</v>
       </c>
     </row>
     <row r="84">
@@ -4869,13 +4869,13 @@
         <v>76</v>
       </c>
       <c r="E84" s="0">
-        <v>181454445.04337955</v>
+        <v>59347865.416679978</v>
       </c>
       <c r="F84" s="0">
-        <v>-647284.42882755771</v>
+        <v>-275193.40138191357</v>
       </c>
       <c r="G84" s="0">
-        <v>181455599.53645039</v>
+        <v>59348503.44300624</v>
       </c>
     </row>
     <row r="85">
@@ -4892,13 +4892,13 @@
         <v>66</v>
       </c>
       <c r="E85" s="0">
-        <v>182991767.60919809</v>
+        <v>62326159.346817374</v>
       </c>
       <c r="F85" s="0">
-        <v>-646291.86183643341</v>
+        <v>-1215526.8723803759</v>
       </c>
       <c r="G85" s="0">
-        <v>182992908.89515209</v>
+        <v>62338011.233134069</v>
       </c>
     </row>
     <row r="86">
@@ -4915,13 +4915,13 @@
         <v>65</v>
       </c>
       <c r="E86" s="0">
-        <v>180680347.70720077</v>
+        <v>59220560.243357658</v>
       </c>
       <c r="F86" s="0">
-        <v>-1114210.4519968033</v>
+        <v>-1200795.344860673</v>
       </c>
       <c r="G86" s="0">
-        <v>180683783.20293802</v>
+        <v>59232733.053586111</v>
       </c>
     </row>
     <row r="87">
@@ -4938,13 +4938,13 @@
         <v>51</v>
       </c>
       <c r="E87" s="0">
-        <v>180880662.00006652</v>
+        <v>59014612.859510541</v>
       </c>
       <c r="F87" s="0">
-        <v>-5386266.2440004349</v>
+        <v>-6905221.3107974529</v>
       </c>
       <c r="G87" s="0">
-        <v>180960840.37612548</v>
+        <v>59417224.87889348</v>
       </c>
     </row>
     <row r="88">
@@ -4961,13 +4961,13 @@
         <v>68</v>
       </c>
       <c r="E88" s="0">
-        <v>190683005.04744053</v>
+        <v>70545514.60235703</v>
       </c>
       <c r="F88" s="0">
-        <v>5434175.3345007897</v>
+        <v>2462662.0232752562</v>
       </c>
       <c r="G88" s="0">
-        <v>190760422.19362047</v>
+        <v>70588485.851109251</v>
       </c>
     </row>
     <row r="89">
@@ -4984,13 +4984,13 @@
         <v>51</v>
       </c>
       <c r="E89" s="0">
-        <v>183336842.10899091</v>
+        <v>61122407.286673546</v>
       </c>
       <c r="F89" s="0">
-        <v>-5386266.2440004349</v>
+        <v>-6905221.3107974529</v>
       </c>
       <c r="G89" s="0">
-        <v>183415946.79456943</v>
+        <v>61511224.616886757</v>
       </c>
     </row>
     <row r="90">
@@ -5007,13 +5007,13 @@
         <v>47</v>
       </c>
       <c r="E90" s="0">
-        <v>195516307.18741036</v>
+        <v>73651884.51787591</v>
       </c>
       <c r="F90" s="0">
-        <v>-5327160.0561163425</v>
+        <v>-8289793.8776416779</v>
       </c>
       <c r="G90" s="0">
-        <v>195588867.29685125</v>
+        <v>74116939.869157538</v>
       </c>
     </row>
     <row r="91">
@@ -5030,13 +5030,13 @@
         <v>36</v>
       </c>
       <c r="E91" s="0">
-        <v>172949825.4315896</v>
+        <v>49215846.804716349</v>
       </c>
       <c r="F91" s="0">
-        <v>-9848970.1255707741</v>
+        <v>-11351666.461169004</v>
       </c>
       <c r="G91" s="0">
-        <v>173230032.98894709</v>
+        <v>50508018.25602483</v>
       </c>
     </row>
     <row r="92">
@@ -5053,13 +5053,13 @@
         <v>37</v>
       </c>
       <c r="E92" s="0">
-        <v>176403508.04462719</v>
+        <v>53067440.75232327</v>
       </c>
       <c r="F92" s="0">
-        <v>-6395287.5125336647</v>
+        <v>-7500072.5135620833</v>
       </c>
       <c r="G92" s="0">
-        <v>176519396.53425857</v>
+        <v>53594816.500385836</v>
       </c>
     </row>
     <row r="93">
@@ -5076,13 +5076,13 @@
         <v>29</v>
       </c>
       <c r="E93" s="0">
-        <v>166919445.46830464</v>
+        <v>42063751.824190021</v>
       </c>
       <c r="F93" s="0">
-        <v>-14785049.201622963</v>
+        <v>-16962728.851288915</v>
       </c>
       <c r="G93" s="0">
-        <v>167572966.06356508</v>
+        <v>45355191.407482766</v>
       </c>
     </row>
     <row r="94">
@@ -5099,13 +5099,13 @@
         <v>24</v>
       </c>
       <c r="E94" s="0">
-        <v>174014434.51774073</v>
+        <v>50097590.145203471</v>
       </c>
       <c r="F94" s="0">
-        <v>-33229060.088346958</v>
+        <v>-37736708.79995501</v>
       </c>
       <c r="G94" s="0">
-        <v>177158668.58520937</v>
+        <v>62720233.811820172</v>
       </c>
     </row>
     <row r="95">
@@ -5122,13 +5122,13 @@
         <v>43</v>
       </c>
       <c r="E95" s="0">
-        <v>176841645.61648583</v>
+        <v>53985532.77395618</v>
       </c>
       <c r="F95" s="0">
-        <v>-6395287.5125336647</v>
+        <v>-7500072.5135620833</v>
       </c>
       <c r="G95" s="0">
-        <v>176957247.17206338</v>
+        <v>54504025.875127666</v>
       </c>
     </row>
     <row r="96">
@@ -5145,13 +5145,13 @@
         <v>44</v>
       </c>
       <c r="E96" s="0">
-        <v>179365664.44254136</v>
+        <v>56797498.418115497</v>
       </c>
       <c r="F96" s="0">
-        <v>-9357443.9104499817</v>
+        <v>-11230130.179355502</v>
       </c>
       <c r="G96" s="0">
-        <v>179609585.87294713</v>
+        <v>57897078.081722774</v>
       </c>
     </row>
     <row r="97">
@@ -5168,13 +5168,13 @@
         <v>15</v>
       </c>
       <c r="E97" s="0">
-        <v>146100663.14040947</v>
+        <v>17776433.904820085</v>
       </c>
       <c r="F97" s="0">
-        <v>-35960117.635006428</v>
+        <v>-41799196.408862949</v>
       </c>
       <c r="G97" s="0">
-        <v>150461070.81365234</v>
+        <v>45422179.855211027</v>
       </c>
     </row>
     <row r="98">
@@ -5191,13 +5191,13 @@
         <v>23</v>
       </c>
       <c r="E98" s="0">
-        <v>158120569.60661602</v>
+        <v>31777961.27577424</v>
       </c>
       <c r="F98" s="0">
-        <v>-22541845.564831734</v>
+        <v>-25973013.250205875</v>
       </c>
       <c r="G98" s="0">
-        <v>159719282.9128325</v>
+        <v>41041883.974057242</v>
       </c>
     </row>
     <row r="99">
@@ -5214,13 +5214,13 @@
         <v>10</v>
       </c>
       <c r="E99" s="0">
-        <v>168630335.18298149</v>
+        <v>46861092.349439621</v>
       </c>
       <c r="F99" s="0">
-        <v>-49581331.586598873</v>
+        <v>-57665889.167347312</v>
       </c>
       <c r="G99" s="0">
-        <v>175768308.82108682</v>
+        <v>74305563.382855073</v>
       </c>
     </row>
     <row r="100">
@@ -5237,13 +5237,13 @@
         <v>9</v>
       </c>
       <c r="E100" s="0">
-        <v>160811166.86329651</v>
+        <v>36687312.954514503</v>
       </c>
       <c r="F100" s="0">
-        <v>-51394191.817601204</v>
+        <v>-60024661.777167797</v>
       </c>
       <c r="G100" s="0">
-        <v>168824152.1243906</v>
+        <v>70348553.313382894</v>
       </c>
     </row>
     <row r="101">
@@ -5260,13 +5260,13 @@
         <v>16</v>
       </c>
       <c r="E101" s="0">
-        <v>159518935.21058369</v>
+        <v>33602617.063477159</v>
       </c>
       <c r="F101" s="0">
-        <v>-22541845.564831734</v>
+        <v>-25973013.250205875</v>
       </c>
       <c r="G101" s="0">
-        <v>161103772.43313429</v>
+        <v>42470381.33582104</v>
       </c>
     </row>
     <row r="102">
@@ -5283,13 +5283,13 @@
         <v>39</v>
       </c>
       <c r="E102" s="0">
-        <v>185574137.95657063</v>
+        <v>62765266.49247551</v>
       </c>
       <c r="F102" s="0">
-        <v>-28271747.256655216</v>
+        <v>-31994019.25079298</v>
       </c>
       <c r="G102" s="0">
-        <v>187715349.3225008</v>
+        <v>70449243.755285129</v>
       </c>
     </row>
     <row r="103">
@@ -5306,13 +5306,13 @@
         <v>10</v>
       </c>
       <c r="E103" s="0">
-        <v>166926400.69827557</v>
+        <v>42916606.630465388</v>
       </c>
       <c r="F103" s="0">
-        <v>-39066991.866956711</v>
+        <v>-45075548.004610777</v>
       </c>
       <c r="G103" s="0">
-        <v>171437023.72478971</v>
+        <v>62238574.47427661</v>
       </c>
     </row>
     <row r="104">
@@ -5329,13 +5329,13 @@
         <v>17</v>
       </c>
       <c r="E104" s="0">
-        <v>159518935.21058369</v>
+        <v>33602617.063477159</v>
       </c>
       <c r="F104" s="0">
-        <v>-39066991.866956711</v>
+        <v>-45075548.004610896</v>
       </c>
       <c r="G104" s="0">
-        <v>164233128.64416623</v>
+        <v>56222245.609995581</v>
       </c>
     </row>
     <row r="105">
@@ -5352,13 +5352,13 @@
         <v>11</v>
       </c>
       <c r="E105" s="0">
-        <v>169798686.47514725</v>
+        <v>49565741.517618656</v>
       </c>
       <c r="F105" s="0">
-        <v>-49228692.733890057</v>
+        <v>-56849555.598803878</v>
       </c>
       <c r="G105" s="0">
-        <v>176791001.2330184</v>
+        <v>75423038.283888295</v>
       </c>
     </row>
     <row r="106">
@@ -5375,13 +5375,13 @@
         <v>10</v>
       </c>
       <c r="E106" s="0">
-        <v>156412060.97863436</v>
+        <v>30326265.467728973</v>
       </c>
       <c r="F106" s="0">
-        <v>-49581331.586598873</v>
+        <v>-57665889.167347312</v>
       </c>
       <c r="G106" s="0">
-        <v>164082422.15875623</v>
+        <v>65153949.616887808</v>
       </c>
     </row>
     <row r="107">
@@ -5398,13 +5398,13 @@
         <v>17</v>
       </c>
       <c r="E107" s="0">
-        <v>169685650.75346756</v>
+        <v>45519523.206668258</v>
       </c>
       <c r="F107" s="0">
-        <v>-28900276.324073315</v>
+        <v>-33158641.861419797</v>
       </c>
       <c r="G107" s="0">
-        <v>172129155.1226449</v>
+        <v>56316272.275926709</v>
       </c>
     </row>
     <row r="108">
@@ -5421,13 +5421,13 @@
         <v>24</v>
       </c>
       <c r="E108" s="0">
-        <v>165877365.96982432</v>
+        <v>40788245.6746912</v>
       </c>
       <c r="F108" s="0">
-        <v>-28900276.324073315</v>
+        <v>-33158641.861419797</v>
       </c>
       <c r="G108" s="0">
-        <v>168376145.91353142</v>
+        <v>52565925.420493335</v>
       </c>
     </row>
     <row r="109">
@@ -5444,13 +5444,13 @@
         <v>24</v>
       </c>
       <c r="E109" s="0">
-        <v>174014434.51774073</v>
+        <v>50097590.14520359</v>
       </c>
       <c r="F109" s="0">
-        <v>-20763207.776156902</v>
+        <v>-23849297.390907407</v>
       </c>
       <c r="G109" s="0">
-        <v>175248778.07758015</v>
+        <v>55484750.376988657</v>
       </c>
     </row>
     <row r="110">
@@ -5467,13 +5467,13 @@
         <v>31</v>
       </c>
       <c r="E110" s="0">
-        <v>171855524.54435682</v>
+        <v>47674814.214309931</v>
       </c>
       <c r="F110" s="0">
-        <v>-20763207.776156902</v>
+        <v>-23849297.390907407</v>
       </c>
       <c r="G110" s="0">
-        <v>173105263.10188231</v>
+        <v>53307381.256341145</v>
       </c>
     </row>
     <row r="111">
@@ -5490,13 +5490,13 @@
         <v>26</v>
       </c>
       <c r="E111" s="0">
-        <v>191220365.55042839</v>
+        <v>68886956.748473883</v>
       </c>
       <c r="F111" s="0">
-        <v>-28271747.256655216</v>
+        <v>-31994019.250792861</v>
       </c>
       <c r="G111" s="0">
-        <v>193299042.66235685</v>
+        <v>75954131.407621369</v>
       </c>
     </row>
     <row r="112">
@@ -5513,13 +5513,13 @@
         <v>34</v>
       </c>
       <c r="E112" s="0">
-        <v>203651507.17772102</v>
+        <v>81518308.829511762</v>
       </c>
       <c r="F112" s="0">
-        <v>-21383651.102162838</v>
+        <v>-24832206.926560402</v>
       </c>
       <c r="G112" s="0">
-        <v>204771084.16526097</v>
+        <v>85216624.993408233</v>
       </c>
     </row>
     <row r="113">
@@ -5536,13 +5536,13 @@
         <v>25</v>
       </c>
       <c r="E113" s="0">
-        <v>182272942.65300179</v>
+        <v>59302773.093420148</v>
       </c>
       <c r="F113" s="0">
-        <v>-37219170.154081822</v>
+        <v>-41578202.905846596</v>
       </c>
       <c r="G113" s="0">
-        <v>186034115.82379985</v>
+        <v>72426278.749148965</v>
       </c>
     </row>
     <row r="114">
@@ -5559,13 +5559,13 @@
         <v>26</v>
       </c>
       <c r="E114" s="0">
-        <v>198296471.85164785</v>
+        <v>76505786.618697047</v>
       </c>
       <c r="F114" s="0">
-        <v>-41595650.271922588</v>
+        <v>-45530037.652749062</v>
       </c>
       <c r="G114" s="0">
-        <v>202612163.6781846</v>
+        <v>89028757.796603858</v>
       </c>
     </row>
     <row r="115">
@@ -5582,13 +5582,13 @@
         <v>1</v>
       </c>
       <c r="E115" s="0">
-        <v>286524793.46852589</v>
+        <v>195707644.75732231</v>
       </c>
       <c r="F115" s="0">
-        <v>-62200874.418279529</v>
+        <v>-56942877.566736996</v>
       </c>
       <c r="G115" s="0">
-        <v>293198577.84542543</v>
+        <v>203823388.06436974</v>
       </c>
     </row>
     <row r="116">
@@ -5605,13 +5605,13 @@
         <v>11</v>
       </c>
       <c r="E116" s="0">
-        <v>166926400.69827604</v>
+        <v>42916606.630465508</v>
       </c>
       <c r="F116" s="0">
-        <v>-49228692.733890057</v>
+        <v>-56849555.598803878</v>
       </c>
       <c r="G116" s="0">
-        <v>174034155.95327595</v>
+        <v>71229959.261925802</v>
       </c>
     </row>
     <row r="117">
@@ -5628,13 +5628,13 @@
         <v>11</v>
       </c>
       <c r="E117" s="0">
-        <v>165638339.41834736</v>
+        <v>47249664.137313843</v>
       </c>
       <c r="F117" s="0">
-        <v>-51027243.230381489</v>
+        <v>-57850813.92302227</v>
       </c>
       <c r="G117" s="0">
-        <v>173320047.9949165</v>
+        <v>74694360.112695992</v>
       </c>
     </row>
     <row r="118">
@@ -5651,13 +5651,13 @@
         <v>41</v>
       </c>
       <c r="E118" s="0">
-        <v>207188853.62743658</v>
+        <v>84999257.446499735</v>
       </c>
       <c r="F118" s="0">
-        <v>-20023911.399464131</v>
+        <v>-23778332.563171864</v>
       </c>
       <c r="G118" s="0">
-        <v>208154217.09680766</v>
+        <v>88262579.080497876</v>
       </c>
     </row>
     <row r="119">
@@ -5674,13 +5674,13 @@
         <v>13</v>
       </c>
       <c r="E119" s="0">
-        <v>189115346.88749743</v>
+        <v>69288707.644488096</v>
       </c>
       <c r="F119" s="0">
-        <v>-53048236.690983772</v>
+        <v>-57100702.269874692</v>
       </c>
       <c r="G119" s="0">
-        <v>196414688.46397695</v>
+        <v>89785384.148848057</v>
       </c>
     </row>
     <row r="120">
@@ -5697,13 +5697,13 @@
         <v>20</v>
       </c>
       <c r="E120" s="0">
-        <v>198296471.85164785</v>
+        <v>76505786.618697047</v>
       </c>
       <c r="F120" s="0">
-        <v>-61442864.410543442</v>
+        <v>-63699533.18087101</v>
       </c>
       <c r="G120" s="0">
-        <v>207597486.34264287</v>
+        <v>99552829.761923358</v>
       </c>
     </row>
     <row r="121">
@@ -5720,13 +5720,13 @@
         <v>27</v>
       </c>
       <c r="E121" s="0">
-        <v>201772745.82929611</v>
+        <v>79688205.272027969</v>
       </c>
       <c r="F121" s="0">
-        <v>-31043269.993054867</v>
+        <v>-34728789.129194975</v>
       </c>
       <c r="G121" s="0">
-        <v>204146823.56420693</v>
+        <v>86926974.259184688</v>
       </c>
     </row>
     <row r="122">
@@ -5743,13 +5743,13 @@
         <v>34</v>
       </c>
       <c r="E122" s="0">
-        <v>203651507.17772102</v>
+        <v>81518308.829511762</v>
       </c>
       <c r="F122" s="0">
-        <v>-41769748.699092865</v>
+        <v>-45177464.186105728</v>
       </c>
       <c r="G122" s="0">
-        <v>207890952.86265519</v>
+        <v>93199988.973768234</v>
       </c>
     </row>
     <row r="123">
@@ -5766,13 +5766,13 @@
         <v>12</v>
       </c>
       <c r="E123" s="0">
-        <v>179575871.7409997</v>
+        <v>58886465.65158689</v>
       </c>
       <c r="F123" s="0">
-        <v>-62587711.837481499</v>
+        <v>-67502944.262775898</v>
       </c>
       <c r="G123" s="0">
-        <v>190170227.38744253</v>
+        <v>89578252.500698805</v>
       </c>
     </row>
     <row r="124">
@@ -5789,13 +5789,13 @@
         <v>13</v>
       </c>
       <c r="E124" s="0">
-        <v>189115346.88749743</v>
+        <v>69288707.644488096</v>
       </c>
       <c r="F124" s="0">
-        <v>-76568767.788982391</v>
+        <v>-75589670.790879965</v>
       </c>
       <c r="G124" s="0">
-        <v>204027916.29848498</v>
+        <v>102541325.02224143</v>
       </c>
     </row>
     <row r="125">
@@ -5812,13 +5812,13 @@
         <v>12</v>
       </c>
       <c r="E125" s="0">
-        <v>179575871.7409997</v>
+        <v>58886465.65158689</v>
       </c>
       <c r="F125" s="0">
-        <v>-45780222.999399662</v>
+        <v>-51052045.91988945</v>
       </c>
       <c r="G125" s="0">
-        <v>185319514.70208079</v>
+        <v>77935404.211064592</v>
       </c>
     </row>
     <row r="126">
@@ -5835,13 +5835,13 @@
         <v>19</v>
       </c>
       <c r="E126" s="0">
-        <v>178282832.58726883</v>
+        <v>55461278.987528563</v>
       </c>
       <c r="F126" s="0">
-        <v>-45780222.999399662</v>
+        <v>-51052045.91988945</v>
       </c>
       <c r="G126" s="0">
-        <v>184066828.11743915</v>
+        <v>75380799.011014596</v>
       </c>
     </row>
     <row r="127">
@@ -5858,13 +5858,13 @@
         <v>41</v>
       </c>
       <c r="E127" s="0">
-        <v>195521542.46259642</v>
+        <v>73316374.437046528</v>
       </c>
       <c r="F127" s="0">
-        <v>-21383651.102162838</v>
+        <v>-24832206.926560402</v>
       </c>
       <c r="G127" s="0">
-        <v>196687401.98958328</v>
+        <v>77407552.9999284</v>
       </c>
     </row>
     <row r="128">
@@ -5881,13 +5881,13 @@
         <v>52</v>
       </c>
       <c r="E128" s="0">
-        <v>183336842.10899091</v>
+        <v>61122407.286673546</v>
       </c>
       <c r="F128" s="0">
-        <v>-11251268.259423256</v>
+        <v>-13770933.893878818</v>
       </c>
       <c r="G128" s="0">
-        <v>183681759.33375248</v>
+        <v>62654507.362420336</v>
       </c>
     </row>
     <row r="129">
@@ -5904,13 +5904,13 @@
         <v>55</v>
       </c>
       <c r="E129" s="0">
-        <v>194122799.21385932</v>
+        <v>72858069.176807881</v>
       </c>
       <c r="F129" s="0">
-        <v>-3933652.0825669766</v>
+        <v>-7495978.5365737677</v>
       </c>
       <c r="G129" s="0">
-        <v>194162650.35616666</v>
+        <v>73242664.741210073</v>
       </c>
     </row>
     <row r="130">
@@ -5927,13 +5927,13 @@
         <v>47</v>
       </c>
       <c r="E130" s="0">
-        <v>204768032.18436432</v>
+        <v>82635138.959863782</v>
       </c>
       <c r="F130" s="0">
-        <v>-12137161.380395412</v>
+        <v>-15513442.403743267</v>
       </c>
       <c r="G130" s="0">
-        <v>205127418.18448022</v>
+        <v>84078731.473127365</v>
       </c>
     </row>
     <row r="131">
@@ -5950,13 +5950,13 @@
         <v>55</v>
       </c>
       <c r="E131" s="0">
-        <v>203719816.48523879</v>
+        <v>81669348.385045409</v>
       </c>
       <c r="F131" s="0">
-        <v>4314870.7262077332</v>
+        <v>-355095.16813182831</v>
       </c>
       <c r="G131" s="0">
-        <v>203765506.74283236</v>
+        <v>81670120.351425648</v>
       </c>
     </row>
     <row r="132">
@@ -5973,13 +5973,13 @@
         <v>48</v>
       </c>
       <c r="E132" s="0">
-        <v>204768032.18436432</v>
+        <v>82635138.959863782</v>
       </c>
       <c r="F132" s="0">
-        <v>-1942190.8357925415</v>
+        <v>-6120140.5568647385</v>
       </c>
       <c r="G132" s="0">
-        <v>204777242.65625686</v>
+        <v>82861464.57402125</v>
       </c>
     </row>
     <row r="133">
@@ -5996,13 +5996,13 @@
         <v>3</v>
       </c>
       <c r="E133" s="0">
-        <v>202150693.75699711</v>
+        <v>80310932.744701743</v>
       </c>
       <c r="F133" s="0">
-        <v>11327672.479402065</v>
+        <v>5716003.9324741364</v>
       </c>
       <c r="G133" s="0">
-        <v>202467822.50578937</v>
+        <v>80514089.569963262</v>
       </c>
     </row>
     <row r="134">
@@ -6019,13 +6019,13 @@
         <v>54</v>
       </c>
       <c r="E134" s="0">
-        <v>203719816.48523879</v>
+        <v>81669348.38504529</v>
       </c>
       <c r="F134" s="0">
-        <v>-3933652.0825669766</v>
+        <v>-7495978.5365737677</v>
       </c>
       <c r="G134" s="0">
-        <v>203757790.64243421</v>
+        <v>82012634.147786498</v>
       </c>
     </row>
     <row r="135">
@@ -6042,13 +6042,13 @@
         <v>3</v>
       </c>
       <c r="E135" s="0">
-        <v>198988571.07149911</v>
+        <v>77793311.024660826</v>
       </c>
       <c r="F135" s="0">
-        <v>20716805.263317585</v>
+        <v>13191452.224705458</v>
       </c>
       <c r="G135" s="0">
-        <v>200064083.32680628</v>
+        <v>78903825.331705585</v>
       </c>
     </row>
     <row r="136">
@@ -6065,13 +6065,13 @@
         <v>73</v>
       </c>
       <c r="E136" s="0">
-        <v>181797148.50814509</v>
+        <v>63113113.35233295</v>
       </c>
       <c r="F136" s="0">
-        <v>5434175.3345007897</v>
+        <v>2462662.0232752562</v>
       </c>
       <c r="G136" s="0">
-        <v>181878347.98913985</v>
+        <v>63161141.386657268</v>
       </c>
     </row>
     <row r="137">
@@ -6088,13 +6088,13 @@
         <v>47</v>
       </c>
       <c r="E137" s="0">
-        <v>188701070.58794379</v>
+        <v>66763746.072603822</v>
       </c>
       <c r="F137" s="0">
-        <v>-12142396.655582905</v>
+        <v>-15177932.322913766</v>
       </c>
       <c r="G137" s="0">
-        <v>189091332.00011486</v>
+        <v>68467272.614337951</v>
       </c>
     </row>
     <row r="138">
@@ -6111,13 +6111,13 @@
         <v>61</v>
       </c>
       <c r="E138" s="0">
-        <v>185903278.00709367</v>
+        <v>65727183.035951018</v>
       </c>
       <c r="F138" s="0">
-        <v>654448.29415369034</v>
+        <v>-2355669.5431308746</v>
       </c>
       <c r="G138" s="0">
-        <v>185904429.95354489</v>
+        <v>65769383.217708849</v>
       </c>
     </row>
     <row r="139">
@@ -6134,13 +6134,13 @@
         <v>69</v>
       </c>
       <c r="E139" s="0">
-        <v>198988571.07149911</v>
+        <v>77793311.024660826</v>
       </c>
       <c r="F139" s="0">
-        <v>12399808.484629154</v>
+        <v>7204681.4536236525</v>
       </c>
       <c r="G139" s="0">
-        <v>199374538.66412464</v>
+        <v>78126222.710609823</v>
       </c>
     </row>
     <row r="140">
@@ -6157,13 +6157,13 @@
         <v>53</v>
       </c>
       <c r="E140" s="0">
-        <v>188141190.86358929</v>
+        <v>66923944.842297077</v>
       </c>
       <c r="F140" s="0">
-        <v>-5327160.0561163425</v>
+        <v>-8289793.8776416779</v>
       </c>
       <c r="G140" s="0">
-        <v>188216594.20421201</v>
+        <v>67435414.107044727</v>
       </c>
     </row>
     <row r="141">
@@ -6180,13 +6180,13 @@
         <v>68</v>
       </c>
       <c r="E141" s="0">
-        <v>190683005.04744053</v>
+        <v>70545514.60235703</v>
       </c>
       <c r="F141" s="0">
-        <v>4094242.4605708122</v>
+        <v>-43114.968680024147</v>
       </c>
       <c r="G141" s="0">
-        <v>190726954.66359279</v>
+        <v>70545527.777541593</v>
       </c>
     </row>
     <row r="142">
@@ -6203,13 +6203,13 @@
         <v>61</v>
       </c>
       <c r="E142" s="0">
-        <v>202150693.75699711</v>
+        <v>80310932.744701743</v>
       </c>
       <c r="F142" s="0">
-        <v>4094242.4605708122</v>
+        <v>-43114.968680024147</v>
       </c>
       <c r="G142" s="0">
-        <v>202192150.70759097</v>
+        <v>80310944.31784831</v>
       </c>
     </row>
     <row r="143">
@@ -6226,13 +6226,13 @@
         <v>47</v>
       </c>
       <c r="E143" s="0">
-        <v>195521542.46259642</v>
+        <v>73316374.437046528</v>
       </c>
       <c r="F143" s="0">
-        <v>-12142396.655582905</v>
+        <v>-15177932.322913766</v>
       </c>
       <c r="G143" s="0">
-        <v>195898216.84613264</v>
+        <v>74870958.256136671</v>
       </c>
     </row>
     <row r="144">
@@ -6249,13 +6249,13 @@
         <v>38</v>
       </c>
       <c r="E144" s="0">
-        <v>185574137.95657063</v>
+        <v>62765266.49247551</v>
       </c>
       <c r="F144" s="0">
-        <v>-17618192.691186905</v>
+        <v>-20546077.965297818</v>
       </c>
       <c r="G144" s="0">
-        <v>186408587.22716639</v>
+        <v>66042562.015927017</v>
       </c>
     </row>
     <row r="145">
@@ -6272,13 +6272,13 @@
         <v>25</v>
       </c>
       <c r="E145" s="0">
-        <v>182272942.65300179</v>
+        <v>59302773.093420148</v>
       </c>
       <c r="F145" s="0">
-        <v>-24970551.953085899</v>
+        <v>-28531525.851738334</v>
       </c>
       <c r="G145" s="0">
-        <v>183975417.07583174</v>
+        <v>65809322.014423527</v>
       </c>
     </row>
     <row r="146">
@@ -6295,13 +6295,13 @@
         <v>32</v>
       </c>
       <c r="E146" s="0">
-        <v>178221778.69467211</v>
+        <v>54779818.606034994</v>
       </c>
       <c r="F146" s="0">
-        <v>-24970551.953085899</v>
+        <v>-28531525.851738334</v>
       </c>
       <c r="G146" s="0">
-        <v>179962581.84949014</v>
+        <v>61764686.463532791</v>
       </c>
     </row>
     <row r="147">
@@ -6318,13 +6318,13 @@
         <v>46</v>
       </c>
       <c r="E147" s="0">
-        <v>187809942.191782</v>
+        <v>65356747.643569112</v>
       </c>
       <c r="F147" s="0">
-        <v>-19853996.926397324</v>
+        <v>-23137559.116391182</v>
       </c>
       <c r="G147" s="0">
-        <v>188856441.72236723</v>
+        <v>69331458.259650603</v>
       </c>
     </row>
     <row r="148">
@@ -6341,13 +6341,13 @@
         <v>39</v>
       </c>
       <c r="E148" s="0">
-        <v>193991888.28682947</v>
+        <v>71621726.626877189</v>
       </c>
       <c r="F148" s="0">
-        <v>-19853996.926397324</v>
+        <v>-23137559.116391182</v>
       </c>
       <c r="G148" s="0">
-        <v>195005215.09704071</v>
+        <v>75266316.283445314</v>
       </c>
     </row>
     <row r="149">
@@ -6364,13 +6364,13 @@
         <v>46</v>
       </c>
       <c r="E149" s="0">
-        <v>188701070.58794379</v>
+        <v>66763746.072603822</v>
       </c>
       <c r="F149" s="0">
-        <v>-5887039.7804703713</v>
+        <v>-8129595.1079486609</v>
       </c>
       <c r="G149" s="0">
-        <v>188792879.31066939</v>
+        <v>67256881.478896305</v>
       </c>
     </row>
     <row r="150">
@@ -6387,13 +6387,13 @@
         <v>53</v>
       </c>
       <c r="E150" s="0">
-        <v>183837615.64546156</v>
+        <v>62346781.083824992</v>
       </c>
       <c r="F150" s="0">
-        <v>-5887039.7804703713</v>
+        <v>-8129595.1079486609</v>
       </c>
       <c r="G150" s="0">
-        <v>183931851.95497078</v>
+        <v>62874569.00952547</v>
       </c>
     </row>
     <row r="151">
@@ -6410,13 +6410,13 @@
         <v>61</v>
       </c>
       <c r="E151" s="0">
-        <v>194122799.21385932</v>
+        <v>72858069.176807881</v>
       </c>
       <c r="F151" s="0">
-        <v>654448.29415369034</v>
+        <v>-2355669.5431308746</v>
       </c>
       <c r="G151" s="0">
-        <v>194123902.38503364</v>
+        <v>72896141.346225977</v>
       </c>
     </row>
     <row r="152">
@@ -6433,13 +6433,13 @@
         <v>60</v>
       </c>
       <c r="E152" s="0">
-        <v>188141190.86358929</v>
+        <v>66923944.842297077</v>
       </c>
       <c r="F152" s="0">
-        <v>-1583464.5623426437</v>
+        <v>-3552431.3494764567</v>
       </c>
       <c r="G152" s="0">
-        <v>188147854.2518881</v>
+        <v>67018162.92429661</v>
       </c>
     </row>
     <row r="153">
@@ -6456,13 +6456,13 @@
         <v>80</v>
       </c>
       <c r="E153" s="0">
-        <v>172300091.06279755</v>
+        <v>56821917.773165703</v>
       </c>
       <c r="F153" s="0">
-        <v>-4116773.7612514496</v>
+        <v>457702.82975023985</v>
       </c>
       <c r="G153" s="0">
-        <v>172349265.17525295</v>
+        <v>56823761.150602885</v>
       </c>
     </row>
     <row r="154">
@@ -6479,13 +6479,13 @@
         <v>93</v>
       </c>
       <c r="E154" s="0">
-        <v>175448820.56342018</v>
+        <v>57009551.814641893</v>
       </c>
       <c r="F154" s="0">
-        <v>-10390581.34180212</v>
+        <v>-2295860.8666314483</v>
       </c>
       <c r="G154" s="0">
-        <v>175756231.23438844</v>
+        <v>57055761.980936401</v>
       </c>
     </row>
     <row r="155">
@@ -6502,13 +6502,13 @@
         <v>95</v>
       </c>
       <c r="E155" s="0">
-        <v>162742883.1190337</v>
+        <v>52221409.986713529</v>
       </c>
       <c r="F155" s="0">
-        <v>-8229613.5335565806</v>
+        <v>-396170.83579987288</v>
       </c>
       <c r="G155" s="0">
-        <v>162950828.61037302</v>
+        <v>52222912.713976055</v>
       </c>
     </row>
     <row r="156">
@@ -6525,13 +6525,13 @@
         <v>93</v>
       </c>
       <c r="E156" s="0">
-        <v>175448820.56342018</v>
+        <v>57009551.814641893</v>
       </c>
       <c r="F156" s="0">
-        <v>-4116773.7612514496</v>
+        <v>457702.82975023985</v>
       </c>
       <c r="G156" s="0">
-        <v>175497112.40728873</v>
+        <v>57011389.12521515</v>
       </c>
     </row>
     <row r="157">
@@ -6548,13 +6548,13 @@
         <v>94</v>
       </c>
       <c r="E157" s="0">
-        <v>175045926.56922257</v>
+        <v>56316939.220188022</v>
       </c>
       <c r="F157" s="0">
-        <v>-9987687.3476036787</v>
+        <v>-1603248.2721771598</v>
       </c>
       <c r="G157" s="0">
-        <v>175330631.399739</v>
+        <v>56339755.48538164</v>
       </c>
     </row>
     <row r="158">
@@ -6571,13 +6571,13 @@
         <v>109</v>
       </c>
       <c r="E158" s="0">
-        <v>157202516.49961102</v>
+        <v>49338340.210312724</v>
       </c>
       <c r="F158" s="0">
-        <v>-28939364.717662215</v>
+        <v>-8281160.2623112202</v>
       </c>
       <c r="G158" s="0">
-        <v>159844042.81696689</v>
+        <v>50028486.185358874</v>
       </c>
     </row>
     <row r="159">
@@ -6594,13 +6594,13 @@
         <v>116</v>
       </c>
       <c r="E159" s="0">
-        <v>151450660.76317275</v>
+        <v>47066019.559302807</v>
       </c>
       <c r="F159" s="0">
-        <v>-26825322.420158029</v>
+        <v>-7520338.8885926604</v>
       </c>
       <c r="G159" s="0">
-        <v>153807999.03953975</v>
+        <v>47663043.274175785</v>
       </c>
     </row>
     <row r="160">
@@ -6617,13 +6617,13 @@
         <v>101</v>
       </c>
       <c r="E160" s="0">
-        <v>160536464.9526366</v>
+        <v>50913551.388552308</v>
       </c>
       <c r="F160" s="0">
-        <v>-15512981.743940592</v>
+        <v>-3224142.7235850692</v>
       </c>
       <c r="G160" s="0">
-        <v>161284249.64043129</v>
+        <v>51015534.999613628</v>
       </c>
     </row>
     <row r="161">
@@ -6640,13 +6640,13 @@
         <v>109</v>
       </c>
       <c r="E161" s="0">
-        <v>158880532.85649371</v>
+        <v>50050733.240105182</v>
       </c>
       <c r="F161" s="0">
-        <v>-13857049.647797227</v>
+        <v>-2361324.5751380921</v>
       </c>
       <c r="G161" s="0">
-        <v>159483671.7212922</v>
+        <v>50106404.297468014</v>
       </c>
     </row>
     <row r="162">
@@ -6663,13 +6663,13 @@
         <v>102</v>
       </c>
       <c r="E162" s="0">
-        <v>160536464.9526366</v>
+        <v>50913551.388552308</v>
       </c>
       <c r="F162" s="0">
-        <v>-6023195.3671604395</v>
+        <v>911687.7623617053</v>
       </c>
       <c r="G162" s="0">
-        <v>160649417.86984509</v>
+        <v>50921713.340880394</v>
       </c>
     </row>
     <row r="163">
@@ -6686,13 +6686,13 @@
         <v>82</v>
       </c>
       <c r="E163" s="0">
-        <v>166536774.83307791</v>
+        <v>54581242.925873756</v>
       </c>
       <c r="F163" s="0">
-        <v>11396793.768011332</v>
+        <v>9068837.7727528811</v>
       </c>
       <c r="G163" s="0">
-        <v>166926283.96988255</v>
+        <v>55329521.034270242</v>
       </c>
     </row>
     <row r="164">
@@ -6709,13 +6709,13 @@
         <v>88</v>
       </c>
       <c r="E164" s="0">
-        <v>169577906.97706795</v>
+        <v>54948600.712714434</v>
       </c>
       <c r="F164" s="0">
-        <v>-1394589.6755223274</v>
+        <v>2331019.8902010918</v>
       </c>
       <c r="G164" s="0">
-        <v>169583641.35460171</v>
+        <v>54998021.546359591</v>
       </c>
     </row>
     <row r="165">
@@ -6732,13 +6732,13 @@
         <v>73</v>
       </c>
       <c r="E165" s="0">
-        <v>176550514.21636462</v>
+        <v>59659735.066591859</v>
       </c>
       <c r="F165" s="0">
-        <v>7354398.7236685753</v>
+        <v>5153043.8429509997</v>
       </c>
       <c r="G165" s="0">
-        <v>176703625.45983449</v>
+        <v>59881865.778074294</v>
       </c>
     </row>
     <row r="166">
@@ -6755,13 +6755,13 @@
         <v>69</v>
       </c>
       <c r="E166" s="0">
-        <v>188824491.9867723</v>
+        <v>70476966.772210896</v>
       </c>
       <c r="F166" s="0">
-        <v>35650378.458553188</v>
+        <v>23940991.017617758</v>
       </c>
       <c r="G166" s="0">
-        <v>192160449.25608575</v>
+        <v>74432344.423086479</v>
       </c>
     </row>
     <row r="167">
@@ -6778,13 +6778,13 @@
         <v>74</v>
       </c>
       <c r="E167" s="0">
-        <v>173564842.04689288</v>
+        <v>59078385.961133897</v>
       </c>
       <c r="F167" s="0">
-        <v>4368726.5541968346</v>
+        <v>4571694.7374929786</v>
       </c>
       <c r="G167" s="0">
-        <v>173619815.01680106</v>
+        <v>59255008.906804867</v>
       </c>
     </row>
     <row r="168">
@@ -6801,13 +6801,13 @@
         <v>81</v>
       </c>
       <c r="E168" s="0">
-        <v>172300091.06279755</v>
+        <v>56821917.773165703</v>
       </c>
       <c r="F168" s="0">
-        <v>4368726.5541968346</v>
+        <v>4571694.7374929786</v>
       </c>
       <c r="G168" s="0">
-        <v>172355467.42692462</v>
+        <v>57005532.470043868</v>
       </c>
     </row>
     <row r="169">
@@ -6824,13 +6824,13 @@
         <v>74</v>
       </c>
       <c r="E169" s="0">
-        <v>173564842.04689288</v>
+        <v>59078385.961133897</v>
       </c>
       <c r="F169" s="0">
-        <v>17506928.574088573</v>
+        <v>11878153.053825974</v>
       </c>
       <c r="G169" s="0">
-        <v>174445541.48175046</v>
+        <v>60260652.23462835</v>
       </c>
     </row>
     <row r="170">
@@ -6847,13 +6847,13 @@
         <v>75</v>
       </c>
       <c r="E170" s="0">
-        <v>167454707.24081588</v>
+        <v>56269070.680060744</v>
       </c>
       <c r="F170" s="0">
-        <v>34993257.577614784</v>
+        <v>23504098.212783933</v>
       </c>
       <c r="G170" s="0">
-        <v>171071935.31669843</v>
+        <v>60980742.435574398</v>
       </c>
     </row>
     <row r="171">
@@ -6870,13 +6870,13 @@
         <v>3</v>
       </c>
       <c r="E171" s="0">
-        <v>154320385.71335113</v>
+        <v>48442244.919713676</v>
       </c>
       <c r="F171" s="0">
-        <v>10059548.814092159</v>
+        <v>8881665.0859799385</v>
       </c>
       <c r="G171" s="0">
-        <v>154647909.68215695</v>
+        <v>49249721.49729418</v>
       </c>
     </row>
     <row r="172">
@@ -6893,13 +6893,13 @@
         <v>114</v>
       </c>
       <c r="E172" s="0">
-        <v>163602117.30222929</v>
+        <v>51785753.720137134</v>
       </c>
       <c r="F172" s="0">
-        <v>-33619982.512896776</v>
+        <v>-9929859.8926916122</v>
       </c>
       <c r="G172" s="0">
-        <v>167020825.07861072</v>
+        <v>52729179.832908295</v>
       </c>
     </row>
     <row r="173">
@@ -6916,13 +6916,13 @@
         <v>3</v>
       </c>
       <c r="E173" s="0">
-        <v>152702610.67199981</v>
+        <v>47640539.051052511</v>
       </c>
       <c r="F173" s="0">
-        <v>2729814.5454897881</v>
+        <v>5249336.2215431929</v>
       </c>
       <c r="G173" s="0">
-        <v>152727008.72307137</v>
+        <v>47928869.085778199</v>
       </c>
     </row>
     <row r="174">
@@ -6939,13 +6939,13 @@
         <v>103</v>
       </c>
       <c r="E174" s="0">
-        <v>152702610.67199993</v>
+        <v>47640539.051052511</v>
       </c>
       <c r="F174" s="0">
-        <v>-13857049.647797227</v>
+        <v>-2361324.5751380921</v>
       </c>
       <c r="G174" s="0">
-        <v>153330052.92826942</v>
+        <v>47699023.206183277</v>
       </c>
     </row>
     <row r="175">
@@ -6962,13 +6962,13 @@
         <v>3</v>
       </c>
       <c r="E175" s="0">
-        <v>157539283.10358882</v>
+        <v>50203257.982482374</v>
       </c>
       <c r="F175" s="0">
-        <v>19815222.079554081</v>
+        <v>14218855.425965786</v>
       </c>
       <c r="G175" s="0">
-        <v>158780567.91325176</v>
+        <v>52177993.078310289</v>
       </c>
     </row>
     <row r="176">
@@ -6985,13 +6985,13 @@
         <v>89</v>
       </c>
       <c r="E176" s="0">
-        <v>157539283.10358882</v>
+        <v>50203257.982482374</v>
       </c>
       <c r="F176" s="0">
-        <v>2399302.0385220051</v>
+        <v>4690852.8293614984</v>
       </c>
       <c r="G176" s="0">
-        <v>157557552.56751344</v>
+        <v>50421931.85829366</v>
       </c>
     </row>
     <row r="177">
@@ -7008,13 +7008,13 @@
         <v>4</v>
       </c>
       <c r="E177" s="0">
-        <v>151450660.76317263</v>
+        <v>47066019.559302807</v>
       </c>
       <c r="F177" s="0">
-        <v>-29201261.462487221</v>
+        <v>-8583347.4863801003</v>
       </c>
       <c r="G177" s="0">
-        <v>154240125.50760627</v>
+        <v>47842283.089633398</v>
       </c>
     </row>
     <row r="178">
@@ -7031,13 +7031,13 @@
         <v>116</v>
       </c>
       <c r="E178" s="0">
-        <v>157202516.49961102</v>
+        <v>49338340.210312724</v>
       </c>
       <c r="F178" s="0">
-        <v>-21073466.683719754</v>
+        <v>-5248018.2375827432</v>
       </c>
       <c r="G178" s="0">
-        <v>158608707.80597237</v>
+        <v>49616665.649059512</v>
       </c>
     </row>
     <row r="179">
@@ -7054,13 +7054,13 @@
         <v>4</v>
       </c>
       <c r="E179" s="0">
-        <v>151694947.55080372</v>
+        <v>47175314.853058785</v>
       </c>
       <c r="F179" s="0">
-        <v>-30659470.369553566</v>
+        <v>-9235758.4186332226</v>
       </c>
       <c r="G179" s="0">
-        <v>154762270.06535742</v>
+        <v>48070880.635292955</v>
       </c>
     </row>
     <row r="180">
@@ -7077,13 +7077,13 @@
         <v>123</v>
       </c>
       <c r="E180" s="0">
-        <v>155088474.20210731</v>
+        <v>48577518.836594284</v>
       </c>
       <c r="F180" s="0">
-        <v>-26825322.420158029</v>
+        <v>-7520338.8885926604</v>
       </c>
       <c r="G180" s="0">
-        <v>157391336.33489212</v>
+        <v>49156188.148787044</v>
       </c>
     </row>
     <row r="181">
@@ -7100,13 +7100,13 @@
         <v>3</v>
       </c>
       <c r="E181" s="0">
-        <v>151664115.82057119</v>
+        <v>47164039.577660531</v>
       </c>
       <c r="F181" s="0">
-        <v>-3533088.2797646523</v>
+        <v>2375687.0223846436</v>
       </c>
       <c r="G181" s="0">
-        <v>151705262.73148286</v>
+        <v>47223834.216542132</v>
       </c>
     </row>
     <row r="182">
@@ -7123,13 +7123,13 @@
         <v>110</v>
       </c>
       <c r="E182" s="0">
-        <v>151664115.82057119</v>
+        <v>47164039.577660531</v>
       </c>
       <c r="F182" s="0">
-        <v>-21073466.683719754</v>
+        <v>-5248018.2375827432</v>
       </c>
       <c r="G182" s="0">
-        <v>153121177.58724782</v>
+        <v>47455119.056906074</v>
       </c>
     </row>
     <row r="183">
@@ -7146,13 +7146,13 @@
         <v>3</v>
       </c>
       <c r="E183" s="0">
-        <v>149846614.32922474</v>
+        <v>46384628.208934985</v>
       </c>
       <c r="F183" s="0">
-        <v>-17220237.635721684</v>
+        <v>-3493865.142645359</v>
       </c>
       <c r="G183" s="0">
-        <v>150832835.98130131</v>
+        <v>46516027.643341594</v>
       </c>
     </row>
     <row r="184">
@@ -7169,13 +7169,13 @@
         <v>126</v>
       </c>
       <c r="E184" s="0">
-        <v>132042981.98683448</v>
+        <v>41684548.909588069</v>
       </c>
       <c r="F184" s="0">
-        <v>-49510516.087928563</v>
+        <v>-15571086.162154838</v>
       </c>
       <c r="G184" s="0">
-        <v>141019999.62866446</v>
+        <v>44497868.960941151</v>
       </c>
     </row>
     <row r="185">
@@ -7192,13 +7192,13 @@
         <v>4</v>
       </c>
       <c r="E185" s="0">
-        <v>151712034.62180519</v>
+        <v>47247302.446537398</v>
       </c>
       <c r="F185" s="0">
-        <v>-30835935.738969386</v>
+        <v>-9538882.4257850349</v>
       </c>
       <c r="G185" s="0">
-        <v>154814070.36179128</v>
+        <v>48200600.270199224</v>
       </c>
     </row>
     <row r="186">
@@ -7215,13 +7215,13 @@
         <v>123</v>
       </c>
       <c r="E186" s="0">
-        <v>152746652.37657824</v>
+        <v>47786030.708137348</v>
       </c>
       <c r="F186" s="0">
-        <v>-32572150.365150094</v>
+        <v>-9947196.82994093</v>
       </c>
       <c r="G186" s="0">
-        <v>156180936.06987116</v>
+        <v>48810362.174569368</v>
       </c>
     </row>
     <row r="187">
@@ -7238,13 +7238,13 @@
         <v>4</v>
       </c>
       <c r="E187" s="0">
-        <v>151778767.27336663</v>
+        <v>47234898.083202451</v>
       </c>
       <c r="F187" s="0">
-        <v>-31034081.664618492</v>
+        <v>-9502050.7699528337</v>
       </c>
       <c r="G187" s="0">
-        <v>154919038.27415466</v>
+        <v>48181164.014221199</v>
       </c>
     </row>
     <row r="188">
@@ -7261,13 +7261,13 @@
         <v>116</v>
       </c>
       <c r="E188" s="0">
-        <v>155088474.20210731</v>
+        <v>48577518.836594284</v>
       </c>
       <c r="F188" s="0">
-        <v>-32560670.896991014</v>
+        <v>-9714031.0005851835</v>
       </c>
       <c r="G188" s="0">
-        <v>158469656.77882898</v>
+        <v>49539254.481673442</v>
       </c>
     </row>
     <row r="189">
@@ -7284,13 +7284,13 @@
         <v>4</v>
       </c>
       <c r="E189" s="0">
-        <v>151712034.62180507</v>
+        <v>47247302.446537428</v>
       </c>
       <c r="F189" s="0">
-        <v>-30835935.738969281</v>
+        <v>-9538882.4257850647</v>
       </c>
       <c r="G189" s="0">
-        <v>154814070.36179116</v>
+        <v>48200600.270199254</v>
       </c>
     </row>
     <row r="190">
@@ -7307,13 +7307,13 @@
         <v>135</v>
       </c>
       <c r="E190" s="0">
-        <v>151712034.62180522</v>
+        <v>47247302.446537405</v>
       </c>
       <c r="F190" s="0">
-        <v>-30835935.738969281</v>
+        <v>-9538882.4257850647</v>
       </c>
       <c r="G190" s="0">
-        <v>154814070.36179131</v>
+        <v>48200600.270199232</v>
       </c>
     </row>
     <row r="191">
@@ -7330,13 +7330,13 @@
         <v>135</v>
       </c>
       <c r="E191" s="0">
-        <v>151361236.18610129</v>
+        <v>47312509.375259444</v>
       </c>
       <c r="F191" s="0">
-        <v>-31186734.174673229</v>
+        <v>-9473675.4970630407</v>
       </c>
       <c r="G191" s="0">
-        <v>154540726.69774291</v>
+        <v>48251674.27983889</v>
       </c>
     </row>
     <row r="192">
@@ -7353,13 +7353,13 @@
         <v>115</v>
       </c>
       <c r="E192" s="0">
-        <v>158709780.38143617</v>
+        <v>50010389.574868262</v>
       </c>
       <c r="F192" s="0">
-        <v>-28939364.717662215</v>
+        <v>-8281160.2623112202</v>
       </c>
       <c r="G192" s="0">
-        <v>161326628.98289785</v>
+        <v>50691386.652173705</v>
       </c>
     </row>
     <row r="193">
@@ -7376,13 +7376,13 @@
         <v>130</v>
       </c>
       <c r="E193" s="0">
-        <v>152746652.37657824</v>
+        <v>47786030.708137348</v>
       </c>
       <c r="F193" s="0">
-        <v>-30218849.071461618</v>
+        <v>-8922542.8721281439</v>
       </c>
       <c r="G193" s="0">
-        <v>155707156.71238434</v>
+        <v>48611896.714117318</v>
       </c>
     </row>
     <row r="194">
@@ -7399,13 +7399,13 @@
         <v>123</v>
       </c>
       <c r="E194" s="0">
-        <v>151694947.55080366</v>
+        <v>47175314.853058785</v>
       </c>
       <c r="F194" s="0">
-        <v>-30218849.071461618</v>
+        <v>-8922542.8721281439</v>
       </c>
       <c r="G194" s="0">
-        <v>154675582.92000988</v>
+        <v>48011687.147924654</v>
       </c>
     </row>
     <row r="195">
@@ -7422,13 +7422,13 @@
         <v>115</v>
       </c>
       <c r="E195" s="0">
-        <v>163390398.17667091</v>
+        <v>51659089.205248713</v>
       </c>
       <c r="F195" s="0">
-        <v>-22751483.040602326</v>
+        <v>-5960411.2673752308</v>
       </c>
       <c r="G195" s="0">
-        <v>164966821.50322798</v>
+        <v>52001807.660812117</v>
       </c>
     </row>
     <row r="196">
@@ -7445,13 +7445,13 @@
         <v>108</v>
       </c>
       <c r="E196" s="0">
-        <v>158880532.85649371</v>
+        <v>50050733.240105182</v>
       </c>
       <c r="F196" s="0">
-        <v>-22751483.040602326</v>
+        <v>-5960411.2673752308</v>
       </c>
       <c r="G196" s="0">
-        <v>160501257.63155314</v>
+        <v>50404388.701267108</v>
       </c>
     </row>
     <row r="197">
@@ -7468,13 +7468,13 @@
         <v>121</v>
       </c>
       <c r="E197" s="0">
-        <v>150058730.09902474</v>
+        <v>47356159.447437182</v>
       </c>
       <c r="F197" s="0">
-        <v>-41775237.306316435</v>
+        <v>-13017146.967483103</v>
       </c>
       <c r="G197" s="0">
-        <v>155765185.23383525</v>
+        <v>49112645.548617601</v>
       </c>
     </row>
     <row r="198">
@@ -7491,13 +7491,13 @@
         <v>130</v>
       </c>
       <c r="E198" s="0">
-        <v>149517364.52191013</v>
+        <v>46924206.419529468</v>
       </c>
       <c r="F198" s="0">
-        <v>-32572150.365150094</v>
+        <v>-9947196.82994093</v>
       </c>
       <c r="G198" s="0">
-        <v>153024139.51069191</v>
+        <v>47966945.627965488</v>
       </c>
     </row>
     <row r="199">
@@ -7514,13 +7514,13 @@
         <v>122</v>
       </c>
       <c r="E199" s="0">
-        <v>150058730.09902474</v>
+        <v>47356159.447437182</v>
       </c>
       <c r="F199" s="0">
-        <v>-38512319.433689892</v>
+        <v>-11705224.037960485</v>
       </c>
       <c r="G199" s="0">
-        <v>154921984.32467395</v>
+        <v>48781329.495924376</v>
       </c>
     </row>
     <row r="200">
@@ -7537,13 +7537,13 @@
         <v>129</v>
       </c>
       <c r="E200" s="0">
-        <v>144096410.48068586</v>
+        <v>45381199.427858606</v>
       </c>
       <c r="F200" s="0">
-        <v>-35812917.687977314</v>
+        <v>-11042186.947904572</v>
       </c>
       <c r="G200" s="0">
-        <v>148480101.65252498</v>
+        <v>46705279.724069186</v>
       </c>
     </row>
     <row r="201">
@@ -7560,13 +7560,13 @@
         <v>4</v>
       </c>
       <c r="E201" s="0">
-        <v>151528850.96005535</v>
+        <v>47281352.894769318</v>
       </c>
       <c r="F201" s="0">
-        <v>-30728278.700958967</v>
+        <v>-9558893.8742109574</v>
       </c>
       <c r="G201" s="0">
-        <v>154613129.40755865</v>
+        <v>48237939.255923226</v>
       </c>
     </row>
     <row r="202">
@@ -7583,13 +7583,13 @@
         <v>134</v>
       </c>
       <c r="E202" s="0">
-        <v>151361236.18610129</v>
+        <v>47312509.375259444</v>
       </c>
       <c r="F202" s="0">
-        <v>-30728278.700958967</v>
+        <v>-9558893.8742109574</v>
       </c>
       <c r="G202" s="0">
-        <v>154448861.86601877</v>
+        <v>48268478.280161686</v>
       </c>
     </row>
     <row r="203">
@@ -7606,13 +7606,13 @@
         <v>4</v>
       </c>
       <c r="E203" s="0">
-        <v>150613240.80737638</v>
+        <v>47118783.099357382</v>
       </c>
       <c r="F203" s="0">
-        <v>-30391963.646753043</v>
+        <v>-9499179.9562337082</v>
       </c>
       <c r="G203" s="0">
-        <v>153649014.83838516</v>
+        <v>48066767.528149828</v>
       </c>
     </row>
     <row r="204">
@@ -7629,13 +7629,13 @@
         <v>5</v>
       </c>
       <c r="E204" s="0">
-        <v>54003721.627521366</v>
+        <v>17079368.940680944</v>
       </c>
       <c r="F204" s="0">
-        <v>-54003721.627521418</v>
+        <v>-17079368.940680958</v>
       </c>
       <c r="G204" s="0">
-        <v>76372795.544261992</v>
+        <v>24153875.192684803</v>
       </c>
     </row>
     <row r="205">
@@ -7652,13 +7652,13 @@
         <v>129</v>
       </c>
       <c r="E205" s="0">
-        <v>152758131.84473735</v>
+        <v>48019196.537493095</v>
       </c>
       <c r="F205" s="0">
-        <v>-35812917.687977314</v>
+        <v>-11042186.947904572</v>
       </c>
       <c r="G205" s="0">
-        <v>156900006.11223698</v>
+        <v>49272437.819726996</v>
       </c>
     </row>
     <row r="206">
@@ -7675,13 +7675,13 @@
         <v>128</v>
       </c>
       <c r="E206" s="0">
-        <v>132042981.98683448</v>
+        <v>41684548.909588069</v>
       </c>
       <c r="F206" s="0">
-        <v>-41775237.306316435</v>
+        <v>-13017146.967483103</v>
       </c>
       <c r="G206" s="0">
-        <v>138493752.72543722</v>
+        <v>43669757.647242494</v>
       </c>
     </row>
     <row r="207">
@@ -7698,13 +7698,13 @@
         <v>4</v>
       </c>
       <c r="E207" s="0">
-        <v>148104578.84475327</v>
+        <v>46449898.097746849</v>
       </c>
       <c r="F207" s="0">
-        <v>-29721808.812465057</v>
+        <v>-9320496.4492125642</v>
       </c>
       <c r="G207" s="0">
-        <v>151057446.66803575</v>
+        <v>47375781.654246613</v>
       </c>
     </row>
     <row r="208">
@@ -7721,13 +7721,13 @@
         <v>132</v>
       </c>
       <c r="E208" s="0">
-        <v>144096410.48068586</v>
+        <v>45381199.427858606</v>
       </c>
       <c r="F208" s="0">
-        <v>-29721808.812465064</v>
+        <v>-9320496.449212566</v>
       </c>
       <c r="G208" s="0">
-        <v>147129743.53441605</v>
+        <v>46328446.073345244</v>
       </c>
     </row>
     <row r="209">
@@ -7744,13 +7744,13 @@
         <v>106</v>
       </c>
       <c r="E209" s="0">
-        <v>208486409.17898542</v>
+        <v>66485441.415791899</v>
       </c>
       <c r="F209" s="0">
-        <v>-28438338.237351656</v>
+        <v>-8605442.7391520441</v>
       </c>
       <c r="G209" s="0">
-        <v>210417019.02186847</v>
+        <v>67040044.488272242</v>
       </c>
     </row>
     <row r="210">
@@ -7767,13 +7767,13 @@
         <v>113</v>
       </c>
       <c r="E210" s="0">
-        <v>174109697.05597651</v>
+        <v>55275840.606324703</v>
       </c>
       <c r="F210" s="0">
-        <v>-86387142.924424708</v>
+        <v>-27172170.812725395</v>
       </c>
       <c r="G210" s="0">
-        <v>194362869.5805063</v>
+        <v>61593387.805930443</v>
       </c>
     </row>
     <row r="211">
@@ -7790,13 +7790,13 @@
         <v>113</v>
       </c>
       <c r="E211" s="0">
-        <v>171530261.67248017</v>
+        <v>54500625.251918346</v>
       </c>
       <c r="F211" s="0">
-        <v>-41548126.883147418</v>
+        <v>-12644731.424472898</v>
       </c>
       <c r="G211" s="0">
-        <v>176490445.96500865</v>
+        <v>55948256.323562861</v>
       </c>
     </row>
     <row r="212">
@@ -7813,13 +7813,13 @@
         <v>91</v>
       </c>
       <c r="E212" s="0">
-        <v>189590246.21322036</v>
+        <v>61106487.945603401</v>
       </c>
       <c r="F212" s="0">
-        <v>-8497181.6905038357</v>
+        <v>-2150415.4289316535</v>
       </c>
       <c r="G212" s="0">
-        <v>189780566.85517341</v>
+        <v>61144314.171991177</v>
       </c>
     </row>
     <row r="213">
@@ -7836,13 +7836,13 @@
         <v>122</v>
       </c>
       <c r="E213" s="0">
-        <v>158709780.38143617</v>
+        <v>50010389.574868262</v>
       </c>
       <c r="F213" s="0">
-        <v>-38512319.433689892</v>
+        <v>-11705224.037960485</v>
       </c>
       <c r="G213" s="0">
-        <v>163315624.28894019</v>
+        <v>51361963.895561278</v>
       </c>
     </row>
     <row r="214">
@@ -7859,13 +7859,13 @@
         <v>121</v>
       </c>
       <c r="E214" s="0">
-        <v>139778260.76844648</v>
+        <v>44238488.104259804</v>
       </c>
       <c r="F214" s="0">
-        <v>-52055706.636894703</v>
+        <v>-16134818.310660481</v>
       </c>
       <c r="G214" s="0">
-        <v>149156826.11573053</v>
+        <v>47089024.110388622</v>
       </c>
     </row>
     <row r="215">
@@ -7882,13 +7882,13 @@
         <v>107</v>
       </c>
       <c r="E215" s="0">
-        <v>174385372.41643739</v>
+        <v>55696661.413889647</v>
       </c>
       <c r="F215" s="0">
-        <v>-17213780.753805637</v>
+        <v>-4178664.2160276771</v>
       </c>
       <c r="G215" s="0">
-        <v>175232908.89744326</v>
+        <v>55853194.423271567</v>
       </c>
     </row>
     <row r="216">
@@ -7905,13 +7905,13 @@
         <v>100</v>
       </c>
       <c r="E216" s="0">
-        <v>167819833.16302061</v>
+        <v>53741523.276337504</v>
       </c>
       <c r="F216" s="0">
-        <v>-17213780.753805637</v>
+        <v>-4178664.2160276771</v>
       </c>
       <c r="G216" s="0">
-        <v>168700357.58914134</v>
+        <v>53903734.181329556</v>
       </c>
     </row>
     <row r="217">
@@ -7928,13 +7928,13 @@
         <v>94</v>
       </c>
       <c r="E217" s="0">
-        <v>169577906.97706795</v>
+        <v>54948600.712714434</v>
       </c>
       <c r="F217" s="0">
-        <v>-9987687.3476036787</v>
+        <v>-1603248.2721771598</v>
       </c>
       <c r="G217" s="0">
-        <v>169871776.44705018</v>
+        <v>54971984.913295247</v>
       </c>
     </row>
     <row r="218">
@@ -7951,13 +7951,13 @@
         <v>93</v>
       </c>
       <c r="E218" s="0">
-        <v>182529680.13401163</v>
+        <v>58820020.375882685</v>
       </c>
       <c r="F218" s="0">
-        <v>-10390581.34180212</v>
+        <v>-2295860.8666314483</v>
       </c>
       <c r="G218" s="0">
-        <v>182825185.10983437</v>
+        <v>58864809.301807679</v>
       </c>
     </row>
     <row r="219">
@@ -7974,13 +7974,13 @@
         <v>73</v>
       </c>
       <c r="E219" s="0">
-        <v>181797148.50814509</v>
+        <v>63113113.35233295</v>
       </c>
       <c r="F219" s="0">
-        <v>2107764.4318883419</v>
+        <v>1699665.5572100282</v>
       </c>
       <c r="G219" s="0">
-        <v>181809366.85603657</v>
+        <v>63135995.597050607</v>
       </c>
     </row>
     <row r="220">
@@ -7997,13 +7997,13 @@
         <v>72</v>
       </c>
       <c r="E220" s="0">
-        <v>180056788.63764024</v>
+        <v>59482225.130085588</v>
       </c>
       <c r="F220" s="0">
-        <v>-369690.23229765892</v>
+        <v>63148.602164804936</v>
       </c>
       <c r="G220" s="0">
-        <v>180057168.15880367</v>
+        <v>59482258.650560178</v>
       </c>
     </row>
     <row r="221">
@@ -8020,13 +8020,13 @@
         <v>86</v>
       </c>
       <c r="E221" s="0">
-        <v>176535168.22467852</v>
+        <v>58098092.387482345</v>
       </c>
       <c r="F221" s="0">
-        <v>118303.40062952042</v>
+        <v>1733877.4440669417</v>
       </c>
       <c r="G221" s="0">
-        <v>176535207.86463574</v>
+        <v>58123959.518046238</v>
       </c>
     </row>
     <row r="222">
@@ -8043,13 +8043,13 @@
         <v>79</v>
       </c>
       <c r="E222" s="0">
-        <v>176550514.21636462</v>
+        <v>59659735.066591859</v>
       </c>
       <c r="F222" s="0">
-        <v>118303.40062952042</v>
+        <v>1733877.4440669417</v>
       </c>
       <c r="G222" s="0">
-        <v>176550553.85287628</v>
+        <v>59684925.3933267</v>
       </c>
     </row>
     <row r="223">
@@ -8066,13 +8066,13 @@
         <v>78</v>
       </c>
       <c r="E223" s="0">
-        <v>179851786.02487302</v>
+        <v>58935376.782386959</v>
       </c>
       <c r="F223" s="0">
-        <v>-4418626.9646704197</v>
+        <v>-891639.58729398251</v>
       </c>
       <c r="G223" s="0">
-        <v>179906056.59785226</v>
+        <v>58942121.251576498</v>
       </c>
     </row>
     <row r="224">
@@ -8089,13 +8089,13 @@
         <v>85</v>
       </c>
       <c r="E224" s="0">
-        <v>180636280.4827131</v>
+        <v>58674574.93818289</v>
       </c>
       <c r="F224" s="0">
-        <v>-5203121.4225091934</v>
+        <v>-630837.74309045076</v>
       </c>
       <c r="G224" s="0">
-        <v>180711201.36606577</v>
+        <v>58677966.055705674</v>
       </c>
     </row>
     <row r="225">
@@ -8112,13 +8112,13 @@
         <v>112</v>
       </c>
       <c r="E225" s="0">
-        <v>184743158.79458308</v>
+        <v>58860996.668397963</v>
       </c>
       <c r="F225" s="0">
-        <v>-52181588.621753991</v>
+        <v>-16229887.48654598</v>
       </c>
       <c r="G225" s="0">
-        <v>191971229.38734987</v>
+        <v>61057564.450468361</v>
       </c>
     </row>
     <row r="226">
@@ -8135,13 +8135,13 @@
         <v>99</v>
       </c>
       <c r="E226" s="0">
-        <v>175045926.56922257</v>
+        <v>56316939.220188022</v>
       </c>
       <c r="F226" s="0">
-        <v>-17874334.906591177</v>
+        <v>-4798942.0223261118</v>
       </c>
       <c r="G226" s="0">
-        <v>175956154.35906368</v>
+        <v>56521035.797869094</v>
       </c>
     </row>
     <row r="227">
@@ -8158,13 +8158,13 @@
         <v>113</v>
       </c>
       <c r="E227" s="0">
-        <v>184743158.79458308</v>
+        <v>58860996.668397963</v>
       </c>
       <c r="F227" s="0">
-        <v>-28335229.761044502</v>
+        <v>-8284360.0079932809</v>
       </c>
       <c r="G227" s="0">
-        <v>186903504.42678094</v>
+        <v>59441126.751931563</v>
       </c>
     </row>
     <row r="228">
@@ -8181,13 +8181,13 @@
         <v>106</v>
       </c>
       <c r="E228" s="0">
-        <v>174385372.41643739</v>
+        <v>55696661.413889647</v>
       </c>
       <c r="F228" s="0">
-        <v>-28335229.761044502</v>
+        <v>-8284360.0079932809</v>
       </c>
       <c r="G228" s="0">
-        <v>176672418.21640056</v>
+        <v>56309401.643024966</v>
       </c>
     </row>
     <row r="229">
@@ -8204,13 +8204,13 @@
         <v>97</v>
       </c>
       <c r="E229" s="0">
-        <v>207984508.29102218</v>
+        <v>66628547.799273908</v>
       </c>
       <c r="F229" s="0">
-        <v>-7421136.2444033623</v>
+        <v>-2192731.8041991889</v>
       </c>
       <c r="G229" s="0">
-        <v>208116863.69013029</v>
+        <v>66664619.211432345</v>
       </c>
     </row>
     <row r="230">
@@ -8227,13 +8227,13 @@
         <v>98</v>
       </c>
       <c r="E230" s="0">
-        <v>197726857.7385298</v>
+        <v>63350639.140056491</v>
       </c>
       <c r="F230" s="0">
-        <v>-15557747.769712567</v>
+        <v>-4436882.9986523688</v>
       </c>
       <c r="G230" s="0">
-        <v>198337978.67987564</v>
+        <v>63505821.860656113</v>
       </c>
     </row>
     <row r="231">
@@ -8250,13 +8250,13 @@
         <v>70</v>
       </c>
       <c r="E231" s="0">
-        <v>181094564.99579382</v>
+        <v>59384635.897986829</v>
       </c>
       <c r="F231" s="0">
-        <v>-1007164.4764130116</v>
+        <v>-238422.92007499933</v>
       </c>
       <c r="G231" s="0">
-        <v>181097365.66636837</v>
+        <v>59385114.517236412</v>
       </c>
     </row>
     <row r="232">
@@ -8273,13 +8273,13 @@
         <v>77</v>
       </c>
       <c r="E232" s="0">
-        <v>182178906.75446248</v>
+        <v>59486614.673796296</v>
       </c>
       <c r="F232" s="0">
-        <v>-2091506.235080719</v>
+        <v>-340401.69588464499</v>
       </c>
       <c r="G232" s="0">
-        <v>182190912.13499788</v>
+        <v>59487588.610257834</v>
       </c>
     </row>
     <row r="233">
@@ -8296,13 +8296,13 @@
         <v>77</v>
       </c>
       <c r="E233" s="0">
-        <v>181094564.99579382</v>
+        <v>59384635.897986829</v>
       </c>
       <c r="F233" s="0">
-        <v>-1053729.8769271374</v>
+        <v>-437990.92798340321</v>
       </c>
       <c r="G233" s="0">
-        <v>181097630.62411755</v>
+        <v>59386251.075391702</v>
       </c>
     </row>
     <row r="234">
@@ -8319,13 +8319,13 @@
         <v>70</v>
       </c>
       <c r="E234" s="0">
-        <v>180740828.28227067</v>
+        <v>59983364.660234928</v>
       </c>
       <c r="F234" s="0">
-        <v>-1053729.876926899</v>
+        <v>-437990.92798340321</v>
       </c>
       <c r="G234" s="0">
-        <v>180743899.91038364</v>
+        <v>59984963.716049016</v>
       </c>
     </row>
     <row r="235">
@@ -8342,13 +8342,13 @@
         <v>76</v>
       </c>
       <c r="E235" s="0">
-        <v>183054440.78863573</v>
+        <v>59693095.234991074</v>
       </c>
       <c r="F235" s="0">
-        <v>-1007164.47641325</v>
+        <v>-238422.92007505894</v>
       </c>
       <c r="G235" s="0">
-        <v>183057211.47423473</v>
+        <v>59693571.381033413</v>
       </c>
     </row>
     <row r="236">
@@ -8365,13 +8365,13 @@
         <v>83</v>
       </c>
       <c r="E236" s="0">
-        <v>186453907.38378906</v>
+        <v>60465725.561699391</v>
       </c>
       <c r="F236" s="0">
-        <v>-1882698.5105862618</v>
+        <v>-444903.48126977682</v>
       </c>
       <c r="G236" s="0">
-        <v>186463412.31556487</v>
+        <v>60467362.32721246</v>
       </c>
     </row>
     <row r="237">
@@ -8388,13 +8388,13 @@
         <v>97</v>
       </c>
       <c r="E237" s="0">
-        <v>193389611.77179492</v>
+        <v>62321941.486653954</v>
       </c>
       <c r="F237" s="0">
-        <v>-3621770.685828805</v>
+        <v>-977278.26314860582</v>
       </c>
       <c r="G237" s="0">
-        <v>193423522.77876207</v>
+        <v>62329603.427821852</v>
       </c>
     </row>
     <row r="238">
@@ -8411,13 +8411,13 @@
         <v>90</v>
       </c>
       <c r="E238" s="0">
-        <v>184714835.20854652</v>
+        <v>59933350.779820561</v>
       </c>
       <c r="F238" s="0">
-        <v>-3621770.685828805</v>
+        <v>-977278.26314860582</v>
       </c>
       <c r="G238" s="0">
-        <v>184750338.48147944</v>
+        <v>59941318.041069478</v>
       </c>
     </row>
     <row r="239">
@@ -8434,13 +8434,13 @@
         <v>105</v>
       </c>
       <c r="E239" s="0">
-        <v>208486409.17898542</v>
+        <v>66485441.415791899</v>
       </c>
       <c r="F239" s="0">
-        <v>-52352746.442092359</v>
+        <v>-16497204.969833791</v>
       </c>
       <c r="G239" s="0">
-        <v>214959049.29166707</v>
+        <v>68501618.171174645</v>
       </c>
     </row>
     <row r="240">
@@ -8457,13 +8457,13 @@
         <v>98</v>
       </c>
       <c r="E240" s="0">
-        <v>197726857.7385298</v>
+        <v>63350639.140056491</v>
       </c>
       <c r="F240" s="0">
-        <v>-17678786.796895623</v>
+        <v>-5470640.4634165764</v>
       </c>
       <c r="G240" s="0">
-        <v>198515615.9443455</v>
+        <v>63586408.819288008</v>
       </c>
     </row>
     <row r="241">
@@ -8480,13 +8480,13 @@
         <v>105</v>
       </c>
       <c r="E241" s="0">
-        <v>243160368.82418203</v>
+        <v>77512005.922209129</v>
       </c>
       <c r="F241" s="0">
-        <v>-17678786.796895623</v>
+        <v>-5470640.4634165764</v>
       </c>
       <c r="G241" s="0">
-        <v>243802183.06922999</v>
+        <v>77704819.471925646</v>
       </c>
     </row>
     <row r="242">
@@ -8503,13 +8503,13 @@
         <v>126</v>
       </c>
       <c r="E242" s="0">
-        <v>102901633.93195033</v>
+        <v>32637403.453689247</v>
       </c>
       <c r="F242" s="0">
-        <v>-86387142.924424708</v>
+        <v>-27172170.812725395</v>
       </c>
       <c r="G242" s="0">
-        <v>134355813.8991763</v>
+        <v>42467952.280217282</v>
       </c>
     </row>
     <row r="243">
@@ -8526,13 +8526,13 @@
         <v>118</v>
       </c>
       <c r="E243" s="0">
-        <v>347763265.26767617</v>
+        <v>110473810.25421034</v>
       </c>
       <c r="F243" s="0">
-        <v>-52352746.4420923</v>
+        <v>-16497204.969833776</v>
       </c>
       <c r="G243" s="0">
-        <v>351681814.61324686</v>
+        <v>111698793.74415812</v>
       </c>
     </row>
     <row r="244">
@@ -8549,13 +8549,13 @@
         <v>126</v>
       </c>
       <c r="E244" s="0">
-        <v>102901633.93195033</v>
+        <v>32637403.453689247</v>
       </c>
       <c r="F244" s="0">
-        <v>-54003721.627521426</v>
+        <v>-17079368.940680958</v>
       </c>
       <c r="G244" s="0">
-        <v>116211652.66653743</v>
+        <v>36836190.731545299</v>
       </c>
     </row>
     <row r="245">
@@ -8572,13 +8572,13 @@
         <v>132</v>
       </c>
       <c r="E245" s="0">
-        <v>104139875.86397332</v>
+        <v>32942563.886980385</v>
       </c>
       <c r="F245" s="0">
-        <v>-21607409.965067424</v>
+        <v>-6829101.1395471543</v>
       </c>
       <c r="G245" s="0">
-        <v>106357857.77441302</v>
+        <v>33642965.651409932</v>
       </c>
     </row>
     <row r="246">
@@ -8595,13 +8595,13 @@
         <v>125</v>
       </c>
       <c r="E246" s="0">
-        <v>-34895404.791650027</v>
+        <v>-11036118.897169994</v>
       </c>
       <c r="F246" s="0">
-        <v>-191800760.35112166</v>
+        <v>-60752891.291540176</v>
       </c>
       <c r="G246" s="0">
-        <v>194949277.88232896</v>
+        <v>61747143.420519225</v>
       </c>
     </row>
     <row r="247">
@@ -8618,13 +8618,13 @@
         <v>118</v>
       </c>
       <c r="E247" s="0">
-        <v>208315251.35864714</v>
+        <v>66218123.932504058</v>
       </c>
       <c r="F247" s="0">
-        <v>-191800760.35112163</v>
+        <v>-60752891.291540161</v>
       </c>
       <c r="G247" s="0">
-        <v>283165632.83683407</v>
+        <v>89865197.58739844</v>
       </c>
     </row>
   </sheetData>
